--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0634D1FD-939A-45C1-8434-6B2823073284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062D0C70-862E-404E-9B99-B983BAAC96FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A4CA0B7-5981-4D71-A56A-F7CB4EA59286}"/>
   </bookViews>
@@ -577,10 +577,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83062106-38A0-4DD9-9B63-18A3210D82FB}">
-  <sheetPr>
+  <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="11.42578125" style="1"/>
@@ -617,37 +617,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>7318</v>
+        <v>5377</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2">
-        <v>8624</v>
+        <v>3218</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>9001</v>
+        <v>6531</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>6077</v>
+        <v>4504</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>7318</v>
+        <v>3016</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="L2" s="2">
-        <v>8624</v>
+        <v>9943</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -655,37 +655,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>2645</v>
+        <v>8008</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="2">
-        <v>4157</v>
+        <v>1058</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>2951</v>
+        <v>8216</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>2468</v>
+        <v>7612</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>2645</v>
+        <v>5551</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="L3" s="2">
-        <v>4157</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -693,37 +693,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>9801</v>
+        <v>8613</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2">
-        <v>7014</v>
+        <v>4089</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>1234</v>
+        <v>7792</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="2">
-        <v>1357</v>
+        <v>1439</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>9801</v>
+        <v>8688</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="2">
-        <v>1581</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -731,37 +731,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>2165</v>
+        <v>1764</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>5186</v>
+        <v>8058</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>5678</v>
+        <v>6066</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>8642</v>
+        <v>3560</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J5" s="2">
-        <v>8391</v>
+        <v>9390</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="2">
-        <v>5186</v>
+        <v>8036</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -769,37 +769,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>4176</v>
+        <v>7120</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="2">
-        <v>7341</v>
+        <v>2226</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>9012</v>
+        <v>9330</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="2">
-        <v>3591</v>
+        <v>1020</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J6" s="2">
-        <v>4176</v>
+        <v>1324</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="L6" s="2">
-        <v>7341</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -807,37 +807,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>8532</v>
+        <v>5895</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2">
-        <v>2918</v>
+        <v>8706</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="2">
-        <v>5386</v>
+        <v>6301</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="2">
-        <v>5791</v>
+        <v>8684</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="2">
-        <v>8532</v>
+        <v>7067</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2">
-        <v>2918</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -845,37 +845,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>1964</v>
+        <v>8962</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2">
-        <v>2481</v>
+        <v>4675</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>3456</v>
+        <v>2537</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H8" s="2">
-        <v>4026</v>
+        <v>1996</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="J8" s="2">
-        <v>1964</v>
+        <v>9836</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="L8" s="2">
-        <v>1033</v>
+        <v>9856</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -883,37 +883,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2963</v>
+        <v>7928</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="2">
-        <v>6803</v>
+        <v>5063</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="2">
-        <v>7890</v>
+        <v>5296</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="2">
-        <v>9183</v>
+        <v>5402</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="J9" s="2">
-        <v>6064</v>
+        <v>1330</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="2">
-        <v>6803</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -921,37 +921,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>7428</v>
+        <v>8131</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2">
-        <v>9572</v>
+        <v>2844</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2">
-        <v>2345</v>
+        <v>9632</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="2">
-        <v>9971</v>
+        <v>8597</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="2">
-        <v>7428</v>
+        <v>6409</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L10" s="2">
-        <v>9572</v>
+        <v>8913</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -959,37 +959,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>3159</v>
+        <v>4659</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2">
-        <v>3649</v>
+        <v>1248</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="2">
-        <v>1216</v>
+        <v>6394</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="2">
-        <v>6754</v>
+        <v>6164</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="2">
-        <v>3159</v>
+        <v>4904</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="L11" s="2">
-        <v>3649</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -997,37 +997,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>6847</v>
+        <v>2386</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="2">
-        <v>9876</v>
+        <v>9634</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="2">
-        <v>6789</v>
+        <v>9756</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="2">
-        <v>2839</v>
+        <v>6263</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="2">
-        <v>6847</v>
+        <v>4182</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="L12" s="2">
-        <v>8642</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1035,37 +1035,37 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>5291</v>
+        <v>9201</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2">
-        <v>1465</v>
+        <v>8118</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
-        <v>1122</v>
+        <v>5934</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="2">
-        <v>7461</v>
+        <v>5259</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="J13" s="2">
-        <v>5291</v>
+        <v>9947</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="2">
-        <v>1465</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1073,41 +1073,830 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>4871</v>
+        <v>8835</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="4">
-        <v>8820</v>
+        <v>2597</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="4">
-        <v>3344</v>
+        <v>7686</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="4">
-        <v>5902</v>
+        <v>3140</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="4">
-        <v>4093</v>
+        <v>5043</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="L14" s="4">
-        <v>8820</v>
-      </c>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>9842</v>
+      </c>
+      <c r="B18" s="1">
+        <v>7609</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5914</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7625</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3552</v>
+      </c>
+      <c r="F18" s="1">
+        <v>6914</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2749</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2064</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1993</v>
+      </c>
+      <c r="J18" s="1">
+        <v>9652</v>
+      </c>
+      <c r="K18" s="1">
+        <v>4487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2529</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8698</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6312</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7268</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4498</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3787</v>
+      </c>
+      <c r="G19" s="1">
+        <v>9086</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4298</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4593</v>
+      </c>
+      <c r="J19" s="1">
+        <v>7622</v>
+      </c>
+      <c r="K19" s="1">
+        <v>6906</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>6665</v>
+      </c>
+      <c r="B20" s="1">
+        <v>9623</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1429</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2068</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4994</v>
+      </c>
+      <c r="F20" s="1">
+        <v>9119</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4179</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2357</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5085</v>
+      </c>
+      <c r="J20" s="1">
+        <v>9171</v>
+      </c>
+      <c r="K20" s="1">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>7345</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3583</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6767</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4954</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7407</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1997</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1837</v>
+      </c>
+      <c r="H21" s="1">
+        <v>7799</v>
+      </c>
+      <c r="I21" s="1">
+        <v>7688</v>
+      </c>
+      <c r="J21" s="1">
+        <v>9446</v>
+      </c>
+      <c r="K21" s="1">
+        <v>7012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>4828</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1116</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1648</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1372</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4899</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3739</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5328</v>
+      </c>
+      <c r="H22" s="1">
+        <v>7324</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4387</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2949</v>
+      </c>
+      <c r="K22" s="1">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>5817</v>
+      </c>
+      <c r="B23" s="1">
+        <v>9182</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3205</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3347</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8392</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6515</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9455</v>
+      </c>
+      <c r="H23" s="1">
+        <v>9992</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1908</v>
+      </c>
+      <c r="J23" s="1">
+        <v>3596</v>
+      </c>
+      <c r="K23" s="1">
+        <v>9096</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>2768</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2621</v>
+      </c>
+      <c r="C24" s="1">
+        <v>4677</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6523</v>
+      </c>
+      <c r="E24" s="1">
+        <v>8868</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3892</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5861</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4433</v>
+      </c>
+      <c r="I24" s="1">
+        <v>4198</v>
+      </c>
+      <c r="J24" s="1">
+        <v>5237</v>
+      </c>
+      <c r="K24" s="1">
+        <v>7636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>2645</v>
+      </c>
+      <c r="B25" s="1">
+        <v>9237</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5806</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7401</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8322</v>
+      </c>
+      <c r="F25" s="1">
+        <v>4368</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3945</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1033</v>
+      </c>
+      <c r="I25" s="1">
+        <v>4150</v>
+      </c>
+      <c r="J25" s="1">
+        <v>7448</v>
+      </c>
+      <c r="K25" s="1">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>7069</v>
+      </c>
+      <c r="B26" s="1">
+        <v>8746</v>
+      </c>
+      <c r="C26" s="1">
+        <v>6217</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4444</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5086</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9707</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4753</v>
+      </c>
+      <c r="I26" s="1">
+        <v>6970</v>
+      </c>
+      <c r="J26" s="1">
+        <v>5888</v>
+      </c>
+      <c r="K26" s="1">
+        <v>7052</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>4397</v>
+      </c>
+      <c r="B27" s="1">
+        <v>8477</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2471</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3640</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1583</v>
+      </c>
+      <c r="F27" s="1">
+        <v>9640</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2394</v>
+      </c>
+      <c r="H27" s="1">
+        <v>8735</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5221</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2759</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>3408</v>
+      </c>
+      <c r="B28" s="1">
+        <v>8418</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4859</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8252</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1568</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2639</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4889</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1070</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4105</v>
+      </c>
+      <c r="J28" s="1">
+        <v>9745</v>
+      </c>
+      <c r="K28" s="1">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2785</v>
+      </c>
+      <c r="B29" s="1">
+        <v>5778</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2928</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1581</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6986</v>
+      </c>
+      <c r="F29" s="1">
+        <v>8181</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4590</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2535</v>
+      </c>
+      <c r="I29" s="1">
+        <v>8648</v>
+      </c>
+      <c r="J29" s="1">
+        <v>3441</v>
+      </c>
+      <c r="K29" s="1">
+        <v>7867</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>3647</v>
+      </c>
+      <c r="B30" s="1">
+        <v>8677</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5463</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1035</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7412</v>
+      </c>
+      <c r="F30" s="1">
+        <v>7759</v>
+      </c>
+      <c r="G30" s="1">
+        <v>5614</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1538</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1867</v>
+      </c>
+      <c r="J30" s="1">
+        <v>8872</v>
+      </c>
+      <c r="K30" s="1">
+        <v>9956</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>3422</v>
+      </c>
+      <c r="B31" s="1">
+        <v>8633</v>
+      </c>
+      <c r="C31" s="1">
+        <v>9091</v>
+      </c>
+      <c r="D31" s="1">
+        <v>8343</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5867</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5763</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7602</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1139</v>
+      </c>
+      <c r="I31" s="1">
+        <v>7595</v>
+      </c>
+      <c r="J31" s="1">
+        <v>9616</v>
+      </c>
+      <c r="K31" s="1">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>9793</v>
+      </c>
+      <c r="B32" s="1">
+        <v>6660</v>
+      </c>
+      <c r="C32" s="1">
+        <v>5106</v>
+      </c>
+      <c r="D32" s="1">
+        <v>4447</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4189</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2697</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3947</v>
+      </c>
+      <c r="H32" s="1">
+        <v>7818</v>
+      </c>
+      <c r="I32" s="1">
+        <v>9871</v>
+      </c>
+      <c r="J32" s="1">
+        <v>6698</v>
+      </c>
+      <c r="K32" s="1">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>6713</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2739</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6118</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1889</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8632</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3353</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2729</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5744</v>
+      </c>
+      <c r="I33" s="1">
+        <v>9060</v>
+      </c>
+      <c r="J33" s="1">
+        <v>9538</v>
+      </c>
+      <c r="K33" s="1">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1827</v>
+      </c>
+      <c r="B34" s="1">
+        <v>3653</v>
+      </c>
+      <c r="C34" s="1">
+        <v>7916</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2550</v>
+      </c>
+      <c r="E34" s="1">
+        <v>6389</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4425</v>
+      </c>
+      <c r="G34" s="1">
+        <v>3038</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5518</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1739</v>
+      </c>
+      <c r="J34" s="1">
+        <v>7822</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>1731</v>
+      </c>
+      <c r="B35" s="1">
+        <v>7367</v>
+      </c>
+      <c r="C35" s="1">
+        <v>5689</v>
+      </c>
+      <c r="D35" s="1">
+        <v>5759</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5276</v>
+      </c>
+      <c r="F35" s="1">
+        <v>6190</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2421</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5060</v>
+      </c>
+      <c r="I35" s="1">
+        <v>8892</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5737</v>
+      </c>
+      <c r="K35" s="1">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>9635</v>
+      </c>
+      <c r="B36" s="1">
+        <v>8516</v>
+      </c>
+      <c r="C36" s="1">
+        <v>7750</v>
+      </c>
+      <c r="D36" s="1">
+        <v>6393</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6545</v>
+      </c>
+      <c r="F36" s="1">
+        <v>9950</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6116</v>
+      </c>
+      <c r="H36" s="1">
+        <v>8017</v>
+      </c>
+      <c r="I36" s="1">
+        <v>6521</v>
+      </c>
+      <c r="J36" s="1">
+        <v>7486</v>
+      </c>
+      <c r="K36" s="1">
+        <v>8930</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>7101</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3981</v>
+      </c>
+      <c r="C37" s="1">
+        <v>6088</v>
+      </c>
+      <c r="D37" s="1">
+        <v>6346</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6270</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2212</v>
+      </c>
+      <c r="G37" s="1">
+        <v>7160</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4799</v>
+      </c>
+      <c r="I37" s="1">
+        <v>8022</v>
+      </c>
+      <c r="J37" s="1">
+        <v>9785</v>
+      </c>
+      <c r="K37" s="1">
+        <v>9733</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>2043</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3336</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1159</v>
+      </c>
+      <c r="D38" s="1">
+        <v>7027</v>
+      </c>
+      <c r="E38" s="1">
+        <v>7871</v>
+      </c>
+      <c r="F38" s="1">
+        <v>6856</v>
+      </c>
+      <c r="G38" s="1">
+        <v>7667</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>7753</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1083</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3210</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3758</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4596</v>
+      </c>
+      <c r="F39" s="1">
+        <v>8653</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6138</v>
+      </c>
+      <c r="H39" s="1">
+        <v>5440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>5792</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2154</v>
+      </c>
+      <c r="C40" s="1">
+        <v>9048</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2396</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4465</v>
+      </c>
+      <c r="F40" s="1">
+        <v>8979</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2233</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5591</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>8752</v>
+      </c>
+      <c r="B41" s="1">
+        <v>9316</v>
+      </c>
+      <c r="C41" s="1">
+        <v>9868</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062D0C70-862E-404E-9B99-B983BAAC96FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A4CA0B7-5981-4D71-A56A-F7CB4EA59286}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="31">
   <si>
     <t>EQUIPO 1</t>
   </si>
@@ -96,13 +90,49 @@
   </si>
   <si>
     <t>EQUIPO 6</t>
+  </si>
+  <si>
+    <t>EQUIPO 7</t>
+  </si>
+  <si>
+    <t>EQUIPO 8</t>
+  </si>
+  <si>
+    <t>EQUIPO 9</t>
+  </si>
+  <si>
+    <t>EQUIPO 10</t>
+  </si>
+  <si>
+    <t>EQUIPO 11</t>
+  </si>
+  <si>
+    <t>EQUIPO 12</t>
+  </si>
+  <si>
+    <t>EQUIPO 13</t>
+  </si>
+  <si>
+    <t>EQUIPO 14</t>
+  </si>
+  <si>
+    <t>EQUIPO 15</t>
+  </si>
+  <si>
+    <t>EQUIPO 16</t>
+  </si>
+  <si>
+    <t>EQUIPO 17</t>
+  </si>
+  <si>
+    <t>EQUIPO 18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -213,11 +243,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -241,6 +280,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -569,24 +614,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83062106-38A0-4DD9-9B63-18A3210D82FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" style="1"/>
+    <col min="1" max="6" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -612,7 +657,7 @@
       </c>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -650,7 +695,7 @@
         <v>9943</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -688,7 +733,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -726,7 +771,7 @@
         <v>6014</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -764,7 +809,7 @@
         <v>8036</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -802,7 +847,7 @@
         <v>6590</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -840,7 +885,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -878,7 +923,7 @@
         <v>9856</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -916,7 +961,7 @@
         <v>5988</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -954,7 +999,7 @@
         <v>8913</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -992,7 +1037,7 @@
         <v>6825</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1030,7 +1075,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15">
       <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
@@ -1068,7 +1113,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1106,800 +1151,1373 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="16" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="17" spans="1:12">
+      <c r="A17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="9">
         <v>9842</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9">
         <v>7609</v>
       </c>
-      <c r="C18" s="1">
+      <c r="E18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9">
         <v>5914</v>
       </c>
-      <c r="D18" s="1">
+      <c r="G18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="9">
         <v>7625</v>
       </c>
-      <c r="E18" s="1">
+      <c r="I18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2">
         <v>3552</v>
       </c>
-      <c r="F18" s="1">
+      <c r="K18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="2">
         <v>6914</v>
       </c>
-      <c r="G18" s="1">
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9">
+        <v>2529</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9">
+        <v>8698</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="9">
+        <v>6312</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="9">
+        <v>7268</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4498</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="9">
+        <v>6665</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="9">
+        <v>9623</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1429</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="9">
+        <v>2068</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>4994</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2">
+        <v>9119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="9">
+        <v>7345</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="9">
+        <v>3583</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="9">
+        <v>6767</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9">
+        <v>4954</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>7407</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="9">
+        <v>4828</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1116</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1648</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1372</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4899</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="9">
+        <v>5817</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="9">
+        <v>9182</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="9">
+        <v>3205</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="9">
+        <v>3347</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2">
+        <v>8392</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="2">
+        <v>6515</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="9">
+        <v>2768</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>2621</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="9">
+        <v>4677</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="9">
+        <v>6523</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>8868</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="9">
+        <v>2645</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="9">
+        <v>9237</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="9">
+        <v>5806</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="9">
+        <v>7401</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2">
+        <v>8322</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="2">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="9">
+        <v>7069</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="9">
+        <v>8746</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="9">
+        <v>6217</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="9">
+        <v>2021</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="2">
+        <v>4444</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="2">
+        <v>5086</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="9">
+        <v>4397</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="9">
+        <v>8477</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="9">
+        <v>2471</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="9">
+        <v>3640</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1583</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="2">
+        <v>9640</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="9">
+        <v>3408</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="9">
+        <v>8418</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="9">
+        <v>4859</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="9">
+        <v>8252</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1568</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L28" s="2">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="9">
+        <v>2785</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="9">
+        <v>5778</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="9">
+        <v>2928</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="9">
+        <v>1581</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="2">
+        <v>6986</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="2">
+        <v>8181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="10">
+        <v>3647</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="10">
+        <v>8677</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="10">
+        <v>5463</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="10">
+        <v>1035</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="4">
+        <v>7412</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="4">
+        <v>7759</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="33" spans="1:12">
+      <c r="A33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="8"/>
+      <c r="G33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="8"/>
+      <c r="I33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="1">
         <v>2749</v>
       </c>
-      <c r="H18" s="1">
+      <c r="C34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1">
         <v>2064</v>
       </c>
-      <c r="I18" s="1">
+      <c r="E34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
         <v>1993</v>
       </c>
-      <c r="J18" s="1">
+      <c r="G34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" s="1">
         <v>9652</v>
       </c>
-      <c r="K18" s="1">
+      <c r="I34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
         <v>4487</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>2529</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8698</v>
-      </c>
-      <c r="C19" s="1">
-        <v>6312</v>
-      </c>
-      <c r="D19" s="1">
-        <v>7268</v>
-      </c>
-      <c r="E19" s="1">
-        <v>4498</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3787</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="K34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="1">
         <v>9086</v>
       </c>
-      <c r="H19" s="1">
+      <c r="C35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1">
         <v>4298</v>
       </c>
-      <c r="I19" s="1">
+      <c r="E35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1">
         <v>4593</v>
       </c>
-      <c r="J19" s="1">
+      <c r="G35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
         <v>7622</v>
       </c>
-      <c r="K19" s="1">
+      <c r="I35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J35" s="1">
         <v>6906</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>6665</v>
-      </c>
-      <c r="B20" s="1">
-        <v>9623</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1429</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2068</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4994</v>
-      </c>
-      <c r="F20" s="1">
-        <v>9119</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="K35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="1">
         <v>4179</v>
       </c>
-      <c r="H20" s="1">
+      <c r="C36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1">
         <v>2357</v>
       </c>
-      <c r="I20" s="1">
+      <c r="E36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
         <v>5085</v>
       </c>
-      <c r="J20" s="1">
+      <c r="G36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
         <v>9171</v>
       </c>
-      <c r="K20" s="1">
+      <c r="I36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J36" s="1">
         <v>2906</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>7345</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3583</v>
-      </c>
-      <c r="C21" s="1">
-        <v>6767</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4954</v>
-      </c>
-      <c r="E21" s="1">
-        <v>7407</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1997</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="K36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1">
         <v>1837</v>
       </c>
-      <c r="H21" s="1">
+      <c r="C37" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
         <v>7799</v>
       </c>
-      <c r="I21" s="1">
+      <c r="E37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1">
         <v>7688</v>
       </c>
-      <c r="J21" s="1">
+      <c r="G37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1">
         <v>9446</v>
       </c>
-      <c r="K21" s="1">
+      <c r="I37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J37" s="1">
         <v>7012</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>4828</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1116</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1648</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1372</v>
-      </c>
-      <c r="E22" s="1">
-        <v>4899</v>
-      </c>
-      <c r="F22" s="1">
-        <v>3739</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="K37" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="1">
         <v>5328</v>
       </c>
-      <c r="H22" s="1">
+      <c r="C38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1">
         <v>7324</v>
       </c>
-      <c r="I22" s="1">
+      <c r="E38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="1">
         <v>4387</v>
       </c>
-      <c r="J22" s="1">
+      <c r="G38" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" s="1">
         <v>2949</v>
       </c>
-      <c r="K22" s="1">
+      <c r="I38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
         <v>3761</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>5817</v>
-      </c>
-      <c r="B23" s="1">
-        <v>9182</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3205</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3347</v>
-      </c>
-      <c r="E23" s="1">
-        <v>8392</v>
-      </c>
-      <c r="F23" s="1">
-        <v>6515</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="K38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1">
         <v>9455</v>
       </c>
-      <c r="H23" s="1">
+      <c r="C39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1">
         <v>9992</v>
       </c>
-      <c r="I23" s="1">
+      <c r="E39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="1">
         <v>1908</v>
       </c>
-      <c r="J23" s="1">
+      <c r="G39" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
         <v>3596</v>
       </c>
-      <c r="K23" s="1">
+      <c r="I39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1">
         <v>9096</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>2768</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2621</v>
-      </c>
-      <c r="C24" s="1">
-        <v>4677</v>
-      </c>
-      <c r="D24" s="1">
-        <v>6523</v>
-      </c>
-      <c r="E24" s="1">
-        <v>8868</v>
-      </c>
-      <c r="F24" s="1">
-        <v>3892</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="K39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="1">
         <v>5861</v>
       </c>
-      <c r="H24" s="1">
+      <c r="C40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
         <v>4433</v>
       </c>
-      <c r="I24" s="1">
+      <c r="E40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="1">
         <v>4198</v>
       </c>
-      <c r="J24" s="1">
+      <c r="G40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="1">
         <v>5237</v>
       </c>
-      <c r="K24" s="1">
+      <c r="I40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J40" s="1">
         <v>7636</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>2645</v>
-      </c>
-      <c r="B25" s="1">
-        <v>9237</v>
-      </c>
-      <c r="C25" s="1">
-        <v>5806</v>
-      </c>
-      <c r="D25" s="1">
-        <v>7401</v>
-      </c>
-      <c r="E25" s="1">
-        <v>8322</v>
-      </c>
-      <c r="F25" s="1">
-        <v>4368</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="K40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="1">
         <v>3945</v>
       </c>
-      <c r="H25" s="1">
+      <c r="C41" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
         <v>1033</v>
       </c>
-      <c r="I25" s="1">
+      <c r="E41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="1">
         <v>4150</v>
       </c>
-      <c r="J25" s="1">
+      <c r="G41" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="1">
         <v>7448</v>
       </c>
-      <c r="K25" s="1">
+      <c r="I41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="1">
         <v>2113</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>7069</v>
-      </c>
-      <c r="B26" s="1">
-        <v>8746</v>
-      </c>
-      <c r="C26" s="1">
-        <v>6217</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E26" s="1">
-        <v>4444</v>
-      </c>
-      <c r="F26" s="1">
-        <v>5086</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="K41" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="1">
         <v>9707</v>
       </c>
-      <c r="H26" s="1">
+      <c r="C42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="1">
         <v>4753</v>
       </c>
-      <c r="I26" s="1">
+      <c r="E42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1">
         <v>6970</v>
       </c>
-      <c r="J26" s="1">
+      <c r="G42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="1">
         <v>5888</v>
       </c>
-      <c r="K26" s="1">
+      <c r="I42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="1">
         <v>7052</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>4397</v>
-      </c>
-      <c r="B27" s="1">
-        <v>8477</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2471</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3640</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1583</v>
-      </c>
-      <c r="F27" s="1">
-        <v>9640</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="K42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="1">
         <v>2394</v>
       </c>
-      <c r="H27" s="1">
+      <c r="C43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1">
         <v>8735</v>
       </c>
-      <c r="I27" s="1">
+      <c r="E43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="1">
         <v>5221</v>
       </c>
-      <c r="J27" s="1">
+      <c r="G43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="1">
         <v>2759</v>
       </c>
-      <c r="K27" s="1">
+      <c r="I43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1">
         <v>1435</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>3408</v>
-      </c>
-      <c r="B28" s="1">
-        <v>8418</v>
-      </c>
-      <c r="C28" s="1">
-        <v>4859</v>
-      </c>
-      <c r="D28" s="1">
-        <v>8252</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1568</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2639</v>
-      </c>
-      <c r="G28" s="1">
+      <c r="K43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="1">
         <v>4889</v>
       </c>
-      <c r="H28" s="1">
+      <c r="C44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="1">
         <v>1070</v>
       </c>
-      <c r="I28" s="1">
+      <c r="E44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1">
         <v>4105</v>
       </c>
-      <c r="J28" s="1">
+      <c r="G44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1">
         <v>9745</v>
       </c>
-      <c r="K28" s="1">
+      <c r="I44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="1">
         <v>3551</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>2785</v>
-      </c>
-      <c r="B29" s="1">
-        <v>5778</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2928</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1581</v>
-      </c>
-      <c r="E29" s="1">
-        <v>6986</v>
-      </c>
-      <c r="F29" s="1">
-        <v>8181</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="K44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="1">
         <v>4590</v>
       </c>
-      <c r="H29" s="1">
+      <c r="C45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1">
         <v>2535</v>
       </c>
-      <c r="I29" s="1">
+      <c r="E45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1">
         <v>8648</v>
       </c>
-      <c r="J29" s="1">
+      <c r="G45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="1">
         <v>3441</v>
       </c>
-      <c r="K29" s="1">
+      <c r="I45" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="1">
         <v>7867</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>3647</v>
-      </c>
-      <c r="B30" s="1">
-        <v>8677</v>
-      </c>
-      <c r="C30" s="1">
-        <v>5463</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1035</v>
-      </c>
-      <c r="E30" s="1">
-        <v>7412</v>
-      </c>
-      <c r="F30" s="1">
-        <v>7759</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="K45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="1">
         <v>5614</v>
       </c>
-      <c r="H30" s="1">
+      <c r="C46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="1">
         <v>1538</v>
       </c>
-      <c r="I30" s="1">
+      <c r="E46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="1">
         <v>1867</v>
       </c>
-      <c r="J30" s="1">
+      <c r="G46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="1">
         <v>8872</v>
       </c>
-      <c r="K30" s="1">
+      <c r="I46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="1">
         <v>9956</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="K46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L46" s="4"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="1">
         <v>3422</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B64" s="1">
         <v>8633</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C64" s="1">
         <v>9091</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D64" s="1">
         <v>8343</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E64" s="1">
         <v>5867</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F64" s="1">
         <v>5763</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G64" s="1">
         <v>7602</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H64" s="1">
         <v>1139</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I64" s="1">
         <v>7595</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J64" s="1">
         <v>9616</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K64" s="1">
         <v>7742</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="65" spans="1:11">
+      <c r="A65" s="1">
         <v>9793</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B65" s="1">
         <v>6660</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C65" s="1">
         <v>5106</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D65" s="1">
         <v>4447</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E65" s="1">
         <v>4189</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F65" s="1">
         <v>2697</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G65" s="1">
         <v>3947</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H65" s="1">
         <v>7818</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I65" s="1">
         <v>9871</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J65" s="1">
         <v>6698</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K65" s="1">
         <v>6575</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="66" spans="1:11">
+      <c r="A66" s="1">
         <v>6713</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B66" s="1">
         <v>2739</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C66" s="1">
         <v>6118</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D66" s="1">
         <v>1889</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E66" s="1">
         <v>8632</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F66" s="1">
         <v>3353</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G66" s="1">
         <v>2729</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H66" s="1">
         <v>5744</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I66" s="1">
         <v>9060</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J66" s="1">
         <v>9538</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K66" s="1">
         <v>2845</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="67" spans="1:11">
+      <c r="A67" s="1">
         <v>1827</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B67" s="1">
         <v>3653</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C67" s="1">
         <v>7916</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D67" s="1">
         <v>2550</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E67" s="1">
         <v>6389</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F67" s="1">
         <v>4425</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G67" s="1">
         <v>3038</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H67" s="1">
         <v>5518</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I67" s="1">
         <v>1739</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J67" s="1">
         <v>7822</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K67" s="1">
         <v>1018</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="68" spans="1:11">
+      <c r="A68" s="1">
         <v>1731</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B68" s="1">
         <v>7367</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C68" s="1">
         <v>5689</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D68" s="1">
         <v>5759</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E68" s="1">
         <v>5276</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F68" s="1">
         <v>6190</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G68" s="1">
         <v>2421</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H68" s="1">
         <v>5060</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I68" s="1">
         <v>8892</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J68" s="1">
         <v>5737</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K68" s="1">
         <v>4477</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="69" spans="1:11">
+      <c r="A69" s="1">
         <v>9635</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B69" s="1">
         <v>8516</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C69" s="1">
         <v>7750</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D69" s="1">
         <v>6393</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E69" s="1">
         <v>6545</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F69" s="1">
         <v>9950</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G69" s="1">
         <v>6116</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H69" s="1">
         <v>8017</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I69" s="1">
         <v>6521</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J69" s="1">
         <v>7486</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K69" s="1">
         <v>8930</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="70" spans="1:11">
+      <c r="A70" s="1">
         <v>7101</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B70" s="1">
         <v>3981</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C70" s="1">
         <v>6088</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D70" s="1">
         <v>6346</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E70" s="1">
         <v>6270</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F70" s="1">
         <v>2212</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G70" s="1">
         <v>7160</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H70" s="1">
         <v>4799</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I70" s="1">
         <v>8022</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J70" s="1">
         <v>9785</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K70" s="1">
         <v>9733</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="71" spans="1:11">
+      <c r="A71" s="1">
         <v>2043</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B71" s="1">
         <v>3336</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C71" s="1">
         <v>1159</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D71" s="1">
         <v>7027</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E71" s="1">
         <v>7871</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F71" s="1">
         <v>6856</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G71" s="1">
         <v>7667</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H71" s="1">
         <v>1814</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="72" spans="1:11">
+      <c r="A72" s="1">
         <v>7753</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B72" s="1">
         <v>1083</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C72" s="1">
         <v>3210</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D72" s="1">
         <v>3758</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E72" s="1">
         <v>4596</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F72" s="1">
         <v>8653</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G72" s="1">
         <v>6138</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H72" s="1">
         <v>5440</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="73" spans="1:11">
+      <c r="A73" s="1">
         <v>5792</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B73" s="1">
         <v>2154</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C73" s="1">
         <v>9048</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D73" s="1">
         <v>2396</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E73" s="1">
         <v>4465</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F73" s="1">
         <v>8979</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G73" s="1">
         <v>2233</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H73" s="1">
         <v>5591</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+    <row r="74" spans="1:11">
+      <c r="A74" s="1">
         <v>8752</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B74" s="1">
         <v>9316</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C74" s="1">
         <v>9868</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="18">
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AC8047-143E-4949-862E-800358CF030B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -14,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -33,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="37">
   <si>
     <t>EQUIPO 1</t>
   </si>
@@ -126,13 +121,31 @@
   </si>
   <si>
     <t>EQUIPO 18</t>
+  </si>
+  <si>
+    <t>EQUIPO 19</t>
+  </si>
+  <si>
+    <t>EQUIPO 20</t>
+  </si>
+  <si>
+    <t>EQUIPO 21</t>
+  </si>
+  <si>
+    <t>EQUIPO 23</t>
+  </si>
+  <si>
+    <t>EQUIPO 24</t>
+  </si>
+  <si>
+    <t>EQUIPO 22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +289,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -283,9 +299,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,50 +627,50 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <dimension ref="A1:L76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.3984375" style="1"/>
+    <col min="1" max="6" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="9"/>
+      <c r="G1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="9"/>
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="7" t="s">
+      <c r="J1" s="9"/>
+      <c r="K1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" ht="15">
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -695,7 +708,7 @@
         <v>9943</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -733,7 +746,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -771,7 +784,7 @@
         <v>6014</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -809,7 +822,7 @@
         <v>8036</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -847,7 +860,7 @@
         <v>6590</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -885,7 +898,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -923,7 +936,7 @@
         <v>9856</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -961,7 +974,7 @@
         <v>5988</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -999,7 +1012,7 @@
         <v>8913</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -1037,7 +1050,7 @@
         <v>6825</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1075,7 +1088,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1126,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1151,56 +1164,56 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.4" thickBot="1"/>
-    <row r="17" spans="1:12">
-      <c r="A17" s="7" t="s">
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="9"/>
+      <c r="E17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="7" t="s">
+      <c r="H17" s="9"/>
+      <c r="I17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="7" t="s">
+      <c r="J17" s="9"/>
+      <c r="K17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="1">
         <v>9842</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="1">
         <v>7609</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="1">
         <v>5914</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="1">
         <v>7625</v>
       </c>
       <c r="I18" s="5" t="s">
@@ -1216,29 +1229,29 @@
         <v>6914</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="1">
         <v>2529</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="1">
         <v>8698</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="1">
         <v>6312</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="1">
         <v>7268</v>
       </c>
       <c r="I19" s="6" t="s">
@@ -1254,29 +1267,29 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="1">
         <v>6665</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="1">
         <v>9623</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="1">
         <v>1429</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="1">
         <v>2068</v>
       </c>
       <c r="I20" s="5" t="s">
@@ -1292,29 +1305,29 @@
         <v>9119</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="1">
         <v>7345</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="1">
         <v>3583</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="1">
         <v>6767</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="1">
         <v>4954</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -1330,29 +1343,29 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="1">
         <v>4828</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="1">
         <v>1116</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="1">
         <v>1648</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="1">
         <v>1372</v>
       </c>
       <c r="I22" s="5" t="s">
@@ -1368,29 +1381,29 @@
         <v>3739</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="1">
         <v>5817</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="1">
         <v>9182</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="1">
         <v>3205</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="1">
         <v>3347</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -1406,29 +1419,29 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="1">
         <v>2768</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="1">
         <v>2621</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="1">
         <v>4677</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="1">
         <v>6523</v>
       </c>
       <c r="I24" s="5" t="s">
@@ -1444,29 +1457,29 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="1">
         <v>2645</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="1">
         <v>9237</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="1">
         <v>5806</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="1">
         <v>7401</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -1482,29 +1495,29 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="1">
         <v>7069</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="1">
         <v>8746</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="1">
         <v>6217</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="1">
         <v>2021</v>
       </c>
       <c r="I26" s="5" t="s">
@@ -1520,29 +1533,29 @@
         <v>5086</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="1">
         <v>4397</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="1">
         <v>8477</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="1">
         <v>2471</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="1">
         <v>3640</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -1558,29 +1571,29 @@
         <v>9640</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="1">
         <v>3408</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="1">
         <v>8418</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="1">
         <v>4859</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="1">
         <v>8252</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -1596,29 +1609,29 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="1">
         <v>2785</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="1">
         <v>5778</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="1">
         <v>2928</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="1">
         <v>1581</v>
       </c>
       <c r="I29" s="5" t="s">
@@ -1634,29 +1647,29 @@
         <v>8181</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="14.4" thickBot="1">
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="7">
         <v>3647</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="7">
         <v>8677</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <v>5463</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>1035</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -1672,840 +1685,1130 @@
         <v>7759</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="14.4" thickBot="1"/>
-    <row r="33" spans="1:12">
-      <c r="A33" s="7" t="s">
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7" t="s">
+      <c r="D33" s="9"/>
+      <c r="E33" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="7" t="s">
+      <c r="F33" s="9"/>
+      <c r="G33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="7" t="s">
+      <c r="H33" s="9"/>
+      <c r="I33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="7" t="s">
+      <c r="J33" s="9"/>
+      <c r="K33" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="10">
         <v>2749</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="10">
         <v>2064</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="10">
         <v>1993</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="10">
         <v>9652</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="10">
         <v>4487</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="L34" s="2">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="10">
         <v>9086</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="10">
         <v>4298</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="10">
         <v>4593</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="10">
         <v>7622</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="10">
         <v>6906</v>
       </c>
       <c r="K35" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="L35" s="2">
+        <v>5737</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="10">
         <v>4179</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="10">
         <v>2357</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="10">
         <v>5085</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="10">
         <v>9171</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="10">
         <v>2906</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="L36" s="2">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="10">
         <v>1837</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="10">
         <v>7799</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="10">
         <v>7688</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="10">
         <v>9446</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="10">
         <v>7012</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="L37" s="2">
+        <v>9616</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="10">
         <v>5328</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="10">
         <v>7324</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="10">
         <v>4387</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="10">
         <v>2949</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="10">
         <v>3761</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="L38" s="2">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="10">
         <v>9455</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="10">
         <v>9992</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="10">
         <v>1908</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="10">
         <v>3596</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="10">
         <v>9096</v>
       </c>
       <c r="K39" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="L39" s="2">
+        <v>9538</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="10">
         <v>5861</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="10">
         <v>4433</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="10">
         <v>4198</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="10">
         <v>5237</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="10">
         <v>7636</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="L40" s="2">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="10">
         <v>3945</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="10">
         <v>1033</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="10">
         <v>4150</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="10">
         <v>7448</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="10">
         <v>2113</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="L41" s="2">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="10">
         <v>9707</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="10">
         <v>4753</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="10">
         <v>6970</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="10">
         <v>5888</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="10">
         <v>7052</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="L42" s="2">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="10">
         <v>2394</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="10">
         <v>8735</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="10">
         <v>5221</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="10">
         <v>2759</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="10">
         <v>1435</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="L43" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="10">
         <v>4889</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="10">
         <v>1070</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="10">
         <v>4105</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44" s="10">
         <v>9745</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="10">
         <v>3551</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="L44" s="2">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="10">
         <v>4590</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="10">
         <v>2535</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="10">
         <v>8648</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45" s="10">
         <v>3441</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="10">
         <v>7867</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12" ht="14.4" thickBot="1">
+      <c r="L45" s="2">
+        <v>8930</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="7">
         <v>5614</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="7">
         <v>1538</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="7">
         <v>1867</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46" s="7">
         <v>8872</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="7">
         <v>9956</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L46" s="4"/>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="1">
+      <c r="L46" s="4">
+        <v>9733</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H49" s="9"/>
+      <c r="I49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="1">
+        <v>9785</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="10">
+        <v>8633</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10">
+        <v>5867</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="10">
+        <v>7602</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J50" s="10">
+        <v>1139</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L50" s="2">
+        <v>9091</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1">
         <v>3422</v>
       </c>
-      <c r="B64" s="1">
-        <v>8633</v>
-      </c>
-      <c r="C64" s="1">
-        <v>9091</v>
-      </c>
-      <c r="D64" s="1">
+      <c r="C51" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="10">
+        <v>6660</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="10">
+        <v>4189</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H51" s="10">
+        <v>5763</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" s="10">
+        <v>3947</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="1">
+        <v>9793</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="10">
+        <v>2739</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="10">
+        <v>8632</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="10">
+        <v>2697</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="10">
+        <v>2729</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L52" s="2">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" s="1">
+        <v>6713</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="10">
+        <v>3653</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="10">
+        <v>6389</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="10">
+        <v>3353</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J53" s="10">
+        <v>3038</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1827</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="10">
+        <v>7367</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10">
+        <v>5276</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="10">
+        <v>4425</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J54" s="10">
+        <v>2421</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="2">
+        <v>5689</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1731</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="10">
+        <v>8516</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="10">
+        <v>6545</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="10">
+        <v>6190</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" s="10">
+        <v>6116</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L55" s="2">
+        <v>7750</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="1">
+        <v>9635</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="10">
+        <v>3981</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="10">
+        <v>6270</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H56" s="10">
+        <v>9950</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J56" s="10">
+        <v>7160</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L56" s="2">
+        <v>6088</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1">
+        <v>7101</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="10">
+        <v>3336</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="10">
+        <v>7871</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="10">
+        <v>2212</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="10">
+        <v>7667</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L57" s="2">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="1">
+        <v>2043</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="10">
+        <v>1083</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="10">
+        <v>6393</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="10">
+        <v>6856</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J58" s="10">
+        <v>6138</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L58" s="2">
         <v>8343</v>
       </c>
-      <c r="E64" s="1">
-        <v>5867</v>
-      </c>
-      <c r="F64" s="1">
-        <v>5763</v>
-      </c>
-      <c r="G64" s="1">
-        <v>7602</v>
-      </c>
-      <c r="H64" s="1">
-        <v>1139</v>
-      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="1">
+        <v>7753</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="10">
+        <v>2154</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="10">
+        <v>6346</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="10">
+        <v>8653</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" s="10">
+        <v>2233</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L59" s="2">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="1">
+        <v>5792</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="10">
+        <v>3210</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="10">
+        <v>7027</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="10">
+        <v>8979</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J60" s="10">
+        <v>7818</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60" s="2">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" s="1">
+        <v>8752</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="10">
+        <v>9048</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="10">
+        <v>3758</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="10">
+        <v>4596</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="10">
+        <v>5744</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L61" s="2">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="1">
+        <v>9316</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="7">
+        <v>9868</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="7">
+        <v>2396</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="7">
+        <v>4465</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="7">
+        <v>5518</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L62" s="4">
+        <v>5759</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I64" s="1">
         <v>7595</v>
       </c>
-      <c r="J64" s="1">
-        <v>9616</v>
-      </c>
-      <c r="K64" s="1">
-        <v>7742</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="1">
-        <v>9793</v>
-      </c>
-      <c r="B65" s="1">
-        <v>6660</v>
-      </c>
-      <c r="C65" s="1">
-        <v>5106</v>
-      </c>
-      <c r="D65" s="1">
-        <v>4447</v>
-      </c>
-      <c r="E65" s="1">
-        <v>4189</v>
-      </c>
-      <c r="F65" s="1">
-        <v>2697</v>
-      </c>
-      <c r="G65" s="1">
-        <v>3947</v>
-      </c>
-      <c r="H65" s="1">
-        <v>7818</v>
-      </c>
+    </row>
+    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I65" s="1">
         <v>9871</v>
       </c>
-      <c r="J65" s="1">
-        <v>6698</v>
-      </c>
-      <c r="K65" s="1">
-        <v>6575</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" s="1">
-        <v>6713</v>
-      </c>
-      <c r="B66" s="1">
-        <v>2739</v>
-      </c>
-      <c r="C66" s="1">
-        <v>6118</v>
-      </c>
-      <c r="D66" s="1">
-        <v>1889</v>
-      </c>
-      <c r="E66" s="1">
-        <v>8632</v>
-      </c>
-      <c r="F66" s="1">
-        <v>3353</v>
-      </c>
-      <c r="G66" s="1">
-        <v>2729</v>
-      </c>
-      <c r="H66" s="1">
-        <v>5744</v>
-      </c>
+    </row>
+    <row r="66" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I66" s="1">
         <v>9060</v>
       </c>
-      <c r="J66" s="1">
-        <v>9538</v>
-      </c>
-      <c r="K66" s="1">
-        <v>2845</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="A67" s="1">
-        <v>1827</v>
-      </c>
-      <c r="B67" s="1">
-        <v>3653</v>
-      </c>
-      <c r="C67" s="1">
-        <v>7916</v>
-      </c>
-      <c r="D67" s="1">
-        <v>2550</v>
-      </c>
-      <c r="E67" s="1">
-        <v>6389</v>
-      </c>
-      <c r="F67" s="1">
-        <v>4425</v>
-      </c>
-      <c r="G67" s="1">
-        <v>3038</v>
-      </c>
-      <c r="H67" s="1">
-        <v>5518</v>
-      </c>
+    </row>
+    <row r="67" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I67" s="1">
         <v>1739</v>
       </c>
-      <c r="J67" s="1">
-        <v>7822</v>
-      </c>
-      <c r="K67" s="1">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" s="1">
-        <v>1731</v>
-      </c>
-      <c r="B68" s="1">
-        <v>7367</v>
-      </c>
-      <c r="C68" s="1">
-        <v>5689</v>
-      </c>
-      <c r="D68" s="1">
-        <v>5759</v>
-      </c>
-      <c r="E68" s="1">
-        <v>5276</v>
-      </c>
-      <c r="F68" s="1">
-        <v>6190</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2421</v>
-      </c>
-      <c r="H68" s="1">
-        <v>5060</v>
-      </c>
+    </row>
+    <row r="68" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I68" s="1">
         <v>8892</v>
       </c>
-      <c r="J68" s="1">
-        <v>5737</v>
-      </c>
-      <c r="K68" s="1">
-        <v>4477</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" s="1">
-        <v>9635</v>
-      </c>
-      <c r="B69" s="1">
-        <v>8516</v>
-      </c>
-      <c r="C69" s="1">
-        <v>7750</v>
-      </c>
-      <c r="D69" s="1">
-        <v>6393</v>
-      </c>
-      <c r="E69" s="1">
-        <v>6545</v>
-      </c>
-      <c r="F69" s="1">
-        <v>9950</v>
-      </c>
-      <c r="G69" s="1">
-        <v>6116</v>
-      </c>
-      <c r="H69" s="1">
-        <v>8017</v>
-      </c>
+    </row>
+    <row r="69" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I69" s="1">
         <v>6521</v>
       </c>
-      <c r="J69" s="1">
-        <v>7486</v>
-      </c>
-      <c r="K69" s="1">
-        <v>8930</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" s="1">
-        <v>7101</v>
-      </c>
-      <c r="B70" s="1">
-        <v>3981</v>
-      </c>
-      <c r="C70" s="1">
-        <v>6088</v>
-      </c>
-      <c r="D70" s="1">
-        <v>6346</v>
-      </c>
-      <c r="E70" s="1">
-        <v>6270</v>
-      </c>
-      <c r="F70" s="1">
-        <v>2212</v>
-      </c>
-      <c r="G70" s="1">
-        <v>7160</v>
-      </c>
-      <c r="H70" s="1">
-        <v>4799</v>
-      </c>
+    </row>
+    <row r="70" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I70" s="1">
         <v>8022</v>
       </c>
-      <c r="J70" s="1">
-        <v>9785</v>
-      </c>
-      <c r="K70" s="1">
-        <v>9733</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" s="1">
-        <v>2043</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3336</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1159</v>
-      </c>
-      <c r="D71" s="1">
-        <v>7027</v>
-      </c>
-      <c r="E71" s="1">
-        <v>7871</v>
-      </c>
-      <c r="F71" s="1">
-        <v>6856</v>
-      </c>
-      <c r="G71" s="1">
-        <v>7667</v>
-      </c>
-      <c r="H71" s="1">
+    </row>
+    <row r="71" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I71" s="1">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="72" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I72" s="1">
+        <v>8017</v>
+      </c>
+    </row>
+    <row r="73" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I73" s="1">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="74" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I74" s="1">
         <v>1814</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="1">
-        <v>7753</v>
-      </c>
-      <c r="B72" s="1">
-        <v>1083</v>
-      </c>
-      <c r="C72" s="1">
-        <v>3210</v>
-      </c>
-      <c r="D72" s="1">
-        <v>3758</v>
-      </c>
-      <c r="E72" s="1">
-        <v>4596</v>
-      </c>
-      <c r="F72" s="1">
-        <v>8653</v>
-      </c>
-      <c r="G72" s="1">
-        <v>6138</v>
-      </c>
-      <c r="H72" s="1">
+    <row r="75" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I75" s="1">
         <v>5440</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="1">
-        <v>5792</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2154</v>
-      </c>
-      <c r="C73" s="1">
-        <v>9048</v>
-      </c>
-      <c r="D73" s="1">
-        <v>2396</v>
-      </c>
-      <c r="E73" s="1">
-        <v>4465</v>
-      </c>
-      <c r="F73" s="1">
-        <v>8979</v>
-      </c>
-      <c r="G73" s="1">
-        <v>2233</v>
-      </c>
-      <c r="H73" s="1">
+    <row r="76" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I76" s="1">
         <v>5591</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
-      <c r="A74" s="1">
-        <v>8752</v>
-      </c>
-      <c r="B74" s="1">
-        <v>9316</v>
-      </c>
-      <c r="C74" s="1">
-        <v>9868</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -2518,12 +2821,6 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AC8047-143E-4949-862E-800358CF030B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFE6CCB-6B95-4C3D-BCC3-88E587160E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,9 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="37">
   <si>
-    <t>EQUIPO 1</t>
-  </si>
-  <si>
     <t>QR1</t>
   </si>
   <si>
@@ -72,33 +69,6 @@
     <t>FINAL</t>
   </si>
   <si>
-    <t>EQUIPO 2</t>
-  </si>
-  <si>
-    <t>EQUIPO 3</t>
-  </si>
-  <si>
-    <t>EQUIPO 4</t>
-  </si>
-  <si>
-    <t>EQUIPO 5</t>
-  </si>
-  <si>
-    <t>EQUIPO 6</t>
-  </si>
-  <si>
-    <t>EQUIPO 7</t>
-  </si>
-  <si>
-    <t>EQUIPO 8</t>
-  </si>
-  <si>
-    <t>EQUIPO 9</t>
-  </si>
-  <si>
-    <t>EQUIPO 10</t>
-  </si>
-  <si>
     <t>EQUIPO 11</t>
   </si>
   <si>
@@ -139,6 +109,36 @@
   </si>
   <si>
     <t>EQUIPO 22</t>
+  </si>
+  <si>
+    <t>El Trío Dinámico</t>
+  </si>
+  <si>
+    <t>Irene, María, Sofía y Adriana</t>
+  </si>
+  <si>
+    <t>Los John Deere</t>
+  </si>
+  <si>
+    <t>Palencia 1</t>
+  </si>
+  <si>
+    <t>Palencia 2</t>
+  </si>
+  <si>
+    <t>Yo que sé</t>
+  </si>
+  <si>
+    <t>Desmadradas</t>
+  </si>
+  <si>
+    <t>2 y 1</t>
+  </si>
+  <si>
+    <t>Palencia 3</t>
+  </si>
+  <si>
+    <t>Santi y María</t>
   </si>
 </sst>
 </file>
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -296,9 +296,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,68 +638,69 @@
   <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" style="1"/>
+    <col min="1" max="6" width="13.85546875" style="1" customWidth="1"/>
+    <col min="7" max="12" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="8" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="8" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
         <v>5377</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
         <v>3218</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
         <v>6531</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2">
         <v>4504</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
         <v>3016</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2">
         <v>9943</v>
@@ -710,37 +708,37 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>8008</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2">
         <v>1058</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
         <v>8216</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>7612</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
         <v>5551</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2">
         <v>6109</v>
@@ -748,37 +746,37 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>8613</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2">
         <v>4089</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>7792</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2">
         <v>1439</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2">
         <v>8688</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2">
         <v>6014</v>
@@ -786,37 +784,37 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2">
         <v>1764</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>8058</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>6066</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
         <v>3560</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2">
         <v>9390</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>8036</v>
@@ -824,37 +822,37 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2">
         <v>7120</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2">
         <v>2226</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
         <v>9330</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2">
         <v>1020</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2">
         <v>1324</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2">
         <v>6590</v>
@@ -862,37 +860,37 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>5895</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2">
         <v>8706</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
         <v>6301</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2">
         <v>8684</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2">
         <v>7067</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2">
         <v>2077</v>
@@ -900,37 +898,37 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>8962</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2">
         <v>4675</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
         <v>2537</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2">
         <v>1996</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2">
         <v>9836</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L8" s="2">
         <v>9856</v>
@@ -938,37 +936,37 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>7928</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2">
         <v>5063</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
         <v>5296</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2">
         <v>5402</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2">
         <v>1330</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="2">
         <v>5988</v>
@@ -976,37 +974,37 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
         <v>8131</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2">
         <v>2844</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2">
         <v>9632</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2">
         <v>8597</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2">
         <v>6409</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2">
         <v>8913</v>
@@ -1014,37 +1012,37 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>4659</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2">
         <v>1248</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2">
         <v>6394</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2">
         <v>6164</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2">
         <v>4904</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L11" s="2">
         <v>6825</v>
@@ -1052,37 +1050,37 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>2386</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2">
         <v>9634</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="2">
         <v>9756</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2">
         <v>6263</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" s="2">
         <v>4182</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L12" s="2">
         <v>2058</v>
@@ -1090,37 +1088,37 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>9201</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2">
         <v>8118</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2">
         <v>5934</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2">
         <v>5259</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J13" s="2">
         <v>9947</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2">
         <v>4523</v>
@@ -1128,37 +1126,37 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4">
         <v>8835</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="4">
         <v>2597</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="4">
         <v>7686</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="4">
         <v>3140</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4">
         <v>5043</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L14" s="4">
         <v>1434</v>
@@ -1167,63 +1165,63 @@
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" s="1">
         <v>9842</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1">
         <v>7609</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
         <v>5914</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
         <v>7625</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
         <v>3552</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2">
         <v>6914</v>
@@ -1231,37 +1229,37 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1">
         <v>2529</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1">
         <v>8698</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
         <v>6312</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="1">
         <v>7268</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" s="2">
         <v>4498</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2">
         <v>3787</v>
@@ -1269,37 +1267,37 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" s="1">
         <v>6665</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>9623</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1">
         <v>1429</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="1">
         <v>2068</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2">
         <v>4994</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2">
         <v>9119</v>
@@ -1307,37 +1305,37 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1">
         <v>7345</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1">
         <v>3583</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1">
         <v>6767</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
         <v>4954</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2">
         <v>7407</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2">
         <v>1997</v>
@@ -1345,37 +1343,37 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1">
         <v>4828</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1">
         <v>1116</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1">
         <v>1648</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="1">
         <v>1372</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="2">
         <v>4899</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L22" s="2">
         <v>3739</v>
@@ -1383,37 +1381,37 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="1">
         <v>5817</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1">
         <v>9182</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1">
         <v>3205</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="1">
         <v>3347</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2">
         <v>8392</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23" s="2">
         <v>6515</v>
@@ -1421,37 +1419,37 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="1">
         <v>2768</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="1">
         <v>2621</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1">
         <v>4677</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="1">
         <v>6523</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="2">
         <v>8868</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24" s="2">
         <v>3892</v>
@@ -1459,37 +1457,37 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="1">
         <v>2645</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1">
         <v>9237</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1">
         <v>5806</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
         <v>7401</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25" s="2">
         <v>8322</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L25" s="2">
         <v>4368</v>
@@ -1497,37 +1495,37 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1">
         <v>7069</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1">
         <v>8746</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1">
         <v>6217</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H26" s="1">
         <v>2021</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" s="2">
         <v>4444</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L26" s="2">
         <v>5086</v>
@@ -1535,37 +1533,37 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" s="1">
         <v>4397</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1">
         <v>8477</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" s="1">
         <v>2471</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" s="1">
         <v>3640</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" s="2">
         <v>1583</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L27" s="2">
         <v>9640</v>
@@ -1573,37 +1571,37 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1">
         <v>3408</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1">
         <v>8418</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1">
         <v>4859</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H28" s="1">
         <v>8252</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="2">
         <v>1568</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L28" s="2">
         <v>2639</v>
@@ -1611,37 +1609,37 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="1">
         <v>2785</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" s="1">
         <v>5778</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1">
         <v>2928</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1">
         <v>1581</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" s="2">
         <v>6986</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L29" s="2">
         <v>8181</v>
@@ -1649,37 +1647,37 @@
     </row>
     <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="7">
         <v>3647</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" s="7">
         <v>8677</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" s="7">
         <v>5463</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="7">
         <v>1035</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4">
         <v>7412</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L30" s="4">
         <v>7759</v>
@@ -1691,63 +1689,63 @@
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L33" s="9"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2749</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="10">
-        <v>2749</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="1">
+        <v>2064</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="10">
-        <v>2064</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="1">
+        <v>1993</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F34" s="10">
-        <v>1993</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H34" s="10">
+      <c r="H34" s="1">
         <v>9652</v>
       </c>
       <c r="I34" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4487</v>
+      </c>
+      <c r="K34" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="J34" s="10">
-        <v>4487</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>2</v>
       </c>
       <c r="L34" s="2">
         <v>7822</v>
@@ -1755,37 +1753,37 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1">
+        <v>9086</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="10">
-        <v>9086</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="1">
+        <v>4298</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="10">
-        <v>4298</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="10">
+      <c r="F35" s="1">
         <v>4593</v>
       </c>
       <c r="G35" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>7622</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H35" s="10">
-        <v>7622</v>
-      </c>
-      <c r="I35" s="5" t="s">
+      <c r="J35" s="1">
+        <v>6906</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="J35" s="10">
-        <v>6906</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>3</v>
       </c>
       <c r="L35" s="2">
         <v>5737</v>
@@ -1793,37 +1791,37 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4179</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="10">
-        <v>4179</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="10">
+      <c r="D36" s="1">
         <v>2357</v>
       </c>
       <c r="E36" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5085</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F36" s="10">
-        <v>5085</v>
-      </c>
-      <c r="G36" s="5" t="s">
+      <c r="H36" s="1">
+        <v>9171</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="10">
-        <v>9171</v>
-      </c>
-      <c r="I36" s="5" t="s">
+      <c r="J36" s="1">
+        <v>2906</v>
+      </c>
+      <c r="K36" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="J36" s="10">
-        <v>2906</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="L36" s="2">
         <v>7486</v>
@@ -1831,37 +1829,37 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="10">
+        <v>3</v>
+      </c>
+      <c r="B37" s="1">
         <v>1837</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7799</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="10">
-        <v>7799</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="1">
+        <v>7688</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="10">
-        <v>7688</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="1">
+        <v>9446</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H37" s="10">
-        <v>9446</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J37" s="10">
+      <c r="J37" s="1">
         <v>7012</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2">
         <v>9616</v>
@@ -1869,37 +1867,37 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1">
+        <v>5328</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="10">
-        <v>5328</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="1">
+        <v>7324</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="10">
-        <v>7324</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="1">
+        <v>4387</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="10">
-        <v>4387</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H38" s="10">
+      <c r="H38" s="1">
         <v>2949</v>
       </c>
       <c r="I38" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="1">
+        <v>3761</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="J38" s="10">
-        <v>3761</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="L38" s="2">
         <v>6698</v>
@@ -1907,37 +1905,37 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1">
+        <v>9455</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="10">
-        <v>9455</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="1">
+        <v>9992</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="10">
-        <v>9992</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="10">
+      <c r="F39" s="1">
         <v>1908</v>
       </c>
       <c r="G39" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3596</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H39" s="10">
-        <v>3596</v>
-      </c>
-      <c r="I39" s="5" t="s">
+      <c r="J39" s="1">
+        <v>9096</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="J39" s="10">
-        <v>9096</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="L39" s="2">
         <v>9538</v>
@@ -1945,37 +1943,37 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1">
+        <v>5861</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="10">
-        <v>5861</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="10">
+      <c r="D40" s="1">
         <v>4433</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1">
+        <v>4198</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="10">
-        <v>4198</v>
-      </c>
-      <c r="G40" s="5" t="s">
+      <c r="H40" s="1">
+        <v>5237</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="10">
-        <v>5237</v>
-      </c>
-      <c r="I40" s="5" t="s">
+      <c r="J40" s="1">
+        <v>7636</v>
+      </c>
+      <c r="K40" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="J40" s="10">
-        <v>7636</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="L40" s="2">
         <v>7742</v>
@@ -1983,37 +1981,37 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="10">
+        <v>7</v>
+      </c>
+      <c r="B41" s="1">
         <v>3945</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1033</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="10">
-        <v>1033</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="1">
+        <v>4150</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="10">
-        <v>4150</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="H41" s="1">
+        <v>7448</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="10">
-        <v>7448</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="10">
+      <c r="J41" s="1">
         <v>2113</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2">
         <v>6575</v>
@@ -2021,37 +2019,37 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="1">
+        <v>9707</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="10">
-        <v>9707</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="1">
+        <v>4753</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="10">
-        <v>4753</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="1">
+        <v>6970</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="10">
-        <v>6970</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="H42" s="1">
         <v>5888</v>
       </c>
       <c r="I42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="1">
+        <v>7052</v>
+      </c>
+      <c r="K42" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="J42" s="10">
-        <v>7052</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="L42" s="2">
         <v>2845</v>
@@ -2059,37 +2057,37 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2394</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="10">
-        <v>2394</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="1">
+        <v>8735</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="10">
-        <v>8735</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="10">
+      <c r="F43" s="1">
         <v>5221</v>
       </c>
       <c r="G43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2759</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H43" s="10">
-        <v>2759</v>
-      </c>
-      <c r="I43" s="5" t="s">
+      <c r="J43" s="1">
+        <v>1435</v>
+      </c>
+      <c r="K43" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="J43" s="10">
-        <v>1435</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="L43" s="2">
         <v>1018</v>
@@ -2097,37 +2095,37 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4889</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="10">
-        <v>4889</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="10">
+      <c r="D44" s="1">
         <v>1070</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4105</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="10">
-        <v>4105</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="H44" s="1">
+        <v>9745</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="10">
-        <v>9745</v>
-      </c>
-      <c r="I44" s="5" t="s">
+      <c r="J44" s="1">
+        <v>3551</v>
+      </c>
+      <c r="K44" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="J44" s="10">
-        <v>3551</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="L44" s="2">
         <v>4477</v>
@@ -2135,37 +2133,37 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="10">
+        <v>11</v>
+      </c>
+      <c r="B45" s="1">
         <v>4590</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2535</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="10">
-        <v>2535</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="1">
+        <v>8648</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="10">
-        <v>8648</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="H45" s="1">
+        <v>3441</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="10">
-        <v>3441</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J45" s="10">
+      <c r="J45" s="1">
         <v>7867</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L45" s="2">
         <v>8930</v>
@@ -2173,37 +2171,37 @@
     </row>
     <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" s="7">
         <v>5614</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" s="7">
         <v>1538</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F46" s="7">
         <v>1867</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="7">
         <v>8872</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J46" s="7">
         <v>9956</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L46" s="4">
         <v>9733</v>
@@ -2212,63 +2210,63 @@
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L49" s="9"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" s="1">
         <v>9785</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="10">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1">
         <v>8633</v>
       </c>
       <c r="E50" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5867</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="10">
-        <v>5867</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="H50" s="1">
+        <v>7602</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H50" s="10">
-        <v>7602</v>
-      </c>
-      <c r="I50" s="5" t="s">
+      <c r="J50" s="1">
+        <v>1139</v>
+      </c>
+      <c r="K50" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="J50" s="10">
-        <v>1139</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="L50" s="2">
         <v>9091</v>
@@ -2276,37 +2274,37 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51" s="1">
         <v>3422</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6660</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D51" s="10">
-        <v>6660</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="1">
+        <v>4189</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F51" s="10">
-        <v>4189</v>
-      </c>
-      <c r="G51" s="5" t="s">
+      <c r="H51" s="1">
+        <v>5763</v>
+      </c>
+      <c r="I51" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H51" s="10">
-        <v>5763</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J51" s="10">
+      <c r="J51" s="1">
         <v>3947</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2">
         <v>5106</v>
@@ -2314,37 +2312,37 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" s="1">
         <v>9793</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2739</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="10">
-        <v>2739</v>
-      </c>
-      <c r="E52" s="5" t="s">
+      <c r="F52" s="1">
+        <v>8632</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="10">
-        <v>8632</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="10">
+      <c r="H52" s="1">
         <v>2697</v>
       </c>
       <c r="I52" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2729</v>
+      </c>
+      <c r="K52" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="J52" s="10">
-        <v>2729</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>2</v>
       </c>
       <c r="L52" s="2">
         <v>6118</v>
@@ -2352,37 +2350,37 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" s="1">
         <v>6713</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3653</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="10">
-        <v>3653</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53" s="10">
+      <c r="F53" s="1">
         <v>6389</v>
       </c>
       <c r="G53" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3353</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H53" s="10">
-        <v>3353</v>
-      </c>
-      <c r="I53" s="5" t="s">
+      <c r="J53" s="1">
+        <v>3038</v>
+      </c>
+      <c r="K53" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="J53" s="10">
-        <v>3038</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>3</v>
       </c>
       <c r="L53" s="2">
         <v>7916</v>
@@ -2390,37 +2388,37 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B54" s="1">
         <v>1827</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="10">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1">
         <v>7367</v>
       </c>
       <c r="E54" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5276</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="10">
-        <v>5276</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="H54" s="1">
+        <v>4425</v>
+      </c>
+      <c r="I54" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H54" s="10">
-        <v>4425</v>
-      </c>
-      <c r="I54" s="5" t="s">
+      <c r="J54" s="1">
+        <v>2421</v>
+      </c>
+      <c r="K54" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="J54" s="10">
-        <v>2421</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="L54" s="2">
         <v>5689</v>
@@ -2428,37 +2426,37 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" s="1">
         <v>1731</v>
       </c>
       <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1">
+        <v>8516</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="10">
-        <v>8516</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="1">
+        <v>6545</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="10">
-        <v>6545</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="H55" s="1">
+        <v>6190</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H55" s="10">
-        <v>6190</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J55" s="10">
+      <c r="J55" s="1">
         <v>6116</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L55" s="2">
         <v>7750</v>
@@ -2466,37 +2464,37 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="1">
         <v>9635</v>
       </c>
       <c r="C56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3981</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="10">
-        <v>3981</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="1">
+        <v>6270</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="10">
-        <v>6270</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H56" s="10">
+      <c r="H56" s="1">
         <v>9950</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J56" s="1">
+        <v>7160</v>
+      </c>
+      <c r="K56" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="J56" s="10">
-        <v>7160</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="L56" s="2">
         <v>6088</v>
@@ -2504,37 +2502,37 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1">
         <v>7101</v>
       </c>
       <c r="C57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3336</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="10">
-        <v>3336</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="10">
+      <c r="F57" s="1">
         <v>7871</v>
       </c>
       <c r="G57" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2212</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H57" s="10">
-        <v>2212</v>
-      </c>
-      <c r="I57" s="5" t="s">
+      <c r="J57" s="1">
+        <v>7667</v>
+      </c>
+      <c r="K57" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="J57" s="10">
-        <v>7667</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="L57" s="2">
         <v>1159</v>
@@ -2542,37 +2540,37 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="1">
         <v>2043</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="10">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1">
         <v>1083</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="1">
+        <v>6393</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="10">
-        <v>6393</v>
-      </c>
-      <c r="G58" s="5" t="s">
+      <c r="H58" s="1">
+        <v>6856</v>
+      </c>
+      <c r="I58" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H58" s="10">
-        <v>6856</v>
-      </c>
-      <c r="I58" s="5" t="s">
+      <c r="J58" s="1">
+        <v>6138</v>
+      </c>
+      <c r="K58" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="J58" s="10">
-        <v>6138</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="L58" s="2">
         <v>8343</v>
@@ -2580,37 +2578,37 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1">
         <v>7753</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2154</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="10">
-        <v>2154</v>
-      </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="1">
+        <v>6346</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="10">
-        <v>6346</v>
-      </c>
-      <c r="G59" s="5" t="s">
+      <c r="H59" s="1">
+        <v>8653</v>
+      </c>
+      <c r="I59" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="10">
-        <v>8653</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J59" s="10">
+      <c r="J59" s="1">
         <v>2233</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L59" s="2">
         <v>4447</v>
@@ -2618,37 +2616,37 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="1">
         <v>5792</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3210</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="10">
-        <v>3210</v>
-      </c>
-      <c r="E60" s="5" t="s">
+      <c r="F60" s="1">
+        <v>7027</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="10">
-        <v>7027</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H60" s="10">
+      <c r="H60" s="1">
         <v>8979</v>
       </c>
       <c r="I60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="1">
+        <v>7818</v>
+      </c>
+      <c r="K60" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="J60" s="10">
-        <v>7818</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="L60" s="2">
         <v>1889</v>
@@ -2656,37 +2654,37 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" s="1">
         <v>8752</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9048</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="10">
-        <v>9048</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="10">
+      <c r="F61" s="1">
         <v>3758</v>
       </c>
       <c r="G61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H61" s="1">
+        <v>4596</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="10">
-        <v>4596</v>
-      </c>
-      <c r="I61" s="5" t="s">
+      <c r="J61" s="1">
+        <v>5744</v>
+      </c>
+      <c r="K61" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="J61" s="10">
-        <v>5744</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="L61" s="2">
         <v>2550</v>
@@ -2694,37 +2692,37 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" s="1">
         <v>9316</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D62" s="7">
         <v>9868</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F62" s="7">
         <v>2396</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H62" s="7">
         <v>4465</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J62" s="7">
         <v>5518</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L62" s="4">
         <v>5759</v>
@@ -2797,18 +2795,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -2821,6 +2807,18 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFE6CCB-6B95-4C3D-BCC3-88E587160E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B953ECE8-8889-4C23-A669-9624E109F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,12 +120,6 @@
     <t>Los John Deere</t>
   </si>
   <si>
-    <t>Palencia 1</t>
-  </si>
-  <si>
-    <t>Palencia 2</t>
-  </si>
-  <si>
     <t>Yo que sé</t>
   </si>
   <si>
@@ -135,10 +129,16 @@
     <t>2 y 1</t>
   </si>
   <si>
-    <t>Palencia 3</t>
-  </si>
-  <si>
     <t>Santi y María</t>
+  </si>
+  <si>
+    <t>Los raposos de Abarca</t>
+  </si>
+  <si>
+    <t>Los locos escapistas</t>
+  </si>
+  <si>
+    <t>Gacelas y perezosas</t>
   </si>
 </sst>
 </file>
@@ -656,15 +656,15 @@
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L1" s="9"/>
     </row>
@@ -1165,19 +1165,19 @@
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="8" t="s">
@@ -2795,6 +2795,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -2807,18 +2819,6 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B953ECE8-8889-4C23-A669-9624E109F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20625ECC-E39B-477F-9896-70C4645B3386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>FINAL</t>
   </si>
   <si>
-    <t>EQUIPO 11</t>
-  </si>
-  <si>
     <t>EQUIPO 12</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>Gacelas y perezosas</t>
+  </si>
+  <si>
+    <t>Palencia 4</t>
   </si>
 </sst>
 </file>
@@ -195,32 +195,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -265,6 +239,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -274,28 +274,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -642,29 +642,29 @@
     <col min="7" max="12" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L1" s="9"/>
     </row>
@@ -1163,29 +1163,29 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="8" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L17" s="9"/>
     </row>
@@ -1687,29 +1687,29 @@
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L33" s="9"/>
     </row>
@@ -2208,29 +2208,29 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L49" s="9"/>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="A50" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="2">
         <v>9785</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -2276,7 +2276,7 @@
       <c r="A51" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="2">
         <v>3422</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -2314,7 +2314,7 @@
       <c r="A52" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="2">
         <v>9793</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -2352,7 +2352,7 @@
       <c r="A53" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="2">
         <v>6713</v>
       </c>
       <c r="C53" s="5" t="s">
@@ -2390,7 +2390,7 @@
       <c r="A54" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="2">
         <v>1827</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -2428,7 +2428,7 @@
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <v>1731</v>
       </c>
       <c r="C55" s="5" t="s">
@@ -2466,7 +2466,7 @@
       <c r="A56" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>9635</v>
       </c>
       <c r="C56" s="5" t="s">
@@ -2504,7 +2504,7 @@
       <c r="A57" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="2">
         <v>7101</v>
       </c>
       <c r="C57" s="5" t="s">
@@ -2542,7 +2542,7 @@
       <c r="A58" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="2">
         <v>2043</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -2580,7 +2580,7 @@
       <c r="A59" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="2">
         <v>7753</v>
       </c>
       <c r="C59" s="5" t="s">
@@ -2618,7 +2618,7 @@
       <c r="A60" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <v>5792</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -2656,7 +2656,7 @@
       <c r="A61" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="2">
         <v>8752</v>
       </c>
       <c r="C61" s="5" t="s">
@@ -2694,7 +2694,7 @@
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="4">
         <v>9316</v>
       </c>
       <c r="C62" s="3" t="s">

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20625ECC-E39B-477F-9896-70C4645B3386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D54FF6-8225-4554-899D-B5190E2DC296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2729,84 +2729,46 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I64" s="1">
-        <v>7595</v>
-      </c>
+      <c r="I64" s="1"/>
     </row>
     <row r="65" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I65" s="1">
-        <v>9871</v>
-      </c>
+      <c r="I65" s="1"/>
     </row>
     <row r="66" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I66" s="1">
-        <v>9060</v>
-      </c>
+      <c r="I66" s="1"/>
     </row>
     <row r="67" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I67" s="1">
-        <v>1739</v>
-      </c>
+      <c r="I67" s="1"/>
     </row>
     <row r="68" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I68" s="1">
-        <v>8892</v>
-      </c>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I69" s="1">
-        <v>6521</v>
-      </c>
+      <c r="I69" s="1"/>
     </row>
     <row r="70" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I70" s="1">
-        <v>8022</v>
-      </c>
+      <c r="I70" s="1"/>
     </row>
     <row r="71" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I71" s="1">
-        <v>5060</v>
-      </c>
+      <c r="I71" s="1"/>
     </row>
     <row r="72" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I72" s="1">
-        <v>8017</v>
-      </c>
+      <c r="I72" s="1"/>
     </row>
     <row r="73" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I73" s="1">
-        <v>4799</v>
-      </c>
+      <c r="I73" s="1"/>
     </row>
     <row r="74" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I74" s="1">
-        <v>1814</v>
-      </c>
+      <c r="I74" s="1"/>
     </row>
     <row r="75" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I75" s="1">
-        <v>5440</v>
-      </c>
+      <c r="I75" s="1"/>
     </row>
     <row r="76" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I76" s="1">
-        <v>5591</v>
-      </c>
+      <c r="I76" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -2819,8 +2781,20 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D54FF6-8225-4554-899D-B5190E2DC296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8681F849-6159-4A01-BE46-2026837F1C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="EQUIPOS" sheetId="1" r:id="rId1"/>
+    <sheet name="TARJETAS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="67">
   <si>
     <t>QR1</t>
   </si>
@@ -139,13 +140,103 @@
   </si>
   <si>
     <t>Palencia 4</t>
+  </si>
+  <si>
+    <t>COD.</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>COORDENADA</t>
+  </si>
+  <si>
+    <t>CENTRO SOCIAL</t>
+  </si>
+  <si>
+    <t>El trio Dinámico</t>
+  </si>
+  <si>
+    <t>Los Locos escapistas</t>
+  </si>
+  <si>
+    <t>Palencia4</t>
+  </si>
+  <si>
+    <t>PADEL</t>
+  </si>
+  <si>
+    <t>ABUELA JUDITH</t>
+  </si>
+  <si>
+    <t>W24</t>
+  </si>
+  <si>
+    <t>CODIGO ACCESO</t>
+  </si>
+  <si>
+    <t>TRASERA BEA</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>SIGUIENTE COORDENADA</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>SIGUIENTE CODIGO</t>
+  </si>
+  <si>
+    <t>ELOY</t>
+  </si>
+  <si>
+    <t>IGLESIA</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>AMBULANCIA</t>
+  </si>
+  <si>
+    <t>CEMENTERIO</t>
+  </si>
+  <si>
+    <t>BASCULA</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>BUSCAVIEJA</t>
+  </si>
+  <si>
+    <t>Z25</t>
+  </si>
+  <si>
+    <t>LOCO ATADO</t>
+  </si>
+  <si>
+    <t>W20</t>
+  </si>
+  <si>
+    <t>X17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +246,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -182,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -265,11 +365,230 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -297,6 +616,72 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2769,6 +3154,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -2781,20 +3178,620 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4BBB09-74B0-4539-8514-9CCF22A3FBFD}">
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1764</v>
+      </c>
+      <c r="G3" s="24">
+        <v>4089</v>
+      </c>
+      <c r="H3" s="24">
+        <v>8216</v>
+      </c>
+      <c r="I3" s="24">
+        <v>4504</v>
+      </c>
+      <c r="J3" s="24">
+        <v>9390</v>
+      </c>
+      <c r="K3" s="24">
+        <v>6014</v>
+      </c>
+      <c r="L3" s="24">
+        <v>2529</v>
+      </c>
+      <c r="M3" s="24">
+        <v>7609</v>
+      </c>
+      <c r="N3" s="24">
+        <v>6767</v>
+      </c>
+      <c r="O3" s="24">
+        <v>2068</v>
+      </c>
+      <c r="P3" s="24">
+        <v>4498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="29">
+        <v>7120</v>
+      </c>
+      <c r="G5" s="29">
+        <v>8058</v>
+      </c>
+      <c r="H5" s="29">
+        <v>7792</v>
+      </c>
+      <c r="I5" s="29">
+        <v>7612</v>
+      </c>
+      <c r="J5" s="29">
+        <v>1324</v>
+      </c>
+      <c r="K5" s="29">
+        <v>8036</v>
+      </c>
+      <c r="L5" s="29">
+        <v>6665</v>
+      </c>
+      <c r="M5" s="29">
+        <v>8698</v>
+      </c>
+      <c r="N5" s="29">
+        <v>1648</v>
+      </c>
+      <c r="O5" s="29">
+        <v>4954</v>
+      </c>
+      <c r="P5" s="29">
+        <v>4994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="E10" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="24">
+        <v>7928</v>
+      </c>
+      <c r="G10" s="24">
+        <v>4675</v>
+      </c>
+      <c r="H10" s="24">
+        <v>6301</v>
+      </c>
+      <c r="I10" s="24">
+        <v>1020</v>
+      </c>
+      <c r="J10" s="24">
+        <v>1330</v>
+      </c>
+      <c r="K10" s="24">
+        <v>9856</v>
+      </c>
+      <c r="L10" s="24">
+        <v>5817</v>
+      </c>
+      <c r="M10" s="24">
+        <v>1116</v>
+      </c>
+      <c r="N10" s="24">
+        <v>5806</v>
+      </c>
+      <c r="O10" s="24">
+        <v>6523</v>
+      </c>
+      <c r="P10" s="24">
+        <v>8392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="29">
+        <v>8131</v>
+      </c>
+      <c r="G12" s="29">
+        <v>5063</v>
+      </c>
+      <c r="H12" s="29">
+        <v>2537</v>
+      </c>
+      <c r="I12" s="29">
+        <v>8684</v>
+      </c>
+      <c r="J12" s="29">
+        <v>6409</v>
+      </c>
+      <c r="K12" s="29">
+        <v>5988</v>
+      </c>
+      <c r="L12" s="29">
+        <v>2768</v>
+      </c>
+      <c r="M12" s="29">
+        <v>9182</v>
+      </c>
+      <c r="N12" s="29">
+        <v>6217</v>
+      </c>
+      <c r="O12" s="29">
+        <v>7401</v>
+      </c>
+      <c r="P12" s="29">
+        <v>8868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+    </row>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="24">
+        <v>9201</v>
+      </c>
+      <c r="G17" s="24">
+        <v>9634</v>
+      </c>
+      <c r="H17" s="24">
+        <v>6394</v>
+      </c>
+      <c r="I17" s="24">
+        <v>8597</v>
+      </c>
+      <c r="J17" s="24">
+        <v>9947</v>
+      </c>
+      <c r="K17" s="24">
+        <v>2058</v>
+      </c>
+      <c r="L17" s="24">
+        <v>4397</v>
+      </c>
+      <c r="M17" s="24">
+        <v>8746</v>
+      </c>
+      <c r="N17" s="24">
+        <v>2928</v>
+      </c>
+      <c r="O17" s="24">
+        <v>8252</v>
+      </c>
+      <c r="P17" s="24">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="18" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E18" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+    </row>
+    <row r="19" spans="5:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="29">
+        <v>8835</v>
+      </c>
+      <c r="G19" s="29">
+        <v>8118</v>
+      </c>
+      <c r="H19" s="29">
+        <v>9756</v>
+      </c>
+      <c r="I19" s="29">
+        <v>6164</v>
+      </c>
+      <c r="J19" s="29">
+        <v>5043</v>
+      </c>
+      <c r="K19" s="29">
+        <v>4523</v>
+      </c>
+      <c r="L19" s="29">
+        <v>3408</v>
+      </c>
+      <c r="M19" s="29">
+        <v>8477</v>
+      </c>
+      <c r="N19" s="29">
+        <v>5463</v>
+      </c>
+      <c r="O19" s="29">
+        <v>1581</v>
+      </c>
+      <c r="P19" s="29">
+        <v>1568</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8681F849-6159-4A01-BE46-2026837F1C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8476E3ED-A30F-4DB2-BE6A-56561A788344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="67">
   <si>
     <t>QR1</t>
   </si>
@@ -70,9 +70,6 @@
     <t>FINAL</t>
   </si>
   <si>
-    <t>EQUIPO 12</t>
-  </si>
-  <si>
     <t>EQUIPO 13</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>X17</t>
+  </si>
+  <si>
+    <t>Los Rondilleros</t>
   </si>
 </sst>
 </file>
@@ -611,12 +611,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,12 +620,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -640,12 +628,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -682,6 +664,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,30 +1028,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="33"/>
+      <c r="K1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="9"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -1549,30 +1549,30 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="33"/>
+      <c r="E17" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="33"/>
+      <c r="G17" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="8" t="s">
+      <c r="H17" s="33"/>
+      <c r="I17" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17" s="9"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -2073,30 +2073,30 @@
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="33"/>
+      <c r="E33" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="8" t="s">
+      <c r="F33" s="33"/>
+      <c r="G33" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="8" t="s">
+      <c r="H33" s="33"/>
+      <c r="I33" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="8" t="s">
+      <c r="J33" s="33"/>
+      <c r="K33" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" s="9"/>
+      <c r="L33" s="33"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
@@ -2594,30 +2594,30 @@
     </row>
     <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="33"/>
+      <c r="C49" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="8" t="s">
+      <c r="D49" s="33"/>
+      <c r="E49" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="8" t="s">
+      <c r="F49" s="33"/>
+      <c r="G49" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="33"/>
+      <c r="I49" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="8" t="s">
+      <c r="J49" s="33"/>
+      <c r="K49" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="J49" s="9"/>
-      <c r="K49" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49" s="9"/>
+      <c r="L49" s="33"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
@@ -3154,18 +3154,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -3178,6 +3166,18 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -3186,580 +3186,635 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4BBB09-74B0-4539-8514-9CCF22A3FBFD}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="14.140625" customWidth="1"/>
+    <col min="6" max="17" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="E1" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="K1" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="18">
+        <v>1764</v>
+      </c>
+      <c r="G3" s="18">
+        <v>4089</v>
+      </c>
+      <c r="H3" s="18">
+        <v>8216</v>
+      </c>
+      <c r="I3" s="18">
+        <v>4504</v>
+      </c>
+      <c r="J3" s="18">
+        <v>9390</v>
+      </c>
+      <c r="K3" s="18">
+        <v>6014</v>
+      </c>
+      <c r="L3" s="18">
+        <v>2529</v>
+      </c>
+      <c r="M3" s="18">
+        <v>7609</v>
+      </c>
+      <c r="N3" s="18">
+        <v>6767</v>
+      </c>
+      <c r="O3" s="18">
+        <v>2068</v>
+      </c>
+      <c r="P3" s="18">
+        <v>4498</v>
+      </c>
+      <c r="Q3" s="18">
+        <v>6914</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="23">
+        <v>7120</v>
+      </c>
+      <c r="G5" s="23">
+        <v>8058</v>
+      </c>
+      <c r="H5" s="23">
+        <v>7792</v>
+      </c>
+      <c r="I5" s="23">
+        <v>7612</v>
+      </c>
+      <c r="J5" s="23">
+        <v>1324</v>
+      </c>
+      <c r="K5" s="23">
+        <v>8036</v>
+      </c>
+      <c r="L5" s="23">
+        <v>6665</v>
+      </c>
+      <c r="M5" s="23">
+        <v>8698</v>
+      </c>
+      <c r="N5" s="23">
+        <v>1648</v>
+      </c>
+      <c r="O5" s="23">
+        <v>4954</v>
+      </c>
+      <c r="P5" s="23">
+        <v>4994</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I8" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="14" t="s">
+      <c r="L8" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="Q8" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="E10" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="18">
+        <v>7928</v>
+      </c>
+      <c r="G10" s="18">
+        <v>4675</v>
+      </c>
+      <c r="H10" s="18">
+        <v>6301</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1020</v>
+      </c>
+      <c r="J10" s="18">
+        <v>1330</v>
+      </c>
+      <c r="K10" s="18">
+        <v>9856</v>
+      </c>
+      <c r="L10" s="18">
+        <v>5817</v>
+      </c>
+      <c r="M10" s="18">
+        <v>1116</v>
+      </c>
+      <c r="N10" s="18">
+        <v>5806</v>
+      </c>
+      <c r="O10" s="18">
+        <v>6523</v>
+      </c>
+      <c r="P10" s="18">
+        <v>8392</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="23">
+        <v>8131</v>
+      </c>
+      <c r="G12" s="23">
+        <v>5063</v>
+      </c>
+      <c r="H12" s="23">
+        <v>2537</v>
+      </c>
+      <c r="I12" s="23">
+        <v>8684</v>
+      </c>
+      <c r="J12" s="23">
+        <v>6409</v>
+      </c>
+      <c r="K12" s="23">
+        <v>5988</v>
+      </c>
+      <c r="L12" s="23">
+        <v>2768</v>
+      </c>
+      <c r="M12" s="23">
+        <v>9182</v>
+      </c>
+      <c r="N12" s="23">
+        <v>6217</v>
+      </c>
+      <c r="O12" s="23">
+        <v>7401</v>
+      </c>
+      <c r="P12" s="23">
+        <v>8868</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>66515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E15" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M15" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N15" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="22" t="s">
+      <c r="P15" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="31"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+    </row>
+    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E17" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="24">
-        <v>1764</v>
-      </c>
-      <c r="G3" s="24">
-        <v>4089</v>
-      </c>
-      <c r="H3" s="24">
-        <v>8216</v>
-      </c>
-      <c r="I3" s="24">
-        <v>4504</v>
-      </c>
-      <c r="J3" s="24">
-        <v>9390</v>
-      </c>
-      <c r="K3" s="24">
-        <v>6014</v>
-      </c>
-      <c r="L3" s="24">
-        <v>2529</v>
-      </c>
-      <c r="M3" s="24">
-        <v>7609</v>
-      </c>
-      <c r="N3" s="24">
-        <v>6767</v>
-      </c>
-      <c r="O3" s="24">
-        <v>2068</v>
-      </c>
-      <c r="P3" s="24">
-        <v>4498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="22" t="s">
+      <c r="F17" s="18">
+        <v>9201</v>
+      </c>
+      <c r="G17" s="18">
+        <v>9634</v>
+      </c>
+      <c r="H17" s="18">
+        <v>6394</v>
+      </c>
+      <c r="I17" s="18">
+        <v>8597</v>
+      </c>
+      <c r="J17" s="18">
+        <v>9947</v>
+      </c>
+      <c r="K17" s="18">
+        <v>2058</v>
+      </c>
+      <c r="L17" s="18">
+        <v>4397</v>
+      </c>
+      <c r="M17" s="18">
+        <v>8746</v>
+      </c>
+      <c r="N17" s="18">
+        <v>2928</v>
+      </c>
+      <c r="O17" s="18">
+        <v>8252</v>
+      </c>
+      <c r="P17" s="18">
+        <v>1583</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>5086</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="22" t="s">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+    </row>
+    <row r="19" spans="5:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="29">
-        <v>7120</v>
-      </c>
-      <c r="G5" s="29">
-        <v>8058</v>
-      </c>
-      <c r="H5" s="29">
-        <v>7792</v>
-      </c>
-      <c r="I5" s="29">
-        <v>7612</v>
-      </c>
-      <c r="J5" s="29">
-        <v>1324</v>
-      </c>
-      <c r="K5" s="29">
-        <v>8036</v>
-      </c>
-      <c r="L5" s="29">
-        <v>6665</v>
-      </c>
-      <c r="M5" s="29">
-        <v>8698</v>
-      </c>
-      <c r="N5" s="29">
-        <v>1648</v>
-      </c>
-      <c r="O5" s="29">
-        <v>4954</v>
-      </c>
-      <c r="P5" s="29">
-        <v>4994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="22"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="E10" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="24">
-        <v>7928</v>
-      </c>
-      <c r="G10" s="24">
-        <v>4675</v>
-      </c>
-      <c r="H10" s="24">
-        <v>6301</v>
-      </c>
-      <c r="I10" s="24">
-        <v>1020</v>
-      </c>
-      <c r="J10" s="24">
-        <v>1330</v>
-      </c>
-      <c r="K10" s="24">
-        <v>9856</v>
-      </c>
-      <c r="L10" s="24">
-        <v>5817</v>
-      </c>
-      <c r="M10" s="24">
-        <v>1116</v>
-      </c>
-      <c r="N10" s="24">
-        <v>5806</v>
-      </c>
-      <c r="O10" s="24">
-        <v>6523</v>
-      </c>
-      <c r="P10" s="24">
-        <v>8392</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="29">
-        <v>8131</v>
-      </c>
-      <c r="G12" s="29">
-        <v>5063</v>
-      </c>
-      <c r="H12" s="29">
-        <v>2537</v>
-      </c>
-      <c r="I12" s="29">
-        <v>8684</v>
-      </c>
-      <c r="J12" s="29">
-        <v>6409</v>
-      </c>
-      <c r="K12" s="29">
-        <v>5988</v>
-      </c>
-      <c r="L12" s="29">
-        <v>2768</v>
-      </c>
-      <c r="M12" s="29">
-        <v>9182</v>
-      </c>
-      <c r="N12" s="29">
-        <v>6217</v>
-      </c>
-      <c r="O12" s="29">
-        <v>7401</v>
-      </c>
-      <c r="P12" s="29">
-        <v>8868</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E15" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="18"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-    </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E17" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="24">
-        <v>9201</v>
-      </c>
-      <c r="G17" s="24">
-        <v>9634</v>
-      </c>
-      <c r="H17" s="24">
-        <v>6394</v>
-      </c>
-      <c r="I17" s="24">
-        <v>8597</v>
-      </c>
-      <c r="J17" s="24">
-        <v>9947</v>
-      </c>
-      <c r="K17" s="24">
-        <v>2058</v>
-      </c>
-      <c r="L17" s="24">
-        <v>4397</v>
-      </c>
-      <c r="M17" s="24">
-        <v>8746</v>
-      </c>
-      <c r="N17" s="24">
-        <v>2928</v>
-      </c>
-      <c r="O17" s="24">
-        <v>8252</v>
-      </c>
-      <c r="P17" s="24">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="18" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E18" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-    </row>
-    <row r="19" spans="5:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="29">
+      <c r="F19" s="23">
         <v>8835</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="23">
         <v>8118</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="23">
         <v>9756</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="23">
         <v>6164</v>
       </c>
-      <c r="J19" s="29">
+      <c r="J19" s="23">
         <v>5043</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="23">
         <v>4523</v>
       </c>
-      <c r="L19" s="29">
+      <c r="L19" s="23">
         <v>3408</v>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="23">
         <v>8477</v>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="23">
         <v>5463</v>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="23">
         <v>1581</v>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="23">
         <v>1568</v>
       </c>
+      <c r="Q19" s="23">
+        <v>9640</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
+  <mergeCells count="39">
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="F15:F16"/>
@@ -3767,30 +3822,11 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8476E3ED-A30F-4DB2-BE6A-56561A788344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="EQUIPOS" sheetId="1" r:id="rId1"/>
-    <sheet name="TARJETAS" sheetId="2" r:id="rId2"/>
+    <sheet name="EQUIPOS (2)" sheetId="6" r:id="rId2"/>
+    <sheet name="TARJETAS" sheetId="2" r:id="rId3"/>
+    <sheet name="CENTRO SOCIAL" sheetId="5" r:id="rId4"/>
+    <sheet name="AMBULANCIA" sheetId="4" r:id="rId5"/>
+    <sheet name="LOCO ATADO" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="90">
   <si>
     <t>QR1</t>
   </si>
@@ -70,9 +68,6 @@
     <t>FINAL</t>
   </si>
   <si>
-    <t>EQUIPO 13</t>
-  </si>
-  <si>
     <t>EQUIPO 14</t>
   </si>
   <si>
@@ -175,9 +170,6 @@
     <t>TRASERA BEA</t>
   </si>
   <si>
-    <t>D15</t>
-  </si>
-  <si>
     <t>SIGUIENTE COORDENADA</t>
   </si>
   <si>
@@ -199,24 +191,12 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>R13</t>
-  </si>
-  <si>
     <t>AMBULANCIA</t>
   </si>
   <si>
     <t>CEMENTERIO</t>
   </si>
   <si>
-    <t>BASCULA</t>
-  </si>
-  <si>
-    <t>N17</t>
-  </si>
-  <si>
-    <t>BUSCAVIEJA</t>
-  </si>
-  <si>
     <t>Z25</t>
   </si>
   <si>
@@ -230,13 +210,100 @@
   </si>
   <si>
     <t>Los Rondilleros</t>
+  </si>
+  <si>
+    <t>Q31</t>
+  </si>
+  <si>
+    <t>Los psicópatas anónimos</t>
+  </si>
+  <si>
+    <t>CODIGO ANTERIOR</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>W34</t>
+  </si>
+  <si>
+    <t>ALMACEN</t>
+  </si>
+  <si>
+    <t>N18</t>
+  </si>
+  <si>
+    <t>TRASERA SANTI</t>
+  </si>
+  <si>
+    <t>COMPRESOR</t>
+  </si>
+  <si>
+    <t>PLAZA OLIVO</t>
+  </si>
+  <si>
+    <t>Padel</t>
+  </si>
+  <si>
+    <t>Abuela Judith</t>
+  </si>
+  <si>
+    <t>Trasera Bea</t>
+  </si>
+  <si>
+    <t>Centro Social</t>
+  </si>
+  <si>
+    <t>Eloy</t>
+  </si>
+  <si>
+    <t>Iglesia</t>
+  </si>
+  <si>
+    <t>Castillo</t>
+  </si>
+  <si>
+    <t>Ambulancia</t>
+  </si>
+  <si>
+    <t>Cementerio</t>
+  </si>
+  <si>
+    <t>Almacen</t>
+  </si>
+  <si>
+    <t>Trasera Santi</t>
+  </si>
+  <si>
+    <t>Compresor</t>
+  </si>
+  <si>
+    <t>Plaza Olivo</t>
+  </si>
+  <si>
+    <t>MAPA 2</t>
+  </si>
+  <si>
+    <t>MAPA 1</t>
+  </si>
+  <si>
+    <t>MAPA 3</t>
+  </si>
+  <si>
+    <t>MAPA 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,7 +349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -408,6 +475,36 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -426,7 +523,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -441,7 +538,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -456,7 +553,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -468,13 +565,69 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -486,10 +639,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -498,13 +651,13 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -513,13 +666,50 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -528,58 +718,11 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -588,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -620,67 +763,127 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,51 +1212,51 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="6" width="13.85546875" style="1" customWidth="1"/>
-    <col min="7" max="12" width="13.85546875" customWidth="1"/>
+    <col min="1" max="6" width="13.8984375" style="1" customWidth="1"/>
+    <col min="7" max="12" width="13.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="23"/>
+      <c r="E1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="32" t="s">
+      <c r="F1" s="23"/>
+      <c r="G1" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="23"/>
+      <c r="I1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="23"/>
+      <c r="K1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="33"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1294,7 @@
         <v>9943</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1129,7 +1332,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1167,7 +1370,7 @@
         <v>6014</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1205,7 +1408,7 @@
         <v>8036</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1243,7 +1446,7 @@
         <v>6590</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1281,7 +1484,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1319,7 +1522,7 @@
         <v>9856</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1357,7 +1560,7 @@
         <v>5988</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1598,7 @@
         <v>8913</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15">
       <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
@@ -1433,7 +1636,7 @@
         <v>6825</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -1471,7 +1674,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15">
       <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
@@ -1509,7 +1712,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1547,34 +1750,34 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+    <row r="16" spans="1:12" ht="15.75" thickBot="1"/>
+    <row r="17" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="32" t="s">
+      <c r="D17" s="23"/>
+      <c r="E17" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32" t="s">
+      <c r="H17" s="23"/>
+      <c r="I17" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="33"/>
-      <c r="G17" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="33"/>
-      <c r="I17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="33"/>
-      <c r="K17" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="33"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" s="23"/>
+      <c r="K17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:12" ht="15">
       <c r="A18" s="5" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1815,7 @@
         <v>6914</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15">
       <c r="A19" s="6" t="s">
         <v>3</v>
       </c>
@@ -1650,7 +1853,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15">
       <c r="A20" s="5" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1891,7 @@
         <v>9119</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -1726,7 +1929,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
@@ -1764,7 +1967,7 @@
         <v>3739</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
@@ -1802,7 +2005,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15">
       <c r="A24" s="5" t="s">
         <v>4</v>
       </c>
@@ -1840,7 +2043,7 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15">
       <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +2081,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1916,7 +2119,7 @@
         <v>5086</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15">
       <c r="A27" s="6" t="s">
         <v>11</v>
       </c>
@@ -1954,7 +2157,7 @@
         <v>9640</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15">
       <c r="A28" s="5" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +2195,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15">
       <c r="A29" s="5" t="s">
         <v>9</v>
       </c>
@@ -2030,7 +2233,7 @@
         <v>8181</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15.75" thickBot="1">
       <c r="A30" s="3" t="s">
         <v>12</v>
       </c>
@@ -2068,37 +2271,37 @@
         <v>7759</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15">
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="32" t="s">
+    <row r="32" spans="1:12" ht="15.75" thickBot="1"/>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A33" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="D33" s="23"/>
+      <c r="E33" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32" t="s">
+      <c r="F33" s="23"/>
+      <c r="G33" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="32" t="s">
+      <c r="H33" s="23"/>
+      <c r="I33" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="33"/>
-      <c r="I33" s="32" t="s">
+      <c r="J33" s="23"/>
+      <c r="K33" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="33"/>
-      <c r="K33" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="33"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L33" s="23"/>
+    </row>
+    <row r="34" spans="1:12" ht="15">
       <c r="A34" s="5" t="s">
         <v>0</v>
       </c>
@@ -2136,7 +2339,7 @@
         <v>7822</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15">
       <c r="A35" s="5" t="s">
         <v>1</v>
       </c>
@@ -2174,7 +2377,7 @@
         <v>5737</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15">
       <c r="A36" s="5" t="s">
         <v>2</v>
       </c>
@@ -2212,7 +2415,7 @@
         <v>7486</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15">
       <c r="A37" s="6" t="s">
         <v>3</v>
       </c>
@@ -2250,7 +2453,7 @@
         <v>9616</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="15">
       <c r="A38" s="5" t="s">
         <v>4</v>
       </c>
@@ -2288,7 +2491,7 @@
         <v>6698</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
@@ -2326,7 +2529,7 @@
         <v>9538</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15">
       <c r="A40" s="5" t="s">
         <v>6</v>
       </c>
@@ -2364,7 +2567,7 @@
         <v>7742</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15">
       <c r="A41" s="6" t="s">
         <v>7</v>
       </c>
@@ -2402,7 +2605,7 @@
         <v>6575</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15">
       <c r="A42" s="5" t="s">
         <v>8</v>
       </c>
@@ -2440,7 +2643,7 @@
         <v>2845</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12">
       <c r="A43" s="5" t="s">
         <v>9</v>
       </c>
@@ -2478,7 +2681,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12">
       <c r="A44" s="5" t="s">
         <v>10</v>
       </c>
@@ -2516,7 +2719,7 @@
         <v>4477</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12">
       <c r="A45" s="6" t="s">
         <v>11</v>
       </c>
@@ -2554,7 +2757,7 @@
         <v>8930</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="14.4" thickBot="1">
       <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2592,34 +2795,34 @@
         <v>9733</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="32" t="s">
+    <row r="48" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="49" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A49" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="33"/>
-      <c r="C49" s="32" t="s">
+      <c r="D49" s="23"/>
+      <c r="E49" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="33"/>
-      <c r="E49" s="32" t="s">
+      <c r="F49" s="23"/>
+      <c r="G49" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="23"/>
+      <c r="I49" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="F49" s="33"/>
-      <c r="G49" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="33"/>
-      <c r="I49" s="32" t="s">
+      <c r="J49" s="23"/>
+      <c r="K49" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="J49" s="33"/>
-      <c r="K49" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="33"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L49" s="23"/>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="5" t="s">
         <v>2</v>
       </c>
@@ -2657,7 +2860,7 @@
         <v>9091</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12">
       <c r="A51" s="6" t="s">
         <v>3</v>
       </c>
@@ -2695,7 +2898,7 @@
         <v>5106</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12">
       <c r="A52" s="5" t="s">
         <v>0</v>
       </c>
@@ -2733,7 +2936,7 @@
         <v>6118</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>1</v>
       </c>
@@ -2771,7 +2974,7 @@
         <v>7916</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12">
       <c r="A54" s="5" t="s">
         <v>6</v>
       </c>
@@ -2809,7 +3012,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12">
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
@@ -2847,7 +3050,7 @@
         <v>7750</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12">
       <c r="A56" s="5" t="s">
         <v>4</v>
       </c>
@@ -2885,7 +3088,7 @@
         <v>6088</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12">
       <c r="A57" s="5" t="s">
         <v>5</v>
       </c>
@@ -2923,7 +3126,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12">
       <c r="A58" s="5" t="s">
         <v>10</v>
       </c>
@@ -2961,7 +3164,7 @@
         <v>8343</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12">
       <c r="A59" s="6" t="s">
         <v>11</v>
       </c>
@@ -2999,7 +3202,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12">
       <c r="A60" s="5" t="s">
         <v>8</v>
       </c>
@@ -3037,7 +3240,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12">
       <c r="A61" s="5" t="s">
         <v>9</v>
       </c>
@@ -3075,7 +3278,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="14.4" thickBot="1">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3113,47 +3316,59 @@
         <v>5759</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12">
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="9:9">
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="9:9">
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="9:9">
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="9:9">
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="9:9">
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="9:9">
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="9:9">
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="9:9">
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="9:9">
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="9:9">
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="9:9">
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="9:9">
       <c r="I76" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
@@ -3166,18 +3381,6 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -3185,648 +3388,3149 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4BBB09-74B0-4539-8514-9CCF22A3FBFD}">
-  <dimension ref="A1:Q19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="14.140625" customWidth="1"/>
+    <col min="1" max="6" width="13.8984375" style="1" customWidth="1"/>
+    <col min="7" max="12" width="13.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="23"/>
+      <c r="G1" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="23"/>
+      <c r="I1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="23"/>
+      <c r="K1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5377</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3218</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="2">
+        <v>6531</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4504</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="2">
+        <v>3016</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="2">
+        <v>9943</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="2">
+        <v>8008</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1058</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8216</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7612</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5551</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="2">
+        <v>6109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="2">
+        <v>8613</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4089</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7792</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1439</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="2">
+        <v>8688</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="2">
+        <v>6014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1764</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8058</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6066</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3560</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="2">
+        <v>9390</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="2">
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="2">
+        <v>7120</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2226</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9330</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1020</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1324</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="2">
+        <v>6590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5895</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8706</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6301</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8684</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="2">
+        <v>7067</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2">
+        <v>8962</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4675</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2537</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1996</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="2">
+        <v>9836</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="2">
+        <v>9856</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7928</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5063</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5296</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5402</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1330</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="2">
+        <v>8131</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2844</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9632</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8597</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6409</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="2">
+        <v>8913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4659</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1248</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6394</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="2">
+        <v>6164</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4904</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="2">
+        <v>6825</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2386</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9634</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9756</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6263</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4182</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="2">
+        <v>9201</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8118</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="2">
+        <v>5934</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5259</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="2">
+        <v>9947</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="2">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4">
+        <v>8835</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2597</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="4">
+        <v>7686</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="4">
+        <v>3140</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="4">
+        <v>5043</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="17" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="23"/>
+      <c r="E17" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="K17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1">
+        <v>9842</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7609</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5914</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="1">
+        <v>7625</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3552</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L18" s="2">
+        <v>6914</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2529</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="1">
+        <v>8698</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6312</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="1">
+        <v>7268</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4498</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="2">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6665</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1">
+        <v>9623</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1429</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2068</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="2">
+        <v>4994</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" s="2">
+        <v>9119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1">
+        <v>7345</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3583</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="1">
+        <v>6767</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4954</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="2">
+        <v>7407</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="1">
+        <v>4828</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1116</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1648</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1372</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4899</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L22" s="2">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5817</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9182</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3205</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="1">
+        <v>3347</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="2">
+        <v>8392</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" s="2">
+        <v>6515</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2768</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2621</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4677</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="1">
+        <v>6523</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24" s="2">
+        <v>8868</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L24" s="2">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2645</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9237</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5806</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="1">
+        <v>7401</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="2">
+        <v>8322</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L25" s="2">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="1">
+        <v>7069</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="1">
+        <v>8746</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="1">
+        <v>6217</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="2">
+        <v>4444</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L26" s="2">
+        <v>5086</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4397</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="1">
+        <v>8477</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2471</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3640</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1583</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L27" s="2">
+        <v>9640</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3408</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8418</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4859</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="1">
+        <v>8252</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1568</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" s="2">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2785</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="1">
+        <v>5778</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2928</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1581</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J29" s="2">
+        <v>6986</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L29" s="2">
+        <v>8181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="7">
+        <v>3647</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="7">
+        <v>8677</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="7">
+        <v>5463</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1035</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J30" s="4">
+        <v>7412</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L30" s="4">
+        <v>7759</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="33" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A33" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="23"/>
+      <c r="I33" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="23"/>
+      <c r="K33" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="23"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2749</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2064</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1993</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="1">
+        <v>9652</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4487</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L34" s="2">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="1">
+        <v>9086</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>4298</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4593</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="1">
+        <v>7622</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="1">
+        <v>6906</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L35" s="2">
+        <v>5737</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4179</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2357</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5085</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="1">
+        <v>9171</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2906</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L36" s="2">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1837</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7799</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="1">
+        <v>7688</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="1">
+        <v>9446</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="1">
+        <v>7012</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L37" s="2">
+        <v>9616</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="1">
+        <v>5328</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="1">
+        <v>7324</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="1">
+        <v>4387</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2949</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="1">
+        <v>3761</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L38" s="2">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1">
+        <v>9455</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9992</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1908</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3596</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="1">
+        <v>9096</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L39" s="2">
+        <v>9538</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="1">
+        <v>5861</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="1">
+        <v>4433</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="1">
+        <v>4198</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5237</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J40" s="1">
+        <v>7636</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L40" s="2">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3945</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1033</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41" s="1">
+        <v>4150</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" s="1">
+        <v>7448</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2113</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L41" s="2">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1">
+        <v>9707</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="1">
+        <v>4753</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="1">
+        <v>6970</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="1">
+        <v>5888</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J42" s="1">
+        <v>7052</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L42" s="2">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2394</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="1">
+        <v>8735</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5221</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2759</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1435</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L43" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4889</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1070</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4105</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H44" s="1">
+        <v>9745</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J44" s="1">
+        <v>3551</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L44" s="2">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4590</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2535</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="1">
+        <v>8648</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="1">
+        <v>3441</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J45" s="1">
+        <v>7867</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L45" s="2">
+        <v>8930</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="7">
+        <v>5614</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1538</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1867</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H46" s="7">
+        <v>8872</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J46" s="7">
+        <v>9956</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L46" s="4">
+        <v>9733</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14.4" thickBot="1"/>
+    <row r="49" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A49" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="23"/>
+      <c r="E49" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="23"/>
+      <c r="G49" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="23"/>
+      <c r="I49" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" s="23"/>
+      <c r="K49" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" s="23"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="2">
+        <v>9785</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="1">
+        <v>8633</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5867</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="1">
+        <v>7602</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1139</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L50" s="2">
+        <v>9091</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3422</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6660</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="1">
+        <v>4189</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H51" s="1">
+        <v>5763</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J51" s="1">
+        <v>3947</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51" s="2">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="2">
+        <v>9793</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2739</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="1">
+        <v>8632</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2697</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2729</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L52" s="2">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="2">
+        <v>6713</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3653</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6389</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3353</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J53" s="1">
+        <v>3038</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L53" s="2">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1827</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="1">
+        <v>7367</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5276</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" s="1">
+        <v>4425</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2421</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L54" s="2">
+        <v>5689</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1731</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="1">
+        <v>8516</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="1">
+        <v>6545</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H55" s="1">
+        <v>6190</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J55" s="1">
+        <v>6116</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L55" s="2">
+        <v>7750</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="2">
+        <v>9635</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3981</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" s="1">
+        <v>6270</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H56" s="1">
+        <v>9950</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J56" s="1">
+        <v>7160</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L56" s="2">
+        <v>6088</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="2">
+        <v>7101</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3336</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F57" s="1">
+        <v>7871</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2212</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J57" s="1">
+        <v>7667</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L57" s="2">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2043</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1083</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" s="1">
+        <v>6393</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="1">
+        <v>6856</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J58" s="1">
+        <v>6138</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L58" s="2">
+        <v>8343</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="2">
+        <v>7753</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2154</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" s="1">
+        <v>6346</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" s="1">
+        <v>8653</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2233</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L59" s="2">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5792</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3210</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7027</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H60" s="1">
+        <v>8979</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60" s="1">
+        <v>7818</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L60" s="2">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="2">
+        <v>8752</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9048</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" s="1">
+        <v>3758</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H61" s="1">
+        <v>4596</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J61" s="1">
+        <v>5744</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L61" s="2">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="4">
+        <v>9316</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D62" s="7">
+        <v>9868</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F62" s="7">
+        <v>2396</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" s="7">
+        <v>4465</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J62" s="7">
+        <v>5518</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L62" s="4">
+        <v>5759</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="9:9">
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="9:9">
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="9:9">
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="9:9">
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="9:9">
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="9:9">
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="9:9">
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="9:9">
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="9:9">
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="9:9">
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="9:9">
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="9:9">
+      <c r="I76" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="15.19921875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="14.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.796875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" s="28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="18">
-        <v>1764</v>
-      </c>
-      <c r="G3" s="18">
-        <v>4089</v>
-      </c>
-      <c r="H3" s="18">
-        <v>8216</v>
-      </c>
-      <c r="I3" s="18">
-        <v>4504</v>
-      </c>
-      <c r="J3" s="18">
-        <v>9390</v>
-      </c>
-      <c r="K3" s="18">
-        <v>6014</v>
-      </c>
-      <c r="L3" s="18">
-        <v>2529</v>
-      </c>
-      <c r="M3" s="18">
-        <v>7609</v>
-      </c>
-      <c r="N3" s="18">
-        <v>6767</v>
-      </c>
-      <c r="O3" s="18">
-        <v>2068</v>
-      </c>
-      <c r="P3" s="18">
-        <v>4498</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>6914</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E3" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="23">
-        <v>7120</v>
-      </c>
-      <c r="G5" s="23">
-        <v>8058</v>
-      </c>
-      <c r="H5" s="23">
-        <v>7792</v>
-      </c>
-      <c r="I5" s="23">
-        <v>7612</v>
-      </c>
-      <c r="J5" s="23">
-        <v>1324</v>
-      </c>
-      <c r="K5" s="23">
-        <v>8036</v>
-      </c>
-      <c r="L5" s="23">
-        <v>6665</v>
-      </c>
-      <c r="M5" s="23">
-        <v>8698</v>
-      </c>
-      <c r="N5" s="23">
-        <v>1648</v>
-      </c>
-      <c r="O5" s="23">
-        <v>4954</v>
-      </c>
-      <c r="P5" s="23">
-        <v>4994</v>
-      </c>
-      <c r="Q5" s="23">
-        <v>3787</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E5" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="13.8" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="28" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="E8" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E9" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="E10" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="18">
-        <v>7928</v>
-      </c>
-      <c r="G10" s="18">
-        <v>4675</v>
-      </c>
-      <c r="H10" s="18">
-        <v>6301</v>
-      </c>
-      <c r="I10" s="18">
-        <v>1020</v>
-      </c>
-      <c r="J10" s="18">
-        <v>1330</v>
-      </c>
-      <c r="K10" s="18">
-        <v>9856</v>
-      </c>
-      <c r="L10" s="18">
-        <v>5817</v>
-      </c>
-      <c r="M10" s="18">
-        <v>1116</v>
-      </c>
-      <c r="N10" s="18">
-        <v>5806</v>
-      </c>
-      <c r="O10" s="18">
-        <v>6523</v>
-      </c>
-      <c r="P10" s="18">
-        <v>8392</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>3739</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-    </row>
-    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.4" thickBot="1">
+      <c r="A14" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="3" max="3" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="32.4" customHeight="1" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A2" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>1764</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="36">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="29">
+        <v>4089</v>
+      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="16">
+        <v>8058</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A4" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="29">
+        <v>8216</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="16">
+        <v>7792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A5" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="29">
+        <v>4504</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="16">
+        <v>7612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="29">
+        <v>9390</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="16">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" s="29">
+        <v>6014</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="16">
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="29">
+        <v>2529</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="16">
+        <v>6665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="29">
+        <v>7609</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="16">
+        <v>8698</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="29">
+        <v>6767</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="16">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A11" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29">
+        <v>2068</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="16">
+        <v>4954</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="29">
+        <v>4498</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="16">
+        <v>4994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="29">
+        <v>6914</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="16">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.4" customHeight="1" thickBot="1">
+      <c r="A14" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="23">
+      <c r="B14" s="35"/>
+      <c r="C14" s="37">
+        <v>1837</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="20">
+        <v>5328</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="3" max="3" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="32.4" customHeight="1" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A2" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>7928</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="36">
         <v>8131</v>
       </c>
-      <c r="G12" s="23">
+    </row>
+    <row r="3" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="29">
+        <v>4675</v>
+      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="16">
         <v>5063</v>
       </c>
-      <c r="H12" s="23">
+    </row>
+    <row r="4" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A4" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="29">
+        <v>6301</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="16">
         <v>2537</v>
       </c>
-      <c r="I12" s="23">
+    </row>
+    <row r="5" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A5" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="29">
+        <v>1020</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="16">
         <v>8684</v>
       </c>
-      <c r="J12" s="23">
+    </row>
+    <row r="6" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="29">
+        <v>1330</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="16">
         <v>6409</v>
       </c>
-      <c r="K12" s="23">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" s="29">
+        <v>9856</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="16">
         <v>5988</v>
       </c>
-      <c r="L12" s="23">
+    </row>
+    <row r="8" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="29">
+        <v>5817</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="16">
         <v>2768</v>
       </c>
-      <c r="M12" s="23">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="29">
+        <v>1116</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="16">
         <v>9182</v>
       </c>
-      <c r="N12" s="23">
+    </row>
+    <row r="10" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="29">
+        <v>5806</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="16">
         <v>6217</v>
       </c>
-      <c r="O12" s="23">
+    </row>
+    <row r="11" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A11" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29">
+        <v>6523</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="16">
         <v>7401</v>
       </c>
-      <c r="P12" s="23">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="29">
+        <v>8392</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="16">
         <v>8868</v>
       </c>
-      <c r="Q12" s="23">
+    </row>
+    <row r="13" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="29">
+        <v>3739</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="16">
         <v>66515</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="15" t="s">
+    <row r="14" spans="1:5" ht="14.4" customHeight="1" thickBot="1">
+      <c r="A14" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="37">
+        <v>3945</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="20">
+        <v>9707</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="3" max="3" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="32.4" customHeight="1" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E15" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="28" t="s">
+      <c r="D1" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="28">
+        <v>9201</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="36">
+        <v>8835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="29">
+        <v>9634</v>
+      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="16">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="29">
+        <v>6394</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="16">
+        <v>9756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="29">
+        <v>8597</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="16">
+        <v>6164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="29">
+        <v>9947</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="16">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="28" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="29">
+        <v>2058</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="16">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="29">
+        <v>4397</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="16">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="29">
+        <v>8746</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="16">
+        <v>8477</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="29">
+        <v>2928</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="16">
+        <v>5463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29">
+        <v>8252</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="16">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="31"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-    </row>
-    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E17" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="18">
-        <v>9201</v>
-      </c>
-      <c r="G17" s="18">
-        <v>9634</v>
-      </c>
-      <c r="H17" s="18">
-        <v>6394</v>
-      </c>
-      <c r="I17" s="18">
-        <v>8597</v>
-      </c>
-      <c r="J17" s="18">
-        <v>9947</v>
-      </c>
-      <c r="K17" s="18">
-        <v>2058</v>
-      </c>
-      <c r="L17" s="18">
-        <v>4397</v>
-      </c>
-      <c r="M17" s="18">
-        <v>8746</v>
-      </c>
-      <c r="N17" s="18">
-        <v>2928</v>
-      </c>
-      <c r="O17" s="18">
-        <v>8252</v>
-      </c>
-      <c r="P17" s="18">
+      <c r="B12" s="33"/>
+      <c r="C12" s="29">
         <v>1583</v>
       </c>
-      <c r="Q17" s="18">
+      <c r="D12" s="24"/>
+      <c r="E12" s="16">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="29">
         <v>5086</v>
       </c>
-    </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-    </row>
-    <row r="19" spans="5:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="23">
-        <v>8835</v>
-      </c>
-      <c r="G19" s="23">
-        <v>8118</v>
-      </c>
-      <c r="H19" s="23">
-        <v>9756</v>
-      </c>
-      <c r="I19" s="23">
-        <v>6164</v>
-      </c>
-      <c r="J19" s="23">
-        <v>5043</v>
-      </c>
-      <c r="K19" s="23">
-        <v>4523</v>
-      </c>
-      <c r="L19" s="23">
-        <v>3408</v>
-      </c>
-      <c r="M19" s="23">
-        <v>8477</v>
-      </c>
-      <c r="N19" s="23">
-        <v>5463</v>
-      </c>
-      <c r="O19" s="23">
-        <v>1581</v>
-      </c>
-      <c r="P19" s="23">
-        <v>1568</v>
-      </c>
-      <c r="Q19" s="23">
+      <c r="D13" s="24"/>
+      <c r="E13" s="16">
         <v>9640</v>
       </c>
     </row>
+    <row r="14" spans="1:5" ht="14.4" thickBot="1">
+      <c r="A14" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="37">
+        <v>4590</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="20">
+        <v>5614</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
+  <mergeCells count="14">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -289,31 +289,31 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
-      <color/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
-      <color/>
       <name val="Aptos Narrow"/>
     </font>
     <font/>
     <font>
       <sz val="11.0"/>
-      <color/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="11.0"/>
-      <color/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
     </font>
   </fonts>
   <fills count="4">
@@ -753,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -778,9 +778,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -872,6 +869,9 @@
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="26" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -894,9 +894,6 @@
     </xf>
     <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1809,11 +1806,11 @@
         <v>21</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="2"/>
@@ -2282,25 +2279,25 @@
       <c r="A30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>3647.0</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>8677.0</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>5463.0</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>1035.0</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -2819,31 +2816,31 @@
       <c r="A46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>5614.0</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>1538.0</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <v>1867.0</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="9">
         <v>8872.0</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="9">
         <v>9956.0</v>
       </c>
       <c r="K46" s="6" t="s">
@@ -3361,25 +3358,25 @@
       <c r="C62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="9">
         <v>9868.0</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="9">
         <v>2396.0</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="9">
         <v>4465.0</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J62" s="10">
+      <c r="J62" s="9">
         <v>5518.0</v>
       </c>
       <c r="K62" s="6" t="s">
@@ -3709,29 +3706,29 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4299,11 +4296,11 @@
         <v>21</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="2"/>
@@ -4772,25 +4769,25 @@
       <c r="A30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>3647.0</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>8677.0</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>5463.0</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>1035.0</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -5309,31 +5306,31 @@
       <c r="A46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>5614.0</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>1538.0</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <v>1867.0</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="9">
         <v>8872.0</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="9">
         <v>9956.0</v>
       </c>
       <c r="K46" s="6" t="s">
@@ -5851,25 +5848,25 @@
       <c r="C62" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="9">
         <v>9868.0</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="9">
         <v>2396.0</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="9">
         <v>4465.0</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J62" s="10">
+      <c r="J62" s="9">
         <v>5518.0</v>
       </c>
       <c r="K62" s="6" t="s">
@@ -6198,30 +6195,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="I33:J33"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A33:B33"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="K17:L17"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E33:F33"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -6237,336 +6234,333 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="15.14"/>
-    <col customWidth="1" min="3" max="3" width="14.29"/>
+    <col customWidth="1" min="1" max="3" width="17.71"/>
     <col customWidth="1" min="4" max="4" width="10.71"/>
-    <col customWidth="1" min="5" max="8" width="11.86"/>
-    <col customWidth="1" min="9" max="11" width="10.71"/>
+    <col customWidth="1" min="5" max="8" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="27" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="29" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="E9" s="29" t="s">
+      <c r="C9" s="24"/>
+      <c r="E9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="27" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="27" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="32" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="B15" s="35"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -6574,7 +6568,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="35"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6582,7 +6576,7 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="B17" s="35"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -6590,7 +6584,7 @@
       <c r="H17" s="8"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="B18" s="35"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -6598,7 +6592,7 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="B19" s="35"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6606,7 +6600,7 @@
       <c r="H19" s="8"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="B20" s="35"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -6614,7 +6608,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="35"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -6622,7 +6616,7 @@
       <c r="H21" s="8"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="35"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -6630,7 +6624,7 @@
       <c r="H22" s="8"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="B23" s="35"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -6638,7 +6632,7 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="B24" s="35"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -6646,7 +6640,7 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="35"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -6654,7 +6648,7 @@
       <c r="H25" s="8"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="35"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -6662,7 +6656,7 @@
       <c r="H26" s="8"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="B27" s="35"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -6670,7 +6664,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="B28" s="35"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -6678,7 +6672,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -6686,7 +6680,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="B30" s="35"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -6694,7 +6688,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -6702,7 +6696,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="B32" s="35"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -6710,7 +6704,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -6718,7 +6712,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="B34" s="35"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -6726,7 +6720,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
@@ -6734,7 +6728,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="B36" s="35"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
@@ -6742,7 +6736,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="35"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -6750,7 +6744,7 @@
       <c r="H37" s="8"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="35"/>
+      <c r="B38" s="34"/>
       <c r="C38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -6758,7 +6752,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="B39" s="35"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -6766,7 +6760,7 @@
       <c r="H39" s="8"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="B40" s="35"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -6774,7 +6768,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="B41" s="35"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -6782,7 +6776,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="B42" s="35"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -6790,7 +6784,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="B43" s="35"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -6798,7 +6792,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="B44" s="35"/>
+      <c r="B44" s="34"/>
       <c r="C44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -6806,7 +6800,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="B45" s="35"/>
+      <c r="B45" s="34"/>
       <c r="C45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -6814,7 +6808,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="B46" s="35"/>
+      <c r="B46" s="34"/>
       <c r="C46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -6822,7 +6816,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="35"/>
+      <c r="B47" s="34"/>
       <c r="C47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
@@ -6830,7 +6824,7 @@
       <c r="H47" s="8"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="35"/>
+      <c r="B48" s="34"/>
       <c r="C48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
@@ -6838,7 +6832,7 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="35"/>
+      <c r="B49" s="34"/>
       <c r="C49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
@@ -6846,7 +6840,7 @@
       <c r="H49" s="8"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="B50" s="35"/>
+      <c r="B50" s="34"/>
       <c r="C50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
@@ -6854,7 +6848,7 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="B51" s="35"/>
+      <c r="B51" s="34"/>
       <c r="C51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
@@ -6862,7 +6856,7 @@
       <c r="H51" s="8"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="35"/>
+      <c r="B52" s="34"/>
       <c r="C52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -6870,7 +6864,7 @@
       <c r="H52" s="8"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="35"/>
+      <c r="B53" s="34"/>
       <c r="C53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
@@ -6878,7 +6872,7 @@
       <c r="H53" s="8"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="B54" s="35"/>
+      <c r="B54" s="34"/>
       <c r="C54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -6886,7 +6880,7 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="B55" s="35"/>
+      <c r="B55" s="34"/>
       <c r="C55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -6894,7 +6888,7 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="B56" s="35"/>
+      <c r="B56" s="34"/>
       <c r="C56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
@@ -6902,7 +6896,7 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="B57" s="35"/>
+      <c r="B57" s="34"/>
       <c r="C57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -6910,7 +6904,7 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="B58" s="35"/>
+      <c r="B58" s="34"/>
       <c r="C58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -6918,7 +6912,7 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="B59" s="35"/>
+      <c r="B59" s="34"/>
       <c r="C59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -6926,7 +6920,7 @@
       <c r="H59" s="8"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="35"/>
+      <c r="B60" s="34"/>
       <c r="C60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -6934,7 +6928,7 @@
       <c r="H60" s="8"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="35"/>
+      <c r="B61" s="34"/>
       <c r="C61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -6942,7 +6936,7 @@
       <c r="H61" s="8"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="35"/>
+      <c r="B62" s="34"/>
       <c r="C62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -6950,7 +6944,7 @@
       <c r="H62" s="8"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="35"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -6958,7 +6952,7 @@
       <c r="H63" s="8"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="B64" s="35"/>
+      <c r="B64" s="34"/>
       <c r="C64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -6966,7 +6960,7 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="B65" s="35"/>
+      <c r="B65" s="34"/>
       <c r="C65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
@@ -6974,7 +6968,7 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="35"/>
+      <c r="B66" s="34"/>
       <c r="C66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -6982,7 +6976,7 @@
       <c r="H66" s="8"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="35"/>
+      <c r="B67" s="34"/>
       <c r="C67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -6990,7 +6984,7 @@
       <c r="H67" s="8"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="B68" s="35"/>
+      <c r="B68" s="34"/>
       <c r="C68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
@@ -6998,7 +6992,7 @@
       <c r="H68" s="8"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="B69" s="35"/>
+      <c r="B69" s="34"/>
       <c r="C69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
@@ -7006,7 +7000,7 @@
       <c r="H69" s="8"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="35"/>
+      <c r="B70" s="34"/>
       <c r="C70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
@@ -7014,7 +7008,7 @@
       <c r="H70" s="8"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="35"/>
+      <c r="B71" s="34"/>
       <c r="C71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
@@ -7022,7 +7016,7 @@
       <c r="H71" s="8"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="35"/>
+      <c r="B72" s="34"/>
       <c r="C72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
@@ -7030,7 +7024,7 @@
       <c r="H72" s="8"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="35"/>
+      <c r="B73" s="34"/>
       <c r="C73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
@@ -7038,7 +7032,7 @@
       <c r="H73" s="8"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="35"/>
+      <c r="B74" s="34"/>
       <c r="C74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -7046,7 +7040,7 @@
       <c r="H74" s="8"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="35"/>
+      <c r="B75" s="34"/>
       <c r="C75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
@@ -7054,7 +7048,7 @@
       <c r="H75" s="8"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="35"/>
+      <c r="B76" s="34"/>
       <c r="C76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -7062,7 +7056,7 @@
       <c r="H76" s="8"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="35"/>
+      <c r="B77" s="34"/>
       <c r="C77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -7070,7 +7064,7 @@
       <c r="H77" s="8"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="35"/>
+      <c r="B78" s="34"/>
       <c r="C78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -7078,7 +7072,7 @@
       <c r="H78" s="8"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="B79" s="35"/>
+      <c r="B79" s="34"/>
       <c r="C79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -7086,7 +7080,7 @@
       <c r="H79" s="8"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="B80" s="35"/>
+      <c r="B80" s="34"/>
       <c r="C80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
@@ -7094,7 +7088,7 @@
       <c r="H80" s="8"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="B81" s="35"/>
+      <c r="B81" s="34"/>
       <c r="C81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -7102,7 +7096,7 @@
       <c r="H81" s="8"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="B82" s="35"/>
+      <c r="B82" s="34"/>
       <c r="C82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -7110,7 +7104,7 @@
       <c r="H82" s="8"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="B83" s="35"/>
+      <c r="B83" s="34"/>
       <c r="C83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
@@ -7118,7 +7112,7 @@
       <c r="H83" s="8"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="B84" s="35"/>
+      <c r="B84" s="34"/>
       <c r="C84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
@@ -7126,7 +7120,7 @@
       <c r="H84" s="8"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="35"/>
+      <c r="B85" s="34"/>
       <c r="C85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -7134,7 +7128,7 @@
       <c r="H85" s="8"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="35"/>
+      <c r="B86" s="34"/>
       <c r="C86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
@@ -7142,7 +7136,7 @@
       <c r="H86" s="8"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="35"/>
+      <c r="B87" s="34"/>
       <c r="C87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -7150,7 +7144,7 @@
       <c r="H87" s="8"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="35"/>
+      <c r="B88" s="34"/>
       <c r="C88" s="8"/>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
@@ -7158,7 +7152,7 @@
       <c r="H88" s="8"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="B89" s="35"/>
+      <c r="B89" s="34"/>
       <c r="C89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -7166,7 +7160,7 @@
       <c r="H89" s="8"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="B90" s="35"/>
+      <c r="B90" s="34"/>
       <c r="C90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -7174,7 +7168,7 @@
       <c r="H90" s="8"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="35"/>
+      <c r="B91" s="34"/>
       <c r="C91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -7182,7 +7176,7 @@
       <c r="H91" s="8"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="35"/>
+      <c r="B92" s="34"/>
       <c r="C92" s="8"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -7190,7 +7184,7 @@
       <c r="H92" s="8"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="35"/>
+      <c r="B93" s="34"/>
       <c r="C93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
@@ -7198,7 +7192,7 @@
       <c r="H93" s="8"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="35"/>
+      <c r="B94" s="34"/>
       <c r="C94" s="8"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
@@ -7206,7 +7200,7 @@
       <c r="H94" s="8"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="B95" s="35"/>
+      <c r="B95" s="34"/>
       <c r="C95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -7214,7 +7208,7 @@
       <c r="H95" s="8"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="B96" s="35"/>
+      <c r="B96" s="34"/>
       <c r="C96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -7222,7 +7216,7 @@
       <c r="H96" s="8"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="B97" s="35"/>
+      <c r="B97" s="34"/>
       <c r="C97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
@@ -7230,7 +7224,7 @@
       <c r="H97" s="8"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="B98" s="35"/>
+      <c r="B98" s="34"/>
       <c r="C98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
@@ -7238,7 +7232,7 @@
       <c r="H98" s="8"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="B99" s="35"/>
+      <c r="B99" s="34"/>
       <c r="C99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -7246,7 +7240,7 @@
       <c r="H99" s="8"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="B100" s="35"/>
+      <c r="B100" s="34"/>
       <c r="C100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -7269,26 +7263,30 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="8.43"/>
-    <col customWidth="1" min="4" max="4" width="13.57"/>
-    <col customWidth="1" min="5" max="5" width="10.43"/>
-    <col customWidth="1" min="6" max="11" width="10.71"/>
+    <col customWidth="1" min="3" max="5" width="16.57"/>
+    <col customWidth="1" min="6" max="6" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+    <row r="1" ht="53.25" customHeight="1">
+      <c r="A1" s="35" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>84</v>
       </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="40" t="s">
@@ -7302,6 +7300,12 @@
       <c r="E2" s="44">
         <v>7120.0</v>
       </c>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="45" t="s">
@@ -7312,9 +7316,15 @@
         <v>4089.0</v>
       </c>
       <c r="D3" s="48"/>
-      <c r="E3" s="25">
+      <c r="E3" s="24">
         <v>8058.0</v>
       </c>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="45" t="s">
@@ -7325,9 +7335,15 @@
         <v>8216.0</v>
       </c>
       <c r="D4" s="48"/>
-      <c r="E4" s="25">
+      <c r="E4" s="24">
         <v>7792.0</v>
       </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="45" t="s">
@@ -7338,9 +7354,15 @@
         <v>4504.0</v>
       </c>
       <c r="D5" s="48"/>
-      <c r="E5" s="25">
+      <c r="E5" s="24">
         <v>7612.0</v>
       </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="45" t="s">
@@ -7351,9 +7373,15 @@
         <v>9390.0</v>
       </c>
       <c r="D6" s="48"/>
-      <c r="E6" s="25">
+      <c r="E6" s="24">
         <v>1324.0</v>
       </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
     </row>
     <row r="7" ht="13.5" customHeight="1">
       <c r="A7" s="45" t="s">
@@ -7364,9 +7392,15 @@
         <v>6014.0</v>
       </c>
       <c r="D7" s="48"/>
-      <c r="E7" s="25">
+      <c r="E7" s="24">
         <v>8036.0</v>
       </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="45" t="s">
@@ -7377,9 +7411,15 @@
         <v>2529.0</v>
       </c>
       <c r="D8" s="48"/>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>6665.0</v>
       </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
       <c r="A9" s="45" t="s">
@@ -7390,9 +7430,15 @@
         <v>7609.0</v>
       </c>
       <c r="D9" s="48"/>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <v>8698.0</v>
       </c>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="45" t="s">
@@ -7403,12 +7449,18 @@
         <v>6767.0</v>
       </c>
       <c r="D10" s="48"/>
-      <c r="E10" s="25">
+      <c r="E10" s="24">
         <v>1648.0</v>
       </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="45" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="46"/>
@@ -7416,12 +7468,18 @@
         <v>2068.0</v>
       </c>
       <c r="D11" s="48"/>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <v>4954.0</v>
       </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="45" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="46"/>
@@ -7429,9 +7487,15 @@
         <v>4498.0</v>
       </c>
       <c r="D12" s="48"/>
-      <c r="E12" s="25">
+      <c r="E12" s="24">
         <v>4994.0</v>
       </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="45" t="s">
@@ -7442,21 +7506,1371 @@
         <v>6914.0</v>
       </c>
       <c r="D13" s="48"/>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <v>3787.0</v>
       </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="52">
+      <c r="B14" s="50"/>
+      <c r="C14" s="51">
         <v>1837.0</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33">
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
         <v>5328.0</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+    </row>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+    </row>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+    </row>
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+    </row>
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+    </row>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+    </row>
+    <row r="24" ht="13.5" customHeight="1">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+    </row>
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+    </row>
+    <row r="32" ht="13.5" customHeight="1">
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+    </row>
+    <row r="33" ht="13.5" customHeight="1">
+      <c r="A33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+    </row>
+    <row r="34" ht="13.5" customHeight="1">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+    </row>
+    <row r="35" ht="13.5" customHeight="1">
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+    </row>
+    <row r="36" ht="13.5" customHeight="1">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+    </row>
+    <row r="37" ht="13.5" customHeight="1">
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+    </row>
+    <row r="38" ht="13.5" customHeight="1">
+      <c r="A38" s="39"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+    </row>
+    <row r="39" ht="13.5" customHeight="1">
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+    </row>
+    <row r="40" ht="13.5" customHeight="1">
+      <c r="A40" s="39"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+    </row>
+    <row r="41" ht="13.5" customHeight="1">
+      <c r="A41" s="39"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+    </row>
+    <row r="42" ht="13.5" customHeight="1">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+    </row>
+    <row r="43" ht="13.5" customHeight="1">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1">
+      <c r="A44" s="39"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="A45" s="39"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+    </row>
+    <row r="46" ht="13.5" customHeight="1">
+      <c r="A46" s="39"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="A47" s="39"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39"/>
+      <c r="K47" s="39"/>
+    </row>
+    <row r="48" ht="13.5" customHeight="1">
+      <c r="A48" s="39"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="39"/>
+      <c r="K48" s="39"/>
+    </row>
+    <row r="49" ht="13.5" customHeight="1">
+      <c r="A49" s="39"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+    </row>
+    <row r="50" ht="13.5" customHeight="1">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+    </row>
+    <row r="51" ht="13.5" customHeight="1">
+      <c r="A51" s="39"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="39"/>
+    </row>
+    <row r="52" ht="13.5" customHeight="1">
+      <c r="A52" s="39"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+    </row>
+    <row r="53" ht="13.5" customHeight="1">
+      <c r="A53" s="39"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39"/>
+      <c r="K53" s="39"/>
+    </row>
+    <row r="54" ht="13.5" customHeight="1">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+    </row>
+    <row r="55" ht="13.5" customHeight="1">
+      <c r="A55" s="39"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39"/>
+      <c r="K55" s="39"/>
+    </row>
+    <row r="56" ht="13.5" customHeight="1">
+      <c r="A56" s="39"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+    </row>
+    <row r="57" ht="13.5" customHeight="1">
+      <c r="A57" s="39"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="39"/>
+    </row>
+    <row r="58" ht="13.5" customHeight="1">
+      <c r="A58" s="39"/>
+      <c r="B58" s="39"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
+    </row>
+    <row r="59" ht="13.5" customHeight="1">
+      <c r="A59" s="39"/>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
+    </row>
+    <row r="60" ht="13.5" customHeight="1">
+      <c r="A60" s="39"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+    </row>
+    <row r="61" ht="13.5" customHeight="1">
+      <c r="A61" s="39"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
+    </row>
+    <row r="62" ht="13.5" customHeight="1">
+      <c r="A62" s="39"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+    </row>
+    <row r="63" ht="13.5" customHeight="1">
+      <c r="A63" s="39"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39"/>
+    </row>
+    <row r="64" ht="13.5" customHeight="1">
+      <c r="A64" s="39"/>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
+    </row>
+    <row r="65" ht="13.5" customHeight="1">
+      <c r="A65" s="39"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+    </row>
+    <row r="66" ht="13.5" customHeight="1">
+      <c r="A66" s="39"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+    </row>
+    <row r="67" ht="13.5" customHeight="1">
+      <c r="A67" s="39"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
+    </row>
+    <row r="68" ht="13.5" customHeight="1">
+      <c r="A68" s="39"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
+    </row>
+    <row r="69" ht="13.5" customHeight="1">
+      <c r="A69" s="39"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39"/>
+      <c r="K69" s="39"/>
+    </row>
+    <row r="70" ht="13.5" customHeight="1">
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
+    </row>
+    <row r="71" ht="13.5" customHeight="1">
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39"/>
+      <c r="K71" s="39"/>
+    </row>
+    <row r="72" ht="13.5" customHeight="1">
+      <c r="A72" s="39"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39"/>
+      <c r="K72" s="39"/>
+    </row>
+    <row r="73" ht="13.5" customHeight="1">
+      <c r="A73" s="39"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="39"/>
+      <c r="K73" s="39"/>
+    </row>
+    <row r="74" ht="13.5" customHeight="1">
+      <c r="A74" s="39"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="39"/>
+      <c r="K74" s="39"/>
+    </row>
+    <row r="75" ht="13.5" customHeight="1">
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
+    </row>
+    <row r="76" ht="13.5" customHeight="1">
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
+      <c r="K76" s="39"/>
+    </row>
+    <row r="77" ht="13.5" customHeight="1">
+      <c r="A77" s="39"/>
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="39"/>
+    </row>
+    <row r="78" ht="13.5" customHeight="1">
+      <c r="A78" s="39"/>
+      <c r="B78" s="39"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39"/>
+      <c r="K78" s="39"/>
+    </row>
+    <row r="79" ht="13.5" customHeight="1">
+      <c r="A79" s="39"/>
+      <c r="B79" s="39"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39"/>
+      <c r="K79" s="39"/>
+    </row>
+    <row r="80" ht="13.5" customHeight="1">
+      <c r="A80" s="39"/>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
+    </row>
+    <row r="81" ht="13.5" customHeight="1">
+      <c r="A81" s="39"/>
+      <c r="B81" s="39"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="E81" s="39"/>
+      <c r="F81" s="39"/>
+      <c r="G81" s="39"/>
+      <c r="H81" s="39"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="39"/>
+      <c r="K81" s="39"/>
+    </row>
+    <row r="82" ht="13.5" customHeight="1">
+      <c r="A82" s="39"/>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="39"/>
+      <c r="G82" s="39"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
+    </row>
+    <row r="83" ht="13.5" customHeight="1">
+      <c r="A83" s="39"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="39"/>
+      <c r="K83" s="39"/>
+    </row>
+    <row r="84" ht="13.5" customHeight="1">
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
+    </row>
+    <row r="85" ht="13.5" customHeight="1">
+      <c r="A85" s="39"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="39"/>
+      <c r="K85" s="39"/>
+    </row>
+    <row r="86" ht="13.5" customHeight="1">
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
+      <c r="J86" s="39"/>
+      <c r="K86" s="39"/>
+    </row>
+    <row r="87" ht="13.5" customHeight="1">
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="39"/>
+      <c r="K87" s="39"/>
+    </row>
+    <row r="88" ht="13.5" customHeight="1">
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
+      <c r="J88" s="39"/>
+      <c r="K88" s="39"/>
+    </row>
+    <row r="89" ht="13.5" customHeight="1">
+      <c r="A89" s="39"/>
+      <c r="B89" s="39"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+    </row>
+    <row r="90" ht="13.5" customHeight="1">
+      <c r="A90" s="39"/>
+      <c r="B90" s="39"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="39"/>
+      <c r="G90" s="39"/>
+      <c r="H90" s="39"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="39"/>
+      <c r="K90" s="39"/>
+    </row>
+    <row r="91" ht="13.5" customHeight="1">
+      <c r="A91" s="39"/>
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
+      <c r="I91" s="39"/>
+      <c r="J91" s="39"/>
+      <c r="K91" s="39"/>
+    </row>
+    <row r="92" ht="13.5" customHeight="1">
+      <c r="A92" s="39"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
+      <c r="J92" s="39"/>
+      <c r="K92" s="39"/>
+    </row>
+    <row r="93" ht="13.5" customHeight="1">
+      <c r="A93" s="39"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+    </row>
+    <row r="94" ht="13.5" customHeight="1">
+      <c r="A94" s="39"/>
+      <c r="B94" s="39"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="39"/>
+      <c r="E94" s="39"/>
+      <c r="F94" s="39"/>
+      <c r="G94" s="39"/>
+      <c r="H94" s="39"/>
+      <c r="I94" s="39"/>
+      <c r="J94" s="39"/>
+      <c r="K94" s="39"/>
+    </row>
+    <row r="95" ht="13.5" customHeight="1">
+      <c r="A95" s="39"/>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="39"/>
+      <c r="I95" s="39"/>
+      <c r="J95" s="39"/>
+      <c r="K95" s="39"/>
+    </row>
+    <row r="96" ht="13.5" customHeight="1">
+      <c r="A96" s="39"/>
+      <c r="B96" s="39"/>
+      <c r="C96" s="39"/>
+      <c r="D96" s="39"/>
+      <c r="E96" s="39"/>
+      <c r="F96" s="39"/>
+      <c r="G96" s="39"/>
+      <c r="H96" s="39"/>
+      <c r="I96" s="39"/>
+      <c r="J96" s="39"/>
+      <c r="K96" s="39"/>
+    </row>
+    <row r="97" ht="13.5" customHeight="1">
+      <c r="A97" s="39"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="39"/>
+      <c r="I97" s="39"/>
+      <c r="J97" s="39"/>
+      <c r="K97" s="39"/>
+    </row>
+    <row r="98" ht="13.5" customHeight="1">
+      <c r="A98" s="39"/>
+      <c r="B98" s="39"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="39"/>
+      <c r="K98" s="39"/>
+    </row>
+    <row r="99" ht="13.5" customHeight="1">
+      <c r="A99" s="39"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
+      <c r="J99" s="39"/>
+      <c r="K99" s="39"/>
+    </row>
+    <row r="100" ht="13.5" customHeight="1">
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="39"/>
+      <c r="K100" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="10.71"/>
+    <col customWidth="1" min="3" max="5" width="18.43"/>
+    <col customWidth="1" min="6" max="6" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="39.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42">
+        <v>7928.0</v>
+      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44">
+        <v>8131.0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47">
+        <v>4675.0</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="E3" s="24">
+        <v>5063.0</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47">
+        <v>6301.0</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="24">
+        <v>2537.0</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="47">
+        <v>1020.0</v>
+      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="24">
+        <v>8684.0</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47">
+        <v>1330.0</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="24">
+        <v>6409.0</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="A7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47">
+        <v>9856.0</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="24">
+        <v>5988.0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="47">
+        <v>5817.0</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="24">
+        <v>2768.0</v>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="A9" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="47">
+        <v>1116.0</v>
+      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="24">
+        <v>9182.0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="47">
+        <v>5806.0</v>
+      </c>
+      <c r="D10" s="48"/>
+      <c r="E10" s="24">
+        <v>6217.0</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47">
+        <v>6523.0</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="24">
+        <v>7401.0</v>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="A12" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
+        <v>8392.0</v>
+      </c>
+      <c r="D12" s="48"/>
+      <c r="E12" s="24">
+        <v>8868.0</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="46"/>
+      <c r="C13" s="47">
+        <v>3739.0</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="24">
+        <v>66515.0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51">
+        <v>3945.0</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
+        <v>9707.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1"/>
@@ -7547,6 +8961,13 @@
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -7554,13 +8975,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -7569,7 +8983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
@@ -7577,90 +8991,88 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="8.43"/>
-    <col customWidth="1" min="4" max="4" width="13.57"/>
-    <col customWidth="1" min="5" max="5" width="10.43"/>
-    <col customWidth="1" min="6" max="11" width="10.71"/>
+    <col customWidth="1" min="3" max="5" width="17.0"/>
+    <col customWidth="1" min="6" max="6" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>71</v>
+      <c r="A1" s="35" t="s">
+        <v>87</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="38" t="s">
+      <c r="C1" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" ht="13.5" customHeight="1">
       <c r="A2" s="40" t="s">
         <v>85</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="42">
-        <v>7928.0</v>
+        <v>9201.0</v>
       </c>
       <c r="D2" s="43"/>
       <c r="E2" s="44">
-        <v>8131.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+        <v>8835.0</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1">
       <c r="A3" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="46"/>
       <c r="C3" s="47">
-        <v>4675.0</v>
+        <v>9634.0</v>
       </c>
       <c r="D3" s="48"/>
-      <c r="E3" s="25">
-        <v>5063.0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+      <c r="E3" s="24">
+        <v>8118.0</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="A4" s="45" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="46"/>
       <c r="C4" s="47">
-        <v>6301.0</v>
+        <v>6394.0</v>
       </c>
       <c r="D4" s="48"/>
-      <c r="E4" s="25">
-        <v>2537.0</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
+      <c r="E4" s="24">
+        <v>9756.0</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1">
       <c r="A5" s="45" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="46"/>
       <c r="C5" s="47">
-        <v>1020.0</v>
+        <v>8597.0</v>
       </c>
       <c r="D5" s="48"/>
-      <c r="E5" s="25">
-        <v>8684.0</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
+      <c r="E5" s="24">
+        <v>6164.0</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
       <c r="A6" s="45" t="s">
         <v>86</v>
       </c>
       <c r="B6" s="46"/>
       <c r="C6" s="47">
-        <v>1330.0</v>
+        <v>9947.0</v>
       </c>
       <c r="D6" s="48"/>
-      <c r="E6" s="25">
-        <v>6409.0</v>
+      <c r="E6" s="24">
+        <v>5043.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
@@ -7669,24 +9081,24 @@
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="47">
-        <v>9856.0</v>
+        <v>2058.0</v>
       </c>
       <c r="D7" s="48"/>
-      <c r="E7" s="25">
-        <v>5988.0</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+      <c r="E7" s="24">
+        <v>4523.0</v>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
       <c r="A8" s="45" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="46"/>
       <c r="C8" s="47">
-        <v>5817.0</v>
+        <v>4397.0</v>
       </c>
       <c r="D8" s="48"/>
-      <c r="E8" s="25">
-        <v>2768.0</v>
+      <c r="E8" s="24">
+        <v>3408.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
@@ -7695,76 +9107,76 @@
       </c>
       <c r="B9" s="46"/>
       <c r="C9" s="47">
-        <v>1116.0</v>
+        <v>8746.0</v>
       </c>
       <c r="D9" s="48"/>
-      <c r="E9" s="25">
-        <v>9182.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
+      <c r="E9" s="24">
+        <v>8477.0</v>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
       <c r="A10" s="45" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="46"/>
       <c r="C10" s="47">
-        <v>5806.0</v>
+        <v>2928.0</v>
       </c>
       <c r="D10" s="48"/>
-      <c r="E10" s="25">
-        <v>6217.0</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="49" t="s">
+      <c r="E10" s="24">
+        <v>5463.0</v>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="A11" s="45" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="46"/>
       <c r="C11" s="47">
-        <v>6523.0</v>
+        <v>8252.0</v>
       </c>
       <c r="D11" s="48"/>
-      <c r="E11" s="25">
-        <v>7401.0</v>
+      <c r="E11" s="24">
+        <v>1581.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="45" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="46"/>
       <c r="C12" s="47">
-        <v>8392.0</v>
+        <v>1583.0</v>
       </c>
       <c r="D12" s="48"/>
-      <c r="E12" s="25">
-        <v>8868.0</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
+      <c r="E12" s="24">
+        <v>1568.0</v>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
       <c r="A13" s="45" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="46"/>
       <c r="C13" s="47">
-        <v>3739.0</v>
+        <v>5086.0</v>
       </c>
       <c r="D13" s="48"/>
-      <c r="E13" s="25">
-        <v>66515.0</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="E13" s="24">
+        <v>9640.0</v>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="A14" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="52">
-        <v>3945.0</v>
-      </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33">
-        <v>9707.0</v>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51">
+        <v>4590.0</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
+        <v>5614.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1"/>
@@ -7855,314 +9267,13 @@
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-  </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="10.14"/>
-    <col customWidth="1" min="4" max="4" width="13.57"/>
-    <col customWidth="1" min="5" max="5" width="10.43"/>
-    <col customWidth="1" min="6" max="11" width="10.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42">
-        <v>9201.0</v>
-      </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44">
-        <v>8835.0</v>
-      </c>
-    </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47">
-        <v>9634.0</v>
-      </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="25">
-        <v>8118.0</v>
-      </c>
-    </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47">
-        <v>6394.0</v>
-      </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="25">
-        <v>9756.0</v>
-      </c>
-    </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
-        <v>8597.0</v>
-      </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="25">
-        <v>6164.0</v>
-      </c>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
-        <v>9947.0</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="25">
-        <v>5043.0</v>
-      </c>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47">
-        <v>2058.0</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="25">
-        <v>4523.0</v>
-      </c>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47">
-        <v>4397.0</v>
-      </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="25">
-        <v>3408.0</v>
-      </c>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47">
-        <v>8746.0</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="25">
-        <v>8477.0</v>
-      </c>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47">
-        <v>2928.0</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="25">
-        <v>5463.0</v>
-      </c>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
-        <v>8252.0</v>
-      </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="25">
-        <v>1581.0</v>
-      </c>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47">
-        <v>1583.0</v>
-      </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="25">
-        <v>1568.0</v>
-      </c>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47">
-        <v>5086.0</v>
-      </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="25">
-        <v>9640.0</v>
-      </c>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="52">
-        <v>4590.0</v>
-      </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33">
-        <v>5614.0</v>
-      </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
-    <row r="17" ht="13.5" customHeight="1"/>
-    <row r="18" ht="13.5" customHeight="1"/>
-    <row r="19" ht="13.5" customHeight="1"/>
-    <row r="20" ht="13.5" customHeight="1"/>
-    <row r="21" ht="13.5" customHeight="1"/>
-    <row r="22" ht="13.5" customHeight="1"/>
-    <row r="23" ht="13.5" customHeight="1"/>
-    <row r="24" ht="13.5" customHeight="1"/>
-    <row r="25" ht="13.5" customHeight="1"/>
-    <row r="26" ht="13.5" customHeight="1"/>
-    <row r="27" ht="13.5" customHeight="1"/>
-    <row r="28" ht="13.5" customHeight="1"/>
-    <row r="29" ht="13.5" customHeight="1"/>
-    <row r="30" ht="13.5" customHeight="1"/>
-    <row r="31" ht="13.5" customHeight="1"/>
-    <row r="32" ht="13.5" customHeight="1"/>
-    <row r="33" ht="13.5" customHeight="1"/>
-    <row r="34" ht="13.5" customHeight="1"/>
-    <row r="35" ht="13.5" customHeight="1"/>
-    <row r="36" ht="13.5" customHeight="1"/>
-    <row r="37" ht="13.5" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1"/>
-    <row r="39" ht="13.5" customHeight="1"/>
-    <row r="40" ht="13.5" customHeight="1"/>
-    <row r="41" ht="13.5" customHeight="1"/>
-    <row r="42" ht="13.5" customHeight="1"/>
-    <row r="43" ht="13.5" customHeight="1"/>
-    <row r="44" ht="13.5" customHeight="1"/>
-    <row r="45" ht="13.5" customHeight="1"/>
-    <row r="46" ht="13.5" customHeight="1"/>
-    <row r="47" ht="13.5" customHeight="1"/>
-    <row r="48" ht="13.5" customHeight="1"/>
-    <row r="49" ht="13.5" customHeight="1"/>
-    <row r="50" ht="13.5" customHeight="1"/>
-    <row r="51" ht="13.5" customHeight="1"/>
-    <row r="52" ht="13.5" customHeight="1"/>
-    <row r="53" ht="13.5" customHeight="1"/>
-    <row r="54" ht="13.5" customHeight="1"/>
-    <row r="55" ht="13.5" customHeight="1"/>
-    <row r="56" ht="13.5" customHeight="1"/>
-    <row r="57" ht="13.5" customHeight="1"/>
-    <row r="58" ht="13.5" customHeight="1"/>
-    <row r="59" ht="13.5" customHeight="1"/>
-    <row r="60" ht="13.5" customHeight="1"/>
-    <row r="61" ht="13.5" customHeight="1"/>
-    <row r="62" ht="13.5" customHeight="1"/>
-    <row r="63" ht="13.5" customHeight="1"/>
-    <row r="64" ht="13.5" customHeight="1"/>
-    <row r="65" ht="13.5" customHeight="1"/>
-    <row r="66" ht="13.5" customHeight="1"/>
-    <row r="67" ht="13.5" customHeight="1"/>
-    <row r="68" ht="13.5" customHeight="1"/>
-    <row r="69" ht="13.5" customHeight="1"/>
-    <row r="70" ht="13.5" customHeight="1"/>
-    <row r="71" ht="13.5" customHeight="1"/>
-    <row r="72" ht="13.5" customHeight="1"/>
-    <row r="73" ht="13.5" customHeight="1"/>
-    <row r="74" ht="13.5" customHeight="1"/>
-    <row r="75" ht="13.5" customHeight="1"/>
-    <row r="76" ht="13.5" customHeight="1"/>
-    <row r="77" ht="13.5" customHeight="1"/>
-    <row r="78" ht="13.5" customHeight="1"/>
-    <row r="79" ht="13.5" customHeight="1"/>
-    <row r="80" ht="13.5" customHeight="1"/>
-    <row r="81" ht="13.5" customHeight="1"/>
-    <row r="82" ht="13.5" customHeight="1"/>
-    <row r="83" ht="13.5" customHeight="1"/>
-    <row r="84" ht="13.5" customHeight="1"/>
-    <row r="85" ht="13.5" customHeight="1"/>
-    <row r="86" ht="13.5" customHeight="1"/>
-    <row r="87" ht="13.5" customHeight="1"/>
-    <row r="88" ht="13.5" customHeight="1"/>
-    <row r="89" ht="13.5" customHeight="1"/>
-    <row r="90" ht="13.5" customHeight="1"/>
-    <row r="91" ht="13.5" customHeight="1"/>
-    <row r="92" ht="13.5" customHeight="1"/>
-    <row r="93" ht="13.5" customHeight="1"/>
-    <row r="94" ht="13.5" customHeight="1"/>
-    <row r="95" ht="13.5" customHeight="1"/>
-    <row r="96" ht="13.5" customHeight="1"/>
-    <row r="97" ht="13.5" customHeight="1"/>
-    <row r="98" ht="13.5" customHeight="1"/>
-    <row r="99" ht="13.5" customHeight="1"/>
-    <row r="100" ht="13.5" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="14">
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A5:B5"/>
@@ -8170,13 +9281,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="91">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -96,7 +96,7 @@
     <t>Los psicópatas anónimos</t>
   </si>
   <si>
-    <t>EQUIPO 14</t>
+    <t>Las hipi colgas</t>
   </si>
   <si>
     <t>EQUIPO 15</t>
@@ -279,6 +279,12 @@
     <t>Los Locos escapistas</t>
   </si>
   <si>
+    <t xml:space="preserve">La Hipi Colgas </t>
+  </si>
+  <si>
+    <t>Las Hipi Colgas</t>
+  </si>
+  <si>
     <t>LOCO ATADO</t>
   </si>
   <si>
@@ -336,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="45">
     <border/>
     <border>
       <left style="medium">
@@ -632,24 +638,24 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color rgb="FF000000"/>
       </left>
-      <top style="medium">
+      <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <right style="medium">
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
+      <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -657,7 +663,10 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -668,7 +677,10 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -676,40 +688,40 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <right style="medium">
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -717,35 +729,144 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <right style="medium">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <right style="thin">
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -753,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -781,6 +902,9 @@
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -857,33 +981,21 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="31" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -892,15 +1004,52 @@
     <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="35" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="36" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="37" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="38" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="39" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="35" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="36" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="40" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="41" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="42" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="43" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="44" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="42" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="43" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="44" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2335,7 +2484,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
@@ -3705,30 +3854,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
     <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K33:L33"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4825,7 +4974,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
@@ -6195,16 +6344,19 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="C33:D33"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:D17"/>
@@ -6212,13 +6364,10 @@
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="K17:L17"/>
-    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E33:F33"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -6240,327 +6389,327 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="28" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="28" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="28" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="E9" s="28" t="s">
+      <c r="C9" s="25"/>
+      <c r="E9" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="28" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="30" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="27" t="s">
+      <c r="H11" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="H13" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="33" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="B15" s="34"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -6568,7 +6717,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="34"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6576,7 +6725,7 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="B17" s="34"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -6584,7 +6733,7 @@
       <c r="H17" s="8"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="B18" s="34"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -6592,7 +6741,7 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="B19" s="34"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6600,7 +6749,7 @@
       <c r="H19" s="8"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="B20" s="34"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -6608,7 +6757,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="34"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -6616,7 +6765,7 @@
       <c r="H21" s="8"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="34"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -6624,7 +6773,7 @@
       <c r="H22" s="8"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="B23" s="34"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -6632,7 +6781,7 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="B24" s="34"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -6640,7 +6789,7 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="34"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -6648,7 +6797,7 @@
       <c r="H25" s="8"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="34"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -6656,7 +6805,7 @@
       <c r="H26" s="8"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="B27" s="34"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -6664,7 +6813,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -6672,7 +6821,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -6680,7 +6829,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -6688,7 +6837,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -6696,7 +6845,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -6704,7 +6853,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -6712,7 +6861,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -6720,7 +6869,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
@@ -6728,7 +6877,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
@@ -6736,7 +6885,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="34"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -6744,7 +6893,7 @@
       <c r="H37" s="8"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="34"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -6752,7 +6901,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -6760,7 +6909,7 @@
       <c r="H39" s="8"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -6768,7 +6917,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="B41" s="34"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -6776,7 +6925,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="B42" s="34"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -6784,7 +6933,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="B43" s="34"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -6792,7 +6941,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="B44" s="34"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -6800,7 +6949,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="B45" s="34"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -6808,7 +6957,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="B46" s="34"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -6816,7 +6965,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="34"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
@@ -6824,7 +6973,7 @@
       <c r="H47" s="8"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="34"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
@@ -6832,7 +6981,7 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="34"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
@@ -6840,7 +6989,7 @@
       <c r="H49" s="8"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="B50" s="34"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
@@ -6848,7 +6997,7 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="B51" s="34"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
@@ -6856,7 +7005,7 @@
       <c r="H51" s="8"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="34"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -6864,7 +7013,7 @@
       <c r="H52" s="8"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="34"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
@@ -6872,7 +7021,7 @@
       <c r="H53" s="8"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="B54" s="34"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -6880,7 +7029,7 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="B55" s="34"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -6888,7 +7037,7 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="B56" s="34"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
@@ -6896,7 +7045,7 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="B57" s="34"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -6904,7 +7053,7 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="B58" s="34"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -6912,7 +7061,7 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="B59" s="34"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -6920,7 +7069,7 @@
       <c r="H59" s="8"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="34"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -6928,7 +7077,7 @@
       <c r="H60" s="8"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="34"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -6936,7 +7085,7 @@
       <c r="H61" s="8"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="34"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -6944,7 +7093,7 @@
       <c r="H62" s="8"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="34"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -6952,7 +7101,7 @@
       <c r="H63" s="8"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="B64" s="34"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -6960,7 +7109,7 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="B65" s="34"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
@@ -6968,7 +7117,7 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="34"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -6976,7 +7125,7 @@
       <c r="H66" s="8"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="34"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -6984,7 +7133,7 @@
       <c r="H67" s="8"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="B68" s="34"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
@@ -6992,7 +7141,7 @@
       <c r="H68" s="8"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="B69" s="34"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
@@ -7000,7 +7149,7 @@
       <c r="H69" s="8"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="34"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
@@ -7008,7 +7157,7 @@
       <c r="H70" s="8"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="34"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
@@ -7016,7 +7165,7 @@
       <c r="H71" s="8"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="34"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
@@ -7024,7 +7173,7 @@
       <c r="H72" s="8"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="34"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
@@ -7032,7 +7181,7 @@
       <c r="H73" s="8"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="34"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -7040,7 +7189,7 @@
       <c r="H74" s="8"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="34"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
@@ -7048,7 +7197,7 @@
       <c r="H75" s="8"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="34"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -7056,7 +7205,7 @@
       <c r="H76" s="8"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="34"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -7064,7 +7213,7 @@
       <c r="H77" s="8"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="34"/>
+      <c r="B78" s="35"/>
       <c r="C78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -7072,7 +7221,7 @@
       <c r="H78" s="8"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="B79" s="34"/>
+      <c r="B79" s="35"/>
       <c r="C79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -7080,7 +7229,7 @@
       <c r="H79" s="8"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="B80" s="34"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
@@ -7088,7 +7237,7 @@
       <c r="H80" s="8"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="B81" s="34"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -7096,7 +7245,7 @@
       <c r="H81" s="8"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="B82" s="34"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -7104,7 +7253,7 @@
       <c r="H82" s="8"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="B83" s="34"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
@@ -7112,7 +7261,7 @@
       <c r="H83" s="8"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="B84" s="34"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
@@ -7120,7 +7269,7 @@
       <c r="H84" s="8"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="34"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -7128,7 +7277,7 @@
       <c r="H85" s="8"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="34"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
@@ -7136,7 +7285,7 @@
       <c r="H86" s="8"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="34"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -7144,7 +7293,7 @@
       <c r="H87" s="8"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="34"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="8"/>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
@@ -7152,7 +7301,7 @@
       <c r="H88" s="8"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="B89" s="34"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -7160,7 +7309,7 @@
       <c r="H89" s="8"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="B90" s="34"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -7168,7 +7317,7 @@
       <c r="H90" s="8"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="34"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -7176,7 +7325,7 @@
       <c r="H91" s="8"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="34"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="8"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -7184,7 +7333,7 @@
       <c r="H92" s="8"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="34"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
@@ -7192,7 +7341,7 @@
       <c r="H93" s="8"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="34"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="8"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
@@ -7200,7 +7349,7 @@
       <c r="H94" s="8"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="B95" s="34"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -7208,7 +7357,7 @@
       <c r="H95" s="8"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="B96" s="34"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -7216,7 +7365,7 @@
       <c r="H96" s="8"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="B97" s="34"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
@@ -7224,7 +7373,7 @@
       <c r="H97" s="8"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="B98" s="34"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
@@ -7232,7 +7381,7 @@
       <c r="H98" s="8"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="B99" s="34"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -7240,7 +7389,7 @@
       <c r="H99" s="8"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="B100" s="34"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -7268,1393 +7417,1406 @@
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="36" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42">
+      <c r="B2" s="43"/>
+      <c r="C2" s="44">
         <v>1764.0</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44">
+      <c r="D2" s="45"/>
+      <c r="E2" s="46">
         <v>7120.0</v>
       </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47">
+      <c r="B3" s="48"/>
+      <c r="C3" s="49">
         <v>4089.0</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="24">
+      <c r="D3" s="50"/>
+      <c r="E3" s="51">
         <v>8058.0</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47">
+      <c r="B4" s="48"/>
+      <c r="C4" s="49">
         <v>8216.0</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="24">
+      <c r="D4" s="50"/>
+      <c r="E4" s="51">
         <v>7792.0</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>4504.0</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="24">
+      <c r="D5" s="50"/>
+      <c r="E5" s="51">
         <v>7612.0</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>9390.0</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="24">
+      <c r="D6" s="50"/>
+      <c r="E6" s="51">
         <v>1324.0</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47">
+      <c r="B7" s="48"/>
+      <c r="C7" s="49">
         <v>6014.0</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="24">
+      <c r="D7" s="50"/>
+      <c r="E7" s="51">
         <v>8036.0</v>
       </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47">
+      <c r="B8" s="48"/>
+      <c r="C8" s="49">
         <v>2529.0</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="24">
+      <c r="D8" s="50"/>
+      <c r="E8" s="51">
         <v>6665.0</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47">
+      <c r="B9" s="48"/>
+      <c r="C9" s="49">
         <v>7609.0</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="24">
+      <c r="D9" s="50"/>
+      <c r="E9" s="51">
         <v>8698.0</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47">
+      <c r="B10" s="48"/>
+      <c r="C10" s="49">
         <v>6767.0</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="24">
+      <c r="D10" s="50"/>
+      <c r="E10" s="51">
         <v>1648.0</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
+      <c r="B11" s="48"/>
+      <c r="C11" s="49">
         <v>2068.0</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="24">
+      <c r="D11" s="50"/>
+      <c r="E11" s="51">
         <v>4954.0</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47">
+      <c r="B12" s="48"/>
+      <c r="C12" s="49">
         <v>4498.0</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="24">
+      <c r="D12" s="50"/>
+      <c r="E12" s="51">
         <v>4994.0</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47">
+      <c r="B13" s="48"/>
+      <c r="C13" s="49">
         <v>6914.0</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="24">
+      <c r="D13" s="50"/>
+      <c r="E13" s="51">
         <v>3787.0</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51">
+      <c r="B14" s="48"/>
+      <c r="C14" s="49">
         <v>1837.0</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32">
+      <c r="D14" s="50"/>
+      <c r="E14" s="51">
         <v>5328.0</v>
       </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
+      <c r="A15" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54">
+        <v>2357.0</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="56">
+        <v>7799.0</v>
+      </c>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="39"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="39"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="39"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="39"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="39"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="39"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="39"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="39"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="39"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="41"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="39"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="39"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="39"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="41"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="39"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="39"/>
-      <c r="B46" s="39"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="39"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="A48" s="39"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="39"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="39"/>
-      <c r="K49" s="39"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="39"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="39"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="41"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="39"/>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="39"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="39"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="39"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="A56" s="39"/>
-      <c r="B56" s="39"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="41"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="A57" s="39"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="39"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="39"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39"/>
-      <c r="K57" s="39"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="39"/>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
+      <c r="A58" s="41"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+      <c r="K58" s="41"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="39"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="41"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="39"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
+      <c r="A60" s="41"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="41"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="A61" s="39"/>
-      <c r="B61" s="39"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
+      <c r="A61" s="41"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41"/>
+      <c r="J61" s="41"/>
+      <c r="K61" s="41"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="39"/>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
+      <c r="A62" s="41"/>
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+      <c r="K62" s="41"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="A63" s="39"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
+      <c r="A63" s="41"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+      <c r="K63" s="41"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="39"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
+      <c r="A64" s="41"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="41"/>
+      <c r="K64" s="41"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="39"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
+      <c r="A65" s="41"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+      <c r="K65" s="41"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="39"/>
-      <c r="B66" s="39"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
+      <c r="A66" s="41"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="41"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="39"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
+      <c r="A67" s="41"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41"/>
+      <c r="J67" s="41"/>
+      <c r="K67" s="41"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="39"/>
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
+      <c r="A68" s="41"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41"/>
+      <c r="J68" s="41"/>
+      <c r="K68" s="41"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="39"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
+      <c r="A69" s="41"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
+      <c r="J69" s="41"/>
+      <c r="K69" s="41"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="A70" s="39"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
+      <c r="A70" s="41"/>
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="41"/>
+      <c r="K70" s="41"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="A71" s="39"/>
-      <c r="B71" s="39"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="41"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="39"/>
-      <c r="B72" s="39"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39"/>
+      <c r="A72" s="41"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
+      <c r="J72" s="41"/>
+      <c r="K72" s="41"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="A73" s="39"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="41"/>
+      <c r="J73" s="41"/>
+      <c r="K73" s="41"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="A74" s="39"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39"/>
+      <c r="A74" s="41"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="41"/>
+      <c r="J74" s="41"/>
+      <c r="K74" s="41"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="A75" s="39"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
+      <c r="A75" s="41"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+      <c r="K75" s="41"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="A76" s="39"/>
-      <c r="B76" s="39"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
+      <c r="A76" s="41"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="41"/>
+      <c r="K76" s="41"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="39"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
+      <c r="A77" s="41"/>
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="41"/>
+      <c r="J77" s="41"/>
+      <c r="K77" s="41"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="A78" s="39"/>
-      <c r="B78" s="39"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="39"/>
-      <c r="J78" s="39"/>
-      <c r="K78" s="39"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
+      <c r="J78" s="41"/>
+      <c r="K78" s="41"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="A79" s="39"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="39"/>
-      <c r="E79" s="39"/>
-      <c r="F79" s="39"/>
-      <c r="G79" s="39"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
-      <c r="J79" s="39"/>
-      <c r="K79" s="39"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
+      <c r="J79" s="41"/>
+      <c r="K79" s="41"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="A80" s="39"/>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
+      <c r="J80" s="41"/>
+      <c r="K80" s="41"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="A81" s="39"/>
-      <c r="B81" s="39"/>
-      <c r="C81" s="39"/>
-      <c r="D81" s="39"/>
-      <c r="E81" s="39"/>
-      <c r="F81" s="39"/>
-      <c r="G81" s="39"/>
-      <c r="H81" s="39"/>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39"/>
-      <c r="K81" s="39"/>
+      <c r="A81" s="41"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="41"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="39"/>
-      <c r="B82" s="39"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
+      <c r="A82" s="41"/>
+      <c r="B82" s="41"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="41"/>
+      <c r="K82" s="41"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="39"/>
-      <c r="B83" s="39"/>
-      <c r="C83" s="39"/>
-      <c r="D83" s="39"/>
-      <c r="E83" s="39"/>
-      <c r="F83" s="39"/>
-      <c r="G83" s="39"/>
-      <c r="H83" s="39"/>
-      <c r="I83" s="39"/>
-      <c r="J83" s="39"/>
-      <c r="K83" s="39"/>
+      <c r="A83" s="41"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="41"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="39"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39"/>
-      <c r="G84" s="39"/>
-      <c r="H84" s="39"/>
-      <c r="I84" s="39"/>
-      <c r="J84" s="39"/>
-      <c r="K84" s="39"/>
+      <c r="A84" s="41"/>
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
+      <c r="J84" s="41"/>
+      <c r="K84" s="41"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="A85" s="39"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="39"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="39"/>
-      <c r="J85" s="39"/>
-      <c r="K85" s="39"/>
+      <c r="A85" s="41"/>
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="41"/>
+      <c r="J85" s="41"/>
+      <c r="K85" s="41"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="A86" s="39"/>
-      <c r="B86" s="39"/>
-      <c r="C86" s="39"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39"/>
-      <c r="G86" s="39"/>
-      <c r="H86" s="39"/>
-      <c r="I86" s="39"/>
-      <c r="J86" s="39"/>
-      <c r="K86" s="39"/>
+      <c r="A86" s="41"/>
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
+      <c r="J86" s="41"/>
+      <c r="K86" s="41"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="39"/>
-      <c r="B87" s="39"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="39"/>
-      <c r="F87" s="39"/>
-      <c r="G87" s="39"/>
-      <c r="H87" s="39"/>
-      <c r="I87" s="39"/>
-      <c r="J87" s="39"/>
-      <c r="K87" s="39"/>
+      <c r="A87" s="41"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
+      <c r="J87" s="41"/>
+      <c r="K87" s="41"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="39"/>
-      <c r="B88" s="39"/>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39"/>
-      <c r="E88" s="39"/>
-      <c r="F88" s="39"/>
-      <c r="G88" s="39"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="39"/>
-      <c r="J88" s="39"/>
-      <c r="K88" s="39"/>
+      <c r="A88" s="41"/>
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="41"/>
+      <c r="I88" s="41"/>
+      <c r="J88" s="41"/>
+      <c r="K88" s="41"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="39"/>
-      <c r="B89" s="39"/>
-      <c r="C89" s="39"/>
-      <c r="D89" s="39"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39"/>
-      <c r="G89" s="39"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="39"/>
-      <c r="K89" s="39"/>
+      <c r="A89" s="41"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="41"/>
+      <c r="H89" s="41"/>
+      <c r="I89" s="41"/>
+      <c r="J89" s="41"/>
+      <c r="K89" s="41"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="39"/>
-      <c r="B90" s="39"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="39"/>
-      <c r="G90" s="39"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="39"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="39"/>
+      <c r="A90" s="41"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="41"/>
+      <c r="E90" s="41"/>
+      <c r="F90" s="41"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="41"/>
+      <c r="I90" s="41"/>
+      <c r="J90" s="41"/>
+      <c r="K90" s="41"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="A91" s="39"/>
-      <c r="B91" s="39"/>
-      <c r="C91" s="39"/>
-      <c r="D91" s="39"/>
-      <c r="E91" s="39"/>
-      <c r="F91" s="39"/>
-      <c r="G91" s="39"/>
-      <c r="H91" s="39"/>
-      <c r="I91" s="39"/>
-      <c r="J91" s="39"/>
-      <c r="K91" s="39"/>
+      <c r="A91" s="41"/>
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="41"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="41"/>
+      <c r="I91" s="41"/>
+      <c r="J91" s="41"/>
+      <c r="K91" s="41"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="A92" s="39"/>
-      <c r="B92" s="39"/>
-      <c r="C92" s="39"/>
-      <c r="D92" s="39"/>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-      <c r="G92" s="39"/>
-      <c r="H92" s="39"/>
-      <c r="I92" s="39"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="39"/>
+      <c r="A92" s="41"/>
+      <c r="B92" s="41"/>
+      <c r="C92" s="41"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="41"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
+      <c r="H92" s="41"/>
+      <c r="I92" s="41"/>
+      <c r="J92" s="41"/>
+      <c r="K92" s="41"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="39"/>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-      <c r="G93" s="39"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39"/>
-      <c r="J93" s="39"/>
-      <c r="K93" s="39"/>
+      <c r="A93" s="41"/>
+      <c r="B93" s="41"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="41"/>
+      <c r="F93" s="41"/>
+      <c r="G93" s="41"/>
+      <c r="H93" s="41"/>
+      <c r="I93" s="41"/>
+      <c r="J93" s="41"/>
+      <c r="K93" s="41"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="A94" s="39"/>
-      <c r="B94" s="39"/>
-      <c r="C94" s="39"/>
-      <c r="D94" s="39"/>
-      <c r="E94" s="39"/>
-      <c r="F94" s="39"/>
-      <c r="G94" s="39"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="39"/>
-      <c r="J94" s="39"/>
-      <c r="K94" s="39"/>
+      <c r="A94" s="41"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="41"/>
+      <c r="F94" s="41"/>
+      <c r="G94" s="41"/>
+      <c r="H94" s="41"/>
+      <c r="I94" s="41"/>
+      <c r="J94" s="41"/>
+      <c r="K94" s="41"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="39"/>
-      <c r="B95" s="39"/>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39"/>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="39"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
-      <c r="J95" s="39"/>
-      <c r="K95" s="39"/>
+      <c r="A95" s="41"/>
+      <c r="B95" s="41"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="41"/>
+      <c r="F95" s="41"/>
+      <c r="G95" s="41"/>
+      <c r="H95" s="41"/>
+      <c r="I95" s="41"/>
+      <c r="J95" s="41"/>
+      <c r="K95" s="41"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="39"/>
-      <c r="B96" s="39"/>
-      <c r="C96" s="39"/>
-      <c r="D96" s="39"/>
-      <c r="E96" s="39"/>
-      <c r="F96" s="39"/>
-      <c r="G96" s="39"/>
-      <c r="H96" s="39"/>
-      <c r="I96" s="39"/>
-      <c r="J96" s="39"/>
-      <c r="K96" s="39"/>
+      <c r="A96" s="41"/>
+      <c r="B96" s="41"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="41"/>
+      <c r="F96" s="41"/>
+      <c r="G96" s="41"/>
+      <c r="H96" s="41"/>
+      <c r="I96" s="41"/>
+      <c r="J96" s="41"/>
+      <c r="K96" s="41"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="A97" s="39"/>
-      <c r="B97" s="39"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39"/>
-      <c r="G97" s="39"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
-      <c r="K97" s="39"/>
+      <c r="A97" s="41"/>
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="41"/>
+      <c r="I97" s="41"/>
+      <c r="J97" s="41"/>
+      <c r="K97" s="41"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="A98" s="39"/>
-      <c r="B98" s="39"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="39"/>
-      <c r="K98" s="39"/>
+      <c r="A98" s="41"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="41"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="41"/>
+      <c r="K98" s="41"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="39"/>
-      <c r="B99" s="39"/>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="39"/>
-      <c r="F99" s="39"/>
-      <c r="G99" s="39"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
-      <c r="J99" s="39"/>
-      <c r="K99" s="39"/>
+      <c r="A99" s="41"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="41"/>
+      <c r="H99" s="41"/>
+      <c r="I99" s="41"/>
+      <c r="J99" s="41"/>
+      <c r="K99" s="41"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="39"/>
-      <c r="B100" s="39"/>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="39"/>
-      <c r="F100" s="39"/>
-      <c r="G100" s="39"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
-      <c r="J100" s="39"/>
-      <c r="K100" s="39"/>
+      <c r="A100" s="41"/>
+      <c r="B100" s="41"/>
+      <c r="C100" s="41"/>
+      <c r="D100" s="41"/>
+      <c r="E100" s="41"/>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="41"/>
+      <c r="J100" s="41"/>
+      <c r="K100" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A8:B8"/>
@@ -8662,13 +8824,7 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -8690,190 +8846,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="39.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="36" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="40" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42">
+      <c r="B2" s="43"/>
+      <c r="C2" s="44">
         <v>7928.0</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44">
+      <c r="D2" s="45"/>
+      <c r="E2" s="46">
         <v>8131.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47">
+      <c r="B3" s="48"/>
+      <c r="C3" s="49">
         <v>4675.0</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="24">
+      <c r="D3" s="50"/>
+      <c r="E3" s="51">
         <v>5063.0</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47">
+      <c r="B4" s="48"/>
+      <c r="C4" s="49">
         <v>6301.0</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="24">
+      <c r="D4" s="50"/>
+      <c r="E4" s="51">
         <v>2537.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>1020.0</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="24">
+      <c r="D5" s="50"/>
+      <c r="E5" s="51">
         <v>8684.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>1330.0</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="24">
+      <c r="D6" s="50"/>
+      <c r="E6" s="51">
         <v>6409.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47">
+      <c r="B7" s="48"/>
+      <c r="C7" s="49">
         <v>9856.0</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="24">
+      <c r="D7" s="50"/>
+      <c r="E7" s="51">
         <v>5988.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47">
+      <c r="B8" s="48"/>
+      <c r="C8" s="49">
         <v>5817.0</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="24">
+      <c r="D8" s="50"/>
+      <c r="E8" s="51">
         <v>2768.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47">
+      <c r="B9" s="48"/>
+      <c r="C9" s="49">
         <v>1116.0</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="24">
+      <c r="D9" s="50"/>
+      <c r="E9" s="51">
         <v>9182.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47">
+      <c r="B10" s="48"/>
+      <c r="C10" s="49">
         <v>5806.0</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="24">
+      <c r="D10" s="50"/>
+      <c r="E10" s="51">
         <v>6217.0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
+      <c r="B11" s="48"/>
+      <c r="C11" s="49">
         <v>6523.0</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="24">
+      <c r="D11" s="50"/>
+      <c r="E11" s="51">
         <v>7401.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47">
+      <c r="B12" s="48"/>
+      <c r="C12" s="49">
         <v>8392.0</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="24">
+      <c r="D12" s="50"/>
+      <c r="E12" s="51">
         <v>8868.0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47">
+      <c r="B13" s="48"/>
+      <c r="C13" s="49">
         <v>3739.0</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="24">
+      <c r="D13" s="50"/>
+      <c r="E13" s="51">
         <v>66515.0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51">
+      <c r="B14" s="48"/>
+      <c r="C14" s="49">
         <v>3945.0</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32">
+      <c r="D14" s="50"/>
+      <c r="E14" s="51">
         <v>9707.0</v>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="A15" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="58">
+        <v>4433.0</v>
+      </c>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60">
+        <v>1033.0</v>
+      </c>
+    </row>
     <row r="16" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
@@ -8960,7 +9128,14 @@
     <row r="99" ht="13.5" customHeight="1"/>
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A8:B8"/>
@@ -8968,13 +9143,7 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -8996,190 +9165,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="36" t="s">
+      <c r="A1" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1">
+      <c r="A2" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44">
+        <v>9201.0</v>
+      </c>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46">
+        <v>8835.0</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1">
+      <c r="A3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49">
+        <v>9634.0</v>
+      </c>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51">
+        <v>8118.0</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
+      <c r="A4" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49">
+        <v>6394.0</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51">
+        <v>9756.0</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="A5" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
+        <v>8597.0</v>
+      </c>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51">
+        <v>6164.0</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="A6" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
+        <v>9947.0</v>
+      </c>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51">
+        <v>5043.0</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="A7" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49">
+        <v>2058.0</v>
+      </c>
+      <c r="D7" s="50"/>
+      <c r="E7" s="51">
+        <v>4523.0</v>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="A8" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49">
+        <v>4397.0</v>
+      </c>
+      <c r="D8" s="50"/>
+      <c r="E8" s="51">
+        <v>3408.0</v>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="A9" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49">
+        <v>8746.0</v>
+      </c>
+      <c r="D9" s="50"/>
+      <c r="E9" s="51">
+        <v>8477.0</v>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="A10" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49">
+        <v>2928.0</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51">
+        <v>5463.0</v>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="A11" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49">
+        <v>8252.0</v>
+      </c>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51">
+        <v>1581.0</v>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="A12" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49">
+        <v>1583.0</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="51">
+        <v>1568.0</v>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="A13" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49">
+        <v>5086.0</v>
+      </c>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51">
+        <v>9640.0</v>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="A14" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49">
+        <v>4590.0</v>
+      </c>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51">
+        <v>5614.0</v>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="A15" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42">
-        <v>9201.0</v>
-      </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44">
-        <v>8835.0</v>
-      </c>
-    </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47">
-        <v>9634.0</v>
-      </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="24">
-        <v>8118.0</v>
-      </c>
-    </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47">
-        <v>6394.0</v>
-      </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="24">
-        <v>9756.0</v>
-      </c>
-    </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47">
-        <v>8597.0</v>
-      </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="24">
-        <v>6164.0</v>
-      </c>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47">
-        <v>9947.0</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="24">
-        <v>5043.0</v>
-      </c>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47">
-        <v>2058.0</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="24">
-        <v>4523.0</v>
-      </c>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="47">
-        <v>4397.0</v>
-      </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="24">
-        <v>3408.0</v>
-      </c>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47">
-        <v>8746.0</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="24">
-        <v>8477.0</v>
-      </c>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="47">
-        <v>2928.0</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="24">
-        <v>5463.0</v>
-      </c>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
-        <v>8252.0</v>
-      </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="24">
-        <v>1581.0</v>
-      </c>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47">
-        <v>1583.0</v>
-      </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="24">
-        <v>1568.0</v>
-      </c>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47">
-        <v>5086.0</v>
-      </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="24">
-        <v>9640.0</v>
-      </c>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51">
-        <v>4590.0</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32">
-        <v>5614.0</v>
-      </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="58">
+        <v>1070.0</v>
+      </c>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60">
+        <v>2535.0</v>
+      </c>
+    </row>
     <row r="16" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
@@ -9266,7 +9447,14 @@
     <row r="99" ht="13.5" customHeight="1"/>
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A6:B6"/>
@@ -9274,13 +9462,7 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="91">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -874,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -902,9 +902,6 @@
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -1005,7 +1002,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="35" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1018,39 +1015,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="39" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="40" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="41" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="42" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="43" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="43" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="44" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="44" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="42" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="43" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="42" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="43" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="44" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="44" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2484,7 +2479,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
@@ -3854,30 +3849,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K17:L17"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4974,7 +4969,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
@@ -6344,30 +6339,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="C1:D1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
     <mergeCell ref="K49:L49"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G49:H49"/>
     <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -6389,327 +6384,327 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="27" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="29" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="E9" s="29" t="s">
+      <c r="C9" s="24"/>
+      <c r="E9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="27" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="27" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="32" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="B15" s="35"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -6717,7 +6712,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="35"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6725,7 +6720,7 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="B17" s="35"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -6733,7 +6728,7 @@
       <c r="H17" s="8"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="B18" s="35"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -6741,7 +6736,7 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="B19" s="35"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6749,7 +6744,7 @@
       <c r="H19" s="8"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="B20" s="35"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -6757,7 +6752,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="35"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -6765,7 +6760,7 @@
       <c r="H21" s="8"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="35"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -6773,7 +6768,7 @@
       <c r="H22" s="8"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="B23" s="35"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -6781,7 +6776,7 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="B24" s="35"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -6789,7 +6784,7 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="35"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -6797,7 +6792,7 @@
       <c r="H25" s="8"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="35"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -6805,7 +6800,7 @@
       <c r="H26" s="8"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="B27" s="35"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -6813,7 +6808,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="B28" s="35"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -6821,7 +6816,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -6829,7 +6824,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="B30" s="35"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -6837,7 +6832,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -6845,7 +6840,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="B32" s="35"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -6853,7 +6848,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -6861,7 +6856,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="B34" s="35"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -6869,7 +6864,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
@@ -6877,7 +6872,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="B36" s="35"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
@@ -6885,7 +6880,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="35"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -6893,7 +6888,7 @@
       <c r="H37" s="8"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="35"/>
+      <c r="B38" s="34"/>
       <c r="C38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -6901,7 +6896,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="B39" s="35"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -6909,7 +6904,7 @@
       <c r="H39" s="8"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="B40" s="35"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -6917,7 +6912,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="B41" s="35"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -6925,7 +6920,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="B42" s="35"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -6933,7 +6928,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="B43" s="35"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -6941,7 +6936,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="B44" s="35"/>
+      <c r="B44" s="34"/>
       <c r="C44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -6949,7 +6944,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="B45" s="35"/>
+      <c r="B45" s="34"/>
       <c r="C45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -6957,7 +6952,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="B46" s="35"/>
+      <c r="B46" s="34"/>
       <c r="C46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -6965,7 +6960,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="35"/>
+      <c r="B47" s="34"/>
       <c r="C47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
@@ -6973,7 +6968,7 @@
       <c r="H47" s="8"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="35"/>
+      <c r="B48" s="34"/>
       <c r="C48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
@@ -6981,7 +6976,7 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="35"/>
+      <c r="B49" s="34"/>
       <c r="C49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
@@ -6989,7 +6984,7 @@
       <c r="H49" s="8"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="B50" s="35"/>
+      <c r="B50" s="34"/>
       <c r="C50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
@@ -6997,7 +6992,7 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="B51" s="35"/>
+      <c r="B51" s="34"/>
       <c r="C51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
@@ -7005,7 +7000,7 @@
       <c r="H51" s="8"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="35"/>
+      <c r="B52" s="34"/>
       <c r="C52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -7013,7 +7008,7 @@
       <c r="H52" s="8"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="35"/>
+      <c r="B53" s="34"/>
       <c r="C53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
@@ -7021,7 +7016,7 @@
       <c r="H53" s="8"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="B54" s="35"/>
+      <c r="B54" s="34"/>
       <c r="C54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -7029,7 +7024,7 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="B55" s="35"/>
+      <c r="B55" s="34"/>
       <c r="C55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -7037,7 +7032,7 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="B56" s="35"/>
+      <c r="B56" s="34"/>
       <c r="C56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
@@ -7045,7 +7040,7 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="B57" s="35"/>
+      <c r="B57" s="34"/>
       <c r="C57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -7053,7 +7048,7 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="B58" s="35"/>
+      <c r="B58" s="34"/>
       <c r="C58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -7061,7 +7056,7 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="B59" s="35"/>
+      <c r="B59" s="34"/>
       <c r="C59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -7069,7 +7064,7 @@
       <c r="H59" s="8"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="35"/>
+      <c r="B60" s="34"/>
       <c r="C60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -7077,7 +7072,7 @@
       <c r="H60" s="8"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="35"/>
+      <c r="B61" s="34"/>
       <c r="C61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -7085,7 +7080,7 @@
       <c r="H61" s="8"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="35"/>
+      <c r="B62" s="34"/>
       <c r="C62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -7093,7 +7088,7 @@
       <c r="H62" s="8"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="35"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -7101,7 +7096,7 @@
       <c r="H63" s="8"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="B64" s="35"/>
+      <c r="B64" s="34"/>
       <c r="C64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -7109,7 +7104,7 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="B65" s="35"/>
+      <c r="B65" s="34"/>
       <c r="C65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
@@ -7117,7 +7112,7 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="35"/>
+      <c r="B66" s="34"/>
       <c r="C66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -7125,7 +7120,7 @@
       <c r="H66" s="8"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="35"/>
+      <c r="B67" s="34"/>
       <c r="C67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -7133,7 +7128,7 @@
       <c r="H67" s="8"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="B68" s="35"/>
+      <c r="B68" s="34"/>
       <c r="C68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
@@ -7141,7 +7136,7 @@
       <c r="H68" s="8"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="B69" s="35"/>
+      <c r="B69" s="34"/>
       <c r="C69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
@@ -7149,7 +7144,7 @@
       <c r="H69" s="8"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="35"/>
+      <c r="B70" s="34"/>
       <c r="C70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
@@ -7157,7 +7152,7 @@
       <c r="H70" s="8"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="35"/>
+      <c r="B71" s="34"/>
       <c r="C71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
@@ -7165,7 +7160,7 @@
       <c r="H71" s="8"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="35"/>
+      <c r="B72" s="34"/>
       <c r="C72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
@@ -7173,7 +7168,7 @@
       <c r="H72" s="8"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="35"/>
+      <c r="B73" s="34"/>
       <c r="C73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
@@ -7181,7 +7176,7 @@
       <c r="H73" s="8"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="35"/>
+      <c r="B74" s="34"/>
       <c r="C74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -7189,7 +7184,7 @@
       <c r="H74" s="8"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="35"/>
+      <c r="B75" s="34"/>
       <c r="C75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
@@ -7197,7 +7192,7 @@
       <c r="H75" s="8"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="35"/>
+      <c r="B76" s="34"/>
       <c r="C76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -7205,7 +7200,7 @@
       <c r="H76" s="8"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="35"/>
+      <c r="B77" s="34"/>
       <c r="C77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -7213,7 +7208,7 @@
       <c r="H77" s="8"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="35"/>
+      <c r="B78" s="34"/>
       <c r="C78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -7221,7 +7216,7 @@
       <c r="H78" s="8"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="B79" s="35"/>
+      <c r="B79" s="34"/>
       <c r="C79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -7229,7 +7224,7 @@
       <c r="H79" s="8"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="B80" s="35"/>
+      <c r="B80" s="34"/>
       <c r="C80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
@@ -7237,7 +7232,7 @@
       <c r="H80" s="8"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="B81" s="35"/>
+      <c r="B81" s="34"/>
       <c r="C81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -7245,7 +7240,7 @@
       <c r="H81" s="8"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="B82" s="35"/>
+      <c r="B82" s="34"/>
       <c r="C82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -7253,7 +7248,7 @@
       <c r="H82" s="8"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="B83" s="35"/>
+      <c r="B83" s="34"/>
       <c r="C83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
@@ -7261,7 +7256,7 @@
       <c r="H83" s="8"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="B84" s="35"/>
+      <c r="B84" s="34"/>
       <c r="C84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
@@ -7269,7 +7264,7 @@
       <c r="H84" s="8"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="35"/>
+      <c r="B85" s="34"/>
       <c r="C85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -7277,7 +7272,7 @@
       <c r="H85" s="8"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="35"/>
+      <c r="B86" s="34"/>
       <c r="C86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
@@ -7285,7 +7280,7 @@
       <c r="H86" s="8"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="35"/>
+      <c r="B87" s="34"/>
       <c r="C87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -7293,7 +7288,7 @@
       <c r="H87" s="8"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="35"/>
+      <c r="B88" s="34"/>
       <c r="C88" s="8"/>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
@@ -7301,7 +7296,7 @@
       <c r="H88" s="8"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="B89" s="35"/>
+      <c r="B89" s="34"/>
       <c r="C89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -7309,7 +7304,7 @@
       <c r="H89" s="8"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="B90" s="35"/>
+      <c r="B90" s="34"/>
       <c r="C90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -7317,7 +7312,7 @@
       <c r="H90" s="8"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="35"/>
+      <c r="B91" s="34"/>
       <c r="C91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -7325,7 +7320,7 @@
       <c r="H91" s="8"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="35"/>
+      <c r="B92" s="34"/>
       <c r="C92" s="8"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -7333,7 +7328,7 @@
       <c r="H92" s="8"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="35"/>
+      <c r="B93" s="34"/>
       <c r="C93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
@@ -7341,7 +7336,7 @@
       <c r="H93" s="8"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="35"/>
+      <c r="B94" s="34"/>
       <c r="C94" s="8"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
@@ -7349,7 +7344,7 @@
       <c r="H94" s="8"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="B95" s="35"/>
+      <c r="B95" s="34"/>
       <c r="C95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -7357,7 +7352,7 @@
       <c r="H95" s="8"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="B96" s="35"/>
+      <c r="B96" s="34"/>
       <c r="C96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -7365,7 +7360,7 @@
       <c r="H96" s="8"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="B97" s="35"/>
+      <c r="B97" s="34"/>
       <c r="C97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
@@ -7373,7 +7368,7 @@
       <c r="H97" s="8"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="B98" s="35"/>
+      <c r="B98" s="34"/>
       <c r="C98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
@@ -7381,7 +7376,7 @@
       <c r="H98" s="8"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="B99" s="35"/>
+      <c r="B99" s="34"/>
       <c r="C99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -7389,7 +7384,7 @@
       <c r="H99" s="8"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="B100" s="35"/>
+      <c r="B100" s="34"/>
       <c r="C100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -7417,1399 +7412,1435 @@
   </cols>
   <sheetData>
     <row r="1" ht="53.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>1764.0</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46">
+      <c r="D2" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="45">
         <v>7120.0</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="49">
+      <c r="B3" s="47"/>
+      <c r="C3" s="48">
         <v>4089.0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51">
+      <c r="D3" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="50">
         <v>8058.0</v>
       </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48">
         <v>8216.0</v>
       </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51">
+      <c r="D4" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="50">
         <v>7792.0</v>
       </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>4504.0</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51">
+      <c r="D5" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="50">
         <v>7612.0</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>9390.0</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="51">
+      <c r="D6" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="50">
         <v>1324.0</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49">
+      <c r="B7" s="47"/>
+      <c r="C7" s="48">
         <v>6014.0</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="51">
+      <c r="D7" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="50">
         <v>8036.0</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="49">
+      <c r="B8" s="47"/>
+      <c r="C8" s="48">
         <v>2529.0</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="51">
+      <c r="D8" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="50">
         <v>6665.0</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49">
+      <c r="B9" s="47"/>
+      <c r="C9" s="48">
         <v>7609.0</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51">
+      <c r="D9" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="50">
         <v>8698.0</v>
       </c>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48">
         <v>6767.0</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51">
+      <c r="D10" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="50">
         <v>1648.0</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49">
+      <c r="B11" s="47"/>
+      <c r="C11" s="48">
         <v>2068.0</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51">
+      <c r="D11" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="50">
         <v>4954.0</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48">
         <v>4498.0</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51">
+      <c r="D12" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="50">
         <v>4994.0</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49">
+      <c r="B13" s="47"/>
+      <c r="C13" s="48">
         <v>6914.0</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51">
+      <c r="D13" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="50">
         <v>3787.0</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48">
         <v>1837.0</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+      <c r="D14" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="50">
         <v>5328.0</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="54">
+      <c r="B15" s="52"/>
+      <c r="C15" s="53">
         <v>2357.0</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56">
+      <c r="D15" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="55">
         <v>7799.0</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="41"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
+      <c r="A20" s="40"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="41"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
+      <c r="A33" s="40"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="41"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="41"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
+      <c r="A38" s="40"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="41"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="41"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="41"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="41"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="41"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
+      <c r="K44" s="40"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="41"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="41"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="41"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="A48" s="41"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="41"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="41"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="41"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="41"/>
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
+      <c r="A52" s="40"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="41"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
+      <c r="A53" s="40"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="41"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
+      <c r="A54" s="40"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="41"/>
-      <c r="B55" s="41"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="A56" s="41"/>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
+      <c r="A56" s="40"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="A57" s="41"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
+      <c r="A57" s="40"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="41"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
+      <c r="A58" s="40"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="41"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
+      <c r="A59" s="40"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="41"/>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
+      <c r="A60" s="40"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="A61" s="41"/>
-      <c r="B61" s="41"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="41"/>
-      <c r="J61" s="41"/>
-      <c r="K61" s="41"/>
+      <c r="A61" s="40"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="41"/>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
+      <c r="A62" s="40"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="A63" s="41"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
+      <c r="A63" s="40"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="40"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="41"/>
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
+      <c r="A64" s="40"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="41"/>
-      <c r="B65" s="41"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
+      <c r="A65" s="40"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="40"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="41"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
+      <c r="A66" s="40"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="41"/>
-      <c r="B67" s="41"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="40"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="41"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="41"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="41"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
+      <c r="A68" s="40"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="40"/>
+      <c r="I68" s="40"/>
+      <c r="J68" s="40"/>
+      <c r="K68" s="40"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="41"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
+      <c r="A69" s="40"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="40"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="A70" s="41"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="41"/>
-      <c r="K70" s="41"/>
+      <c r="A70" s="40"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="A71" s="41"/>
-      <c r="B71" s="41"/>
-      <c r="C71" s="41"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="41"/>
-      <c r="I71" s="41"/>
-      <c r="J71" s="41"/>
-      <c r="K71" s="41"/>
+      <c r="A71" s="40"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="41"/>
-      <c r="B72" s="41"/>
-      <c r="C72" s="41"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
+      <c r="A72" s="40"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="40"/>
+      <c r="K72" s="40"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="A73" s="41"/>
-      <c r="B73" s="41"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
+      <c r="A73" s="40"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="A74" s="41"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="41"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="41"/>
-      <c r="K74" s="41"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
+      <c r="J74" s="40"/>
+      <c r="K74" s="40"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="A75" s="41"/>
-      <c r="B75" s="41"/>
-      <c r="C75" s="41"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="41"/>
-      <c r="K75" s="41"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="A76" s="41"/>
-      <c r="B76" s="41"/>
-      <c r="C76" s="41"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="41"/>
-      <c r="I76" s="41"/>
-      <c r="J76" s="41"/>
-      <c r="K76" s="41"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="41"/>
-      <c r="B77" s="41"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="41"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="41"/>
-      <c r="H77" s="41"/>
-      <c r="I77" s="41"/>
-      <c r="J77" s="41"/>
-      <c r="K77" s="41"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="40"/>
+      <c r="J77" s="40"/>
+      <c r="K77" s="40"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="A78" s="41"/>
-      <c r="B78" s="41"/>
-      <c r="C78" s="41"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="41"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41"/>
-      <c r="J78" s="41"/>
-      <c r="K78" s="41"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
+      <c r="J78" s="40"/>
+      <c r="K78" s="40"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="A79" s="41"/>
-      <c r="B79" s="41"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="41"/>
-      <c r="J79" s="41"/>
-      <c r="K79" s="41"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="40"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="A80" s="41"/>
-      <c r="B80" s="41"/>
-      <c r="C80" s="41"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="41"/>
-      <c r="K80" s="41"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="40"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="A81" s="41"/>
-      <c r="B81" s="41"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="41"/>
-      <c r="J81" s="41"/>
-      <c r="K81" s="41"/>
+      <c r="A81" s="40"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="40"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="41"/>
-      <c r="B82" s="41"/>
-      <c r="C82" s="41"/>
-      <c r="D82" s="41"/>
-      <c r="E82" s="41"/>
-      <c r="F82" s="41"/>
-      <c r="G82" s="41"/>
-      <c r="H82" s="41"/>
-      <c r="I82" s="41"/>
-      <c r="J82" s="41"/>
-      <c r="K82" s="41"/>
+      <c r="A82" s="40"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="40"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="41"/>
-      <c r="B83" s="41"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="41"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41"/>
-      <c r="I83" s="41"/>
-      <c r="J83" s="41"/>
-      <c r="K83" s="41"/>
+      <c r="A83" s="40"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="40"/>
+      <c r="K83" s="40"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="41"/>
-      <c r="B84" s="41"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41"/>
-      <c r="I84" s="41"/>
-      <c r="J84" s="41"/>
-      <c r="K84" s="41"/>
+      <c r="A84" s="40"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="40"/>
+      <c r="J84" s="40"/>
+      <c r="K84" s="40"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="A85" s="41"/>
-      <c r="B85" s="41"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
-      <c r="J85" s="41"/>
-      <c r="K85" s="41"/>
+      <c r="A85" s="40"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="40"/>
+      <c r="K85" s="40"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="A86" s="41"/>
-      <c r="B86" s="41"/>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="41"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41"/>
-      <c r="I86" s="41"/>
-      <c r="J86" s="41"/>
-      <c r="K86" s="41"/>
+      <c r="A86" s="40"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="40"/>
+      <c r="J86" s="40"/>
+      <c r="K86" s="40"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="41"/>
-      <c r="B87" s="41"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="41"/>
-      <c r="J87" s="41"/>
-      <c r="K87" s="41"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="41"/>
-      <c r="B88" s="41"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="41"/>
-      <c r="I88" s="41"/>
-      <c r="J88" s="41"/>
-      <c r="K88" s="41"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
+      <c r="J88" s="40"/>
+      <c r="K88" s="40"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="41"/>
-      <c r="B89" s="41"/>
-      <c r="C89" s="41"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="41"/>
-      <c r="I89" s="41"/>
-      <c r="J89" s="41"/>
-      <c r="K89" s="41"/>
+      <c r="A89" s="40"/>
+      <c r="B89" s="40"/>
+      <c r="C89" s="40"/>
+      <c r="D89" s="40"/>
+      <c r="E89" s="40"/>
+      <c r="F89" s="40"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="40"/>
+      <c r="I89" s="40"/>
+      <c r="J89" s="40"/>
+      <c r="K89" s="40"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="41"/>
-      <c r="B90" s="41"/>
-      <c r="C90" s="41"/>
-      <c r="D90" s="41"/>
-      <c r="E90" s="41"/>
-      <c r="F90" s="41"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="41"/>
-      <c r="I90" s="41"/>
-      <c r="J90" s="41"/>
-      <c r="K90" s="41"/>
+      <c r="A90" s="40"/>
+      <c r="B90" s="40"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="40"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="40"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="40"/>
+      <c r="J90" s="40"/>
+      <c r="K90" s="40"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="A91" s="41"/>
-      <c r="B91" s="41"/>
-      <c r="C91" s="41"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="41"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="41"/>
-      <c r="I91" s="41"/>
-      <c r="J91" s="41"/>
-      <c r="K91" s="41"/>
+      <c r="A91" s="40"/>
+      <c r="B91" s="40"/>
+      <c r="C91" s="40"/>
+      <c r="D91" s="40"/>
+      <c r="E91" s="40"/>
+      <c r="F91" s="40"/>
+      <c r="G91" s="40"/>
+      <c r="H91" s="40"/>
+      <c r="I91" s="40"/>
+      <c r="J91" s="40"/>
+      <c r="K91" s="40"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="A92" s="41"/>
-      <c r="B92" s="41"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="41"/>
-      <c r="F92" s="41"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="41"/>
-      <c r="I92" s="41"/>
-      <c r="J92" s="41"/>
-      <c r="K92" s="41"/>
+      <c r="A92" s="40"/>
+      <c r="B92" s="40"/>
+      <c r="C92" s="40"/>
+      <c r="D92" s="40"/>
+      <c r="E92" s="40"/>
+      <c r="F92" s="40"/>
+      <c r="G92" s="40"/>
+      <c r="H92" s="40"/>
+      <c r="I92" s="40"/>
+      <c r="J92" s="40"/>
+      <c r="K92" s="40"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="41"/>
-      <c r="B93" s="41"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="41"/>
-      <c r="I93" s="41"/>
-      <c r="J93" s="41"/>
-      <c r="K93" s="41"/>
+      <c r="A93" s="40"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="40"/>
+      <c r="I93" s="40"/>
+      <c r="J93" s="40"/>
+      <c r="K93" s="40"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="A94" s="41"/>
-      <c r="B94" s="41"/>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="41"/>
-      <c r="I94" s="41"/>
-      <c r="J94" s="41"/>
-      <c r="K94" s="41"/>
+      <c r="A94" s="40"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="40"/>
+      <c r="D94" s="40"/>
+      <c r="E94" s="40"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="40"/>
+      <c r="I94" s="40"/>
+      <c r="J94" s="40"/>
+      <c r="K94" s="40"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="41"/>
-      <c r="B95" s="41"/>
-      <c r="C95" s="41"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="41"/>
-      <c r="I95" s="41"/>
-      <c r="J95" s="41"/>
-      <c r="K95" s="41"/>
+      <c r="A95" s="40"/>
+      <c r="B95" s="40"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="40"/>
+      <c r="E95" s="40"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="40"/>
+      <c r="H95" s="40"/>
+      <c r="I95" s="40"/>
+      <c r="J95" s="40"/>
+      <c r="K95" s="40"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="41"/>
-      <c r="B96" s="41"/>
-      <c r="C96" s="41"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="41"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="41"/>
-      <c r="I96" s="41"/>
-      <c r="J96" s="41"/>
-      <c r="K96" s="41"/>
+      <c r="A96" s="40"/>
+      <c r="B96" s="40"/>
+      <c r="C96" s="40"/>
+      <c r="D96" s="40"/>
+      <c r="E96" s="40"/>
+      <c r="F96" s="40"/>
+      <c r="G96" s="40"/>
+      <c r="H96" s="40"/>
+      <c r="I96" s="40"/>
+      <c r="J96" s="40"/>
+      <c r="K96" s="40"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="A97" s="41"/>
-      <c r="B97" s="41"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="41"/>
-      <c r="I97" s="41"/>
-      <c r="J97" s="41"/>
-      <c r="K97" s="41"/>
+      <c r="A97" s="40"/>
+      <c r="B97" s="40"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="40"/>
+      <c r="F97" s="40"/>
+      <c r="G97" s="40"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="40"/>
+      <c r="J97" s="40"/>
+      <c r="K97" s="40"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="A98" s="41"/>
-      <c r="B98" s="41"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="41"/>
-      <c r="I98" s="41"/>
-      <c r="J98" s="41"/>
-      <c r="K98" s="41"/>
+      <c r="A98" s="40"/>
+      <c r="B98" s="40"/>
+      <c r="C98" s="40"/>
+      <c r="D98" s="40"/>
+      <c r="E98" s="40"/>
+      <c r="F98" s="40"/>
+      <c r="G98" s="40"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="40"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="40"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="41"/>
-      <c r="B99" s="41"/>
-      <c r="C99" s="41"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="41"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="41"/>
-      <c r="H99" s="41"/>
-      <c r="I99" s="41"/>
-      <c r="J99" s="41"/>
-      <c r="K99" s="41"/>
+      <c r="A99" s="40"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="40"/>
+      <c r="D99" s="40"/>
+      <c r="E99" s="40"/>
+      <c r="F99" s="40"/>
+      <c r="G99" s="40"/>
+      <c r="H99" s="40"/>
+      <c r="I99" s="40"/>
+      <c r="J99" s="40"/>
+      <c r="K99" s="40"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="41"/>
-      <c r="B100" s="41"/>
-      <c r="C100" s="41"/>
-      <c r="D100" s="41"/>
-      <c r="E100" s="41"/>
-      <c r="F100" s="41"/>
-      <c r="G100" s="41"/>
-      <c r="H100" s="41"/>
-      <c r="I100" s="41"/>
-      <c r="J100" s="41"/>
-      <c r="K100" s="41"/>
+      <c r="A100" s="40"/>
+      <c r="B100" s="40"/>
+      <c r="C100" s="40"/>
+      <c r="D100" s="40"/>
+      <c r="E100" s="40"/>
+      <c r="F100" s="40"/>
+      <c r="G100" s="40"/>
+      <c r="H100" s="40"/>
+      <c r="I100" s="40"/>
+      <c r="J100" s="40"/>
+      <c r="K100" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -8817,14 +8848,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -8846,199 +8869,227 @@
   </cols>
   <sheetData>
     <row r="1" ht="39.75" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>7928.0</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46">
+      <c r="D2" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="45">
         <v>8131.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="49">
+      <c r="B3" s="47"/>
+      <c r="C3" s="48">
         <v>4675.0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51">
+      <c r="D3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="50">
         <v>5063.0</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48">
         <v>6301.0</v>
       </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51">
+      <c r="D4" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="50">
         <v>2537.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>1020.0</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51">
+      <c r="D5" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="50">
         <v>8684.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>1330.0</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="51">
+      <c r="D6" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="50">
         <v>6409.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49">
+      <c r="B7" s="47"/>
+      <c r="C7" s="48">
         <v>9856.0</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="51">
+      <c r="D7" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="50">
         <v>5988.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="49">
+      <c r="B8" s="47"/>
+      <c r="C8" s="48">
         <v>5817.0</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="51">
+      <c r="D8" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="50">
         <v>2768.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49">
+      <c r="B9" s="47"/>
+      <c r="C9" s="48">
         <v>1116.0</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51">
+      <c r="D9" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="50">
         <v>9182.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48">
         <v>5806.0</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51">
+      <c r="D10" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="50">
         <v>6217.0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49">
+      <c r="B11" s="47"/>
+      <c r="C11" s="48">
         <v>6523.0</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51">
+      <c r="D11" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="50">
         <v>7401.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48">
         <v>8392.0</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51">
+      <c r="D12" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="50">
         <v>8868.0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49">
+      <c r="B13" s="47"/>
+      <c r="C13" s="48">
         <v>3739.0</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51">
+      <c r="D13" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="50">
         <v>66515.0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48">
         <v>3945.0</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+      <c r="D14" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="50">
         <v>9707.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="58">
+      <c r="B15" s="52"/>
+      <c r="C15" s="57">
         <v>4433.0</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="60">
+      <c r="D15" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="59">
         <v>1033.0</v>
       </c>
     </row>
@@ -9129,6 +9180,14 @@
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -9136,14 +9195,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -9165,199 +9216,227 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>9201.0</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46">
+      <c r="D2" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="45">
         <v>8835.0</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="49">
+      <c r="B3" s="47"/>
+      <c r="C3" s="48">
         <v>9634.0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51">
+      <c r="D3" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="50">
         <v>8118.0</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48">
         <v>6394.0</v>
       </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51">
+      <c r="D4" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="50">
         <v>9756.0</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48">
         <v>8597.0</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51">
+      <c r="D5" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="50">
         <v>6164.0</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48">
         <v>9947.0</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="51">
+      <c r="D6" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="50">
         <v>5043.0</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49">
+      <c r="B7" s="47"/>
+      <c r="C7" s="48">
         <v>2058.0</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="51">
+      <c r="D7" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="50">
         <v>4523.0</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="49">
+      <c r="B8" s="47"/>
+      <c r="C8" s="48">
         <v>4397.0</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="51">
+      <c r="D8" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="50">
         <v>3408.0</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49">
+      <c r="B9" s="47"/>
+      <c r="C9" s="48">
         <v>8746.0</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51">
+      <c r="D9" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="50">
         <v>8477.0</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48">
         <v>2928.0</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51">
+      <c r="D10" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="50">
         <v>5463.0</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49">
+      <c r="B11" s="47"/>
+      <c r="C11" s="48">
         <v>8252.0</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="51">
+      <c r="D11" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="50">
         <v>1581.0</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48">
         <v>1583.0</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51">
+      <c r="D12" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="50">
         <v>1568.0</v>
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49">
+      <c r="B13" s="47"/>
+      <c r="C13" s="48">
         <v>5086.0</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51">
+      <c r="D13" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="50">
         <v>9640.0</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48">
         <v>4590.0</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+      <c r="D14" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="50">
         <v>5614.0</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="58">
+      <c r="B15" s="52"/>
+      <c r="C15" s="57">
         <v>1070.0</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="60">
+      <c r="D15" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="59">
         <v>2535.0</v>
       </c>
     </row>
@@ -9448,6 +9527,14 @@
     <row r="100" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A5:B5"/>
@@ -9455,14 +9542,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36E7235-A4A8-4265-AE3B-29C85283CC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014BB057-FD51-4128-8C6C-845DF7529113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EQUIPOS QR" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="89">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -367,7 +367,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -1350,11 +1350,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1524,6 +1608,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1553,59 +1682,56 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1945,30 +2071,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="70" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="71"/>
-      <c r="E1" s="70" t="s">
+      <c r="D1" s="64"/>
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="70" t="s">
+      <c r="F1" s="64"/>
+      <c r="G1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="70" t="s">
+      <c r="H1" s="64"/>
+      <c r="I1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="70" t="s">
+      <c r="J1" s="64"/>
+      <c r="K1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="71"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2481,30 +2607,30 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="70" t="s">
+      <c r="B17" s="64"/>
+      <c r="C17" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="70" t="s">
+      <c r="D17" s="64"/>
+      <c r="E17" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="71"/>
-      <c r="G17" s="70" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="70" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="71"/>
-      <c r="K17" s="70" t="s">
+      <c r="J17" s="64"/>
+      <c r="K17" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="71"/>
+      <c r="L17" s="64"/>
     </row>
     <row r="18" spans="1:12" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
@@ -3018,30 +3144,30 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="70" t="s">
+      <c r="B33" s="64"/>
+      <c r="C33" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="72"/>
-      <c r="E33" s="73" t="s">
+      <c r="D33" s="67"/>
+      <c r="E33" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="74"/>
-      <c r="G33" s="70" t="s">
+      <c r="F33" s="66"/>
+      <c r="G33" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="71"/>
-      <c r="I33" s="70" t="s">
+      <c r="H33" s="64"/>
+      <c r="I33" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="71"/>
-      <c r="K33" s="70" t="s">
+      <c r="J33" s="64"/>
+      <c r="K33" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="71"/>
+      <c r="L33" s="64"/>
     </row>
     <row r="34" spans="1:12" ht="13.5" customHeight="1">
       <c r="A34" s="1" t="s">
@@ -3554,30 +3680,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="70" t="s">
+      <c r="B49" s="64"/>
+      <c r="C49" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="70" t="s">
+      <c r="D49" s="64"/>
+      <c r="E49" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="70" t="s">
+      <c r="F49" s="64"/>
+      <c r="G49" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="71"/>
-      <c r="I49" s="70" t="s">
+      <c r="H49" s="64"/>
+      <c r="I49" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="71"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="64"/>
+      <c r="K49" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="71"/>
+      <c r="L49" s="64"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -4392,20 +4518,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
@@ -4416,6 +4528,20 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -4434,30 +4560,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="70" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="71"/>
-      <c r="E1" s="70" t="s">
+      <c r="D1" s="64"/>
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="70" t="s">
+      <c r="F1" s="64"/>
+      <c r="G1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="70" t="s">
+      <c r="H1" s="64"/>
+      <c r="I1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="70" t="s">
+      <c r="J1" s="64"/>
+      <c r="K1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="71"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -4970,30 +5096,30 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="70" t="s">
+      <c r="B17" s="64"/>
+      <c r="C17" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="70" t="s">
+      <c r="D17" s="64"/>
+      <c r="E17" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="71"/>
-      <c r="G17" s="70" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="70" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="71"/>
-      <c r="K17" s="70" t="s">
+      <c r="J17" s="64"/>
+      <c r="K17" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="71"/>
+      <c r="L17" s="64"/>
     </row>
     <row r="18" spans="1:12" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
@@ -5507,30 +5633,30 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="70" t="s">
+      <c r="B33" s="64"/>
+      <c r="C33" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="72"/>
-      <c r="E33" s="73" t="s">
+      <c r="D33" s="67"/>
+      <c r="E33" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="74"/>
-      <c r="G33" s="70" t="s">
+      <c r="F33" s="66"/>
+      <c r="G33" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="71"/>
-      <c r="I33" s="70" t="s">
+      <c r="H33" s="64"/>
+      <c r="I33" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="71"/>
-      <c r="K33" s="70" t="s">
+      <c r="J33" s="64"/>
+      <c r="K33" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="71"/>
+      <c r="L33" s="64"/>
     </row>
     <row r="34" spans="1:12" ht="13.5" customHeight="1">
       <c r="A34" s="1" t="s">
@@ -6043,30 +6169,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="70" t="s">
+      <c r="B49" s="64"/>
+      <c r="C49" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="70" t="s">
+      <c r="D49" s="64"/>
+      <c r="E49" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="70" t="s">
+      <c r="F49" s="64"/>
+      <c r="G49" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="71"/>
-      <c r="I49" s="70" t="s">
+      <c r="H49" s="64"/>
+      <c r="I49" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="71"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="64"/>
+      <c r="K49" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="71"/>
+      <c r="L49" s="64"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -6881,12 +7007,13 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="I1:J1"/>
@@ -6898,13 +7025,12 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -6923,38 +7049,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
+      <c r="D1" s="75"/>
+      <c r="E1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="91"/>
-      <c r="G1" s="92" t="s">
+      <c r="F1" s="75"/>
+      <c r="G1" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="91"/>
-      <c r="I1" s="92" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="91"/>
-      <c r="K1" s="92" t="s">
+      <c r="J1" s="75"/>
+      <c r="K1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="91"/>
-      <c r="M1" s="92" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="93"/>
-      <c r="O1" s="90" t="s">
+      <c r="N1" s="72"/>
+      <c r="O1" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="94"/>
+      <c r="P1" s="74"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -7623,34 +7749,34 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="70" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="70" t="s">
+      <c r="D17" s="69"/>
+      <c r="E17" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="71"/>
-      <c r="G17" s="70" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="70" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="71"/>
-      <c r="K17" s="70" t="s">
+      <c r="J17" s="64"/>
+      <c r="K17" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="72"/>
-      <c r="M17" s="73" t="s">
+      <c r="L17" s="67"/>
+      <c r="M17" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="74"/>
+      <c r="N17" s="66"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
@@ -8243,38 +8369,38 @@
     </row>
     <row r="48" ht="15.75" thickBot="1"/>
     <row r="49" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="87"/>
-      <c r="C49" s="70" t="s">
+      <c r="B49" s="69"/>
+      <c r="C49" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="87"/>
-      <c r="E49" s="70" t="s">
+      <c r="D49" s="69"/>
+      <c r="E49" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="87"/>
-      <c r="G49" s="70" t="s">
+      <c r="F49" s="69"/>
+      <c r="G49" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="87"/>
-      <c r="I49" s="70" t="s">
+      <c r="H49" s="69"/>
+      <c r="I49" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="87"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="69"/>
+      <c r="K49" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="87"/>
-      <c r="M49" s="70" t="s">
+      <c r="L49" s="69"/>
+      <c r="M49" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="N49" s="72"/>
-      <c r="O49" s="73" t="s">
+      <c r="N49" s="67"/>
+      <c r="O49" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="74"/>
+      <c r="P49" s="66"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
@@ -8928,34 +9054,34 @@
     </row>
     <row r="64" spans="1:16" ht="15.75" thickBot="1"/>
     <row r="65" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A65" s="70" t="s">
+      <c r="A65" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="87"/>
-      <c r="C65" s="70" t="s">
+      <c r="B65" s="69"/>
+      <c r="C65" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="87"/>
-      <c r="E65" s="70" t="s">
+      <c r="D65" s="69"/>
+      <c r="E65" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F65" s="87"/>
-      <c r="G65" s="70" t="s">
+      <c r="F65" s="69"/>
+      <c r="G65" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="87"/>
-      <c r="I65" s="70" t="s">
+      <c r="H65" s="69"/>
+      <c r="I65" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J65" s="87"/>
-      <c r="K65" s="70" t="s">
+      <c r="J65" s="69"/>
+      <c r="K65" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="L65" s="88"/>
-      <c r="M65" s="73" t="s">
+      <c r="L65" s="70"/>
+      <c r="M65" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="N65" s="89"/>
+      <c r="N65" s="68"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="1" t="s">
@@ -9548,26 +9674,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="E17:F17"/>
@@ -9578,6 +9684,26 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="M49:N49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -9933,7 +10059,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="2:8" ht="13.5" customHeight="1">
+    <row r="17" spans="1:8" ht="13.5" customHeight="1">
       <c r="B17" s="32"/>
       <c r="C17" s="6"/>
       <c r="E17" s="6"/>
@@ -9941,7 +10067,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="2:8" ht="13.5" customHeight="1">
+    <row r="18" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
       <c r="B18" s="32"/>
       <c r="C18" s="6"/>
       <c r="E18" s="6"/>
@@ -9949,372 +10075,526 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B19" s="32"/>
-      <c r="C19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+    <row r="19" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A19" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>49</v>
+      </c>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B20" s="32"/>
-      <c r="C20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
+    <row r="20" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A20" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="103" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="104" t="s">
+        <v>57</v>
+      </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B21" s="32"/>
-      <c r="C21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+    <row r="21" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A21" s="96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="97" t="s">
+        <v>59</v>
+      </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B22" s="32"/>
-      <c r="C22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+    <row r="22" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A22" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="97" t="s">
+        <v>61</v>
+      </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B23" s="32"/>
-      <c r="C23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+    <row r="23" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A23" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="97" t="s">
+        <v>55</v>
+      </c>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B24" s="32"/>
-      <c r="C24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A24" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>65</v>
+      </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B25" s="32"/>
-      <c r="C25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+    <row r="25" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A25" s="96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>67</v>
+      </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B26" s="32"/>
-      <c r="C26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="26" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A26" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="97"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B27" s="32"/>
-      <c r="C27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="27" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A27" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>63</v>
+      </c>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B28" s="32"/>
-      <c r="C28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="28" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A28" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="97" t="s">
+        <v>72</v>
+      </c>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B29" s="32"/>
-      <c r="C29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+    <row r="29" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A29" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="97" t="s">
+        <v>74</v>
+      </c>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B30" s="32"/>
-      <c r="C30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+    <row r="30" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A30" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="97" t="s">
+        <v>76</v>
+      </c>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B31" s="32"/>
-      <c r="C31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+    <row r="31" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A31" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="97" t="s">
+        <v>70</v>
+      </c>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B32" s="32"/>
-      <c r="C32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+    <row r="32" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A32" s="99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="101" t="s">
+        <v>78</v>
+      </c>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B33" s="32"/>
+    <row r="33" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
       <c r="C33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B34" s="32"/>
+    <row r="34" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B35" s="32"/>
-      <c r="C35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+    <row r="35" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A35" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="107" t="s">
+        <v>49</v>
+      </c>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B36" s="32"/>
-      <c r="C36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+    <row r="36" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A36" s="102" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="104" t="s">
+        <v>59</v>
+      </c>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B37" s="32"/>
-      <c r="C37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+    <row r="37" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A37" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="97" t="s">
+        <v>61</v>
+      </c>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B38" s="32"/>
-      <c r="C38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
+    <row r="38" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A38" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="97" t="s">
+        <v>55</v>
+      </c>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B39" s="32"/>
-      <c r="C39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+    <row r="39" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A39" s="96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="97" t="s">
+        <v>57</v>
+      </c>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B40" s="32"/>
-      <c r="C40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
+    <row r="40" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A40" s="96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="97" t="s">
+        <v>67</v>
+      </c>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B41" s="32"/>
-      <c r="C41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+    <row r="41" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A41" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="97"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B42" s="32"/>
-      <c r="C42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+    <row r="42" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A42" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="97" t="s">
+        <v>63</v>
+      </c>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B43" s="32"/>
-      <c r="C43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+    <row r="43" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A43" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>65</v>
+      </c>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B44" s="32"/>
-      <c r="C44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+    <row r="44" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A44" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="97" t="s">
+        <v>74</v>
+      </c>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B45" s="32"/>
-      <c r="C45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
+    <row r="45" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A45" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="97" t="s">
+        <v>76</v>
+      </c>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B46" s="32"/>
-      <c r="C46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+    <row r="46" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A46" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="97" t="s">
+        <v>70</v>
+      </c>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B47" s="32"/>
-      <c r="C47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
+    <row r="47" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A47" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="97" t="s">
+        <v>72</v>
+      </c>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B48" s="32"/>
-      <c r="C48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
+    <row r="48" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A48" s="99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="101" t="s">
+        <v>78</v>
+      </c>
       <c r="H48" s="6"/>
     </row>
-    <row r="49" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B49" s="32"/>
+    <row r="49" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
       <c r="C49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
       <c r="H49" s="6"/>
     </row>
-    <row r="50" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B50" s="32"/>
+    <row r="50" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
       <c r="C50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
       <c r="H50" s="6"/>
     </row>
-    <row r="51" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B51" s="32"/>
-      <c r="C51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
+    <row r="51" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A51" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="107" t="s">
+        <v>49</v>
+      </c>
       <c r="H51" s="6"/>
     </row>
-    <row r="52" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B52" s="32"/>
-      <c r="C52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
+    <row r="52" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A52" s="108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="104" t="s">
+        <v>61</v>
+      </c>
       <c r="H52" s="6"/>
     </row>
-    <row r="53" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B53" s="32"/>
-      <c r="C53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
+    <row r="53" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A53" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="97" t="s">
+        <v>55</v>
+      </c>
       <c r="H53" s="6"/>
     </row>
-    <row r="54" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B54" s="32"/>
-      <c r="C54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
+    <row r="54" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A54" s="96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="97" t="s">
+        <v>57</v>
+      </c>
       <c r="H54" s="6"/>
     </row>
-    <row r="55" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B55" s="32"/>
-      <c r="C55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
+    <row r="55" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A55" s="96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="97" t="s">
+        <v>59</v>
+      </c>
       <c r="H55" s="6"/>
     </row>
-    <row r="56" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B56" s="32"/>
-      <c r="C56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
+    <row r="56" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A56" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="97"/>
       <c r="H56" s="6"/>
     </row>
-    <row r="57" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B57" s="32"/>
-      <c r="C57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
+    <row r="57" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A57" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="97" t="s">
+        <v>63</v>
+      </c>
       <c r="H57" s="6"/>
     </row>
-    <row r="58" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B58" s="32"/>
-      <c r="C58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
+    <row r="58" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A58" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="97" t="s">
+        <v>65</v>
+      </c>
       <c r="H58" s="6"/>
     </row>
-    <row r="59" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B59" s="32"/>
-      <c r="C59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
+    <row r="59" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A59" s="96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="97" t="s">
+        <v>67</v>
+      </c>
       <c r="H59" s="6"/>
     </row>
-    <row r="60" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B60" s="32"/>
-      <c r="C60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
+    <row r="60" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A60" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="97" t="s">
+        <v>76</v>
+      </c>
       <c r="H60" s="6"/>
     </row>
-    <row r="61" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B61" s="32"/>
-      <c r="C61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
+    <row r="61" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A61" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="97" t="s">
+        <v>70</v>
+      </c>
       <c r="H61" s="6"/>
     </row>
-    <row r="62" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B62" s="32"/>
-      <c r="C62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
+    <row r="62" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A62" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="97" t="s">
+        <v>72</v>
+      </c>
       <c r="H62" s="6"/>
     </row>
-    <row r="63" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B63" s="32"/>
-      <c r="C63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+    <row r="63" spans="1:8" ht="13.5" customHeight="1">
+      <c r="A63" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="97" t="s">
+        <v>74</v>
+      </c>
       <c r="H63" s="6"/>
     </row>
-    <row r="64" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B64" s="32"/>
-      <c r="C64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
+    <row r="64" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A64" s="99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="101" t="s">
+        <v>78</v>
+      </c>
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="2:8" ht="13.5" customHeight="1">
@@ -10607,7 +10887,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup scale="96" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="71" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10625,10 +10905,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="81"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -10646,10 +10926,10 @@
       <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="83"/>
       <c r="C2" s="39">
         <v>1764</v>
       </c>
@@ -10667,10 +10947,10 @@
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="42">
         <v>4089</v>
       </c>
@@ -10688,10 +10968,10 @@
       <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="42">
         <v>8216</v>
       </c>
@@ -10709,10 +10989,10 @@
       <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="42">
         <v>4504</v>
       </c>
@@ -10730,10 +11010,10 @@
       <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="42">
         <v>9390</v>
       </c>
@@ -10751,10 +11031,10 @@
       <c r="K6" s="33"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="42">
         <v>6014</v>
       </c>
@@ -10772,10 +11052,10 @@
       <c r="K7" s="33"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="42">
         <v>2529</v>
       </c>
@@ -10793,10 +11073,10 @@
       <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="79"/>
       <c r="C9" s="42">
         <v>7609</v>
       </c>
@@ -10814,10 +11094,10 @@
       <c r="K9" s="33"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="42">
         <v>6767</v>
       </c>
@@ -10835,10 +11115,10 @@
       <c r="K10" s="33"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="79"/>
       <c r="C11" s="42">
         <v>2068</v>
       </c>
@@ -10856,10 +11136,10 @@
       <c r="K11" s="33"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="42">
         <v>4498</v>
       </c>
@@ -10877,10 +11157,10 @@
       <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="42">
         <v>6914</v>
       </c>
@@ -10898,10 +11178,10 @@
       <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="67"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="44">
         <v>1837</v>
       </c>
@@ -10919,10 +11199,10 @@
       <c r="K14" s="33"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="46">
         <v>2357</v>
       </c>
@@ -10940,10 +11220,10 @@
       <c r="K15" s="33"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="58"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="48">
         <v>4593</v>
       </c>
@@ -11255,10 +11535,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="81"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -11270,10 +11550,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="83"/>
       <c r="C2" s="39">
         <v>7928</v>
       </c>
@@ -11285,10 +11565,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="42">
         <v>4675</v>
       </c>
@@ -11300,10 +11580,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="42">
         <v>6301</v>
       </c>
@@ -11315,10 +11595,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="42">
         <v>1020</v>
       </c>
@@ -11330,10 +11610,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="42">
         <v>1330</v>
       </c>
@@ -11345,10 +11625,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="42">
         <v>9856</v>
       </c>
@@ -11360,10 +11640,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="42">
         <v>5817</v>
       </c>
@@ -11375,10 +11655,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="79"/>
       <c r="C9" s="42">
         <v>1116</v>
       </c>
@@ -11390,10 +11670,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="42">
         <v>5806</v>
       </c>
@@ -11405,10 +11685,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="79"/>
       <c r="C11" s="42">
         <v>6523</v>
       </c>
@@ -11420,10 +11700,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="42">
         <v>8392</v>
       </c>
@@ -11435,10 +11715,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="42">
         <v>3739</v>
       </c>
@@ -11450,10 +11730,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="67"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="44">
         <v>3945</v>
       </c>
@@ -11465,10 +11745,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="46">
         <v>4433</v>
       </c>
@@ -11480,10 +11760,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="58"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="48">
         <v>1908</v>
       </c>
@@ -11613,10 +11893,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="81"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -11628,10 +11908,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="83"/>
       <c r="C2" s="39">
         <v>9201</v>
       </c>
@@ -11643,10 +11923,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="42">
         <v>9634</v>
       </c>
@@ -11658,10 +11938,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="42">
         <v>6394</v>
       </c>
@@ -11673,10 +11953,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="42">
         <v>8597</v>
       </c>
@@ -11688,10 +11968,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="42">
         <v>9947</v>
       </c>
@@ -11703,10 +11983,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="42">
         <v>2058</v>
       </c>
@@ -11718,10 +11998,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="60"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="42">
         <v>4397</v>
       </c>
@@ -11733,10 +12013,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="79"/>
       <c r="C9" s="42">
         <v>8746</v>
       </c>
@@ -11748,10 +12028,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="60"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="42">
         <v>2928</v>
       </c>
@@ -11763,10 +12043,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="79"/>
       <c r="C11" s="42">
         <v>8252</v>
       </c>
@@ -11778,10 +12058,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="42">
         <v>1583</v>
       </c>
@@ -11793,10 +12073,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="42">
         <v>5086</v>
       </c>
@@ -11808,10 +12088,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="67"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="44">
         <v>4590</v>
       </c>
@@ -11823,10 +12103,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="46">
         <v>1070</v>
       </c>
@@ -11838,10 +12118,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="58"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="48">
         <v>5221</v>
       </c>
@@ -11970,151 +12250,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="81" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="57" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="82">
+      <c r="B2" s="94"/>
+      <c r="C2" s="58">
         <v>8835</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="83">
+      <c r="B3" s="89"/>
+      <c r="C3" s="59">
         <v>2597</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="83">
+      <c r="B4" s="89"/>
+      <c r="C4" s="59">
         <v>7686</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="83">
+      <c r="B5" s="89"/>
+      <c r="C5" s="59">
         <v>3140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="83">
+      <c r="B6" s="89"/>
+      <c r="C6" s="59">
         <v>5043</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="83">
+      <c r="B7" s="89"/>
+      <c r="C7" s="59">
         <v>1434</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="83">
+      <c r="B8" s="89"/>
+      <c r="C8" s="59">
         <v>3647</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="83">
+      <c r="B9" s="89"/>
+      <c r="C9" s="59">
         <v>8677</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="83">
+      <c r="B10" s="89"/>
+      <c r="C10" s="59">
         <v>5463</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="83">
+      <c r="B11" s="89"/>
+      <c r="C11" s="59">
         <v>1035</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="83">
+      <c r="B12" s="89"/>
+      <c r="C12" s="59">
         <v>7412</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="83">
+      <c r="B13" s="89"/>
+      <c r="C13" s="59">
         <v>7759</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="84">
+      <c r="B14" s="90"/>
+      <c r="C14" s="60">
         <v>5614</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="85">
+      <c r="B15" s="91"/>
+      <c r="C15" s="61">
         <v>1538</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="80"/>
-      <c r="C16" s="86">
+      <c r="B16" s="92"/>
+      <c r="C16" s="62">
         <v>1867</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -12125,12 +12411,6 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014BB057-FD51-4128-8C6C-845DF7529113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375A9327-426A-42FD-809F-A3B30DA3C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="89">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -367,7 +367,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="82">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1354,46 +1354,7 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -1405,30 +1366,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
-      </top>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1438,7 +1393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1630,20 +1585,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1653,6 +1599,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1683,53 +1638,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3151,11 +3073,11 @@
       <c r="C33" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="67"/>
-      <c r="E33" s="65" t="s">
+      <c r="D33" s="65"/>
+      <c r="E33" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="66"/>
+      <c r="F33" s="67"/>
       <c r="G33" s="63" t="s">
         <v>25</v>
       </c>
@@ -4518,6 +4440,20 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
@@ -4528,20 +4464,6 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -5640,11 +5562,11 @@
       <c r="C33" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="67"/>
-      <c r="E33" s="65" t="s">
+      <c r="D33" s="65"/>
+      <c r="E33" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="66"/>
+      <c r="F33" s="67"/>
       <c r="G33" s="63" t="s">
         <v>25</v>
       </c>
@@ -7007,13 +6929,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="I1:J1"/>
@@ -7025,12 +6946,13 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -7049,38 +6971,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="71" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="71" t="s">
+      <c r="D1" s="72"/>
+      <c r="E1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="75"/>
-      <c r="G1" s="71" t="s">
+      <c r="F1" s="72"/>
+      <c r="G1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="71" t="s">
+      <c r="H1" s="72"/>
+      <c r="I1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="75"/>
-      <c r="K1" s="71" t="s">
+      <c r="J1" s="72"/>
+      <c r="K1" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="71" t="s">
+      <c r="L1" s="72"/>
+      <c r="M1" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="72"/>
-      <c r="O1" s="73" t="s">
+      <c r="N1" s="69"/>
+      <c r="O1" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="74"/>
+      <c r="P1" s="71"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -7752,11 +7674,11 @@
       <c r="A17" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="69"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="69"/>
+      <c r="D17" s="74"/>
       <c r="E17" s="63" t="s">
         <v>22</v>
       </c>
@@ -7772,11 +7694,11 @@
       <c r="K17" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="67"/>
-      <c r="M17" s="65" t="s">
+      <c r="L17" s="65"/>
+      <c r="M17" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="66"/>
+      <c r="N17" s="67"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
@@ -8372,35 +8294,35 @@
       <c r="A49" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="69"/>
+      <c r="B49" s="74"/>
       <c r="C49" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="69"/>
+      <c r="D49" s="74"/>
       <c r="E49" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="69"/>
+      <c r="F49" s="74"/>
       <c r="G49" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="69"/>
+      <c r="H49" s="74"/>
       <c r="I49" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="69"/>
+      <c r="J49" s="74"/>
       <c r="K49" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="69"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="N49" s="67"/>
-      <c r="O49" s="65" t="s">
+      <c r="N49" s="65"/>
+      <c r="O49" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="66"/>
+      <c r="P49" s="67"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
@@ -9057,31 +8979,31 @@
       <c r="A65" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="69"/>
+      <c r="B65" s="74"/>
       <c r="C65" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="69"/>
+      <c r="D65" s="74"/>
       <c r="E65" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F65" s="69"/>
+      <c r="F65" s="74"/>
       <c r="G65" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="69"/>
+      <c r="H65" s="74"/>
       <c r="I65" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J65" s="69"/>
+      <c r="J65" s="74"/>
       <c r="K65" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="L65" s="70"/>
-      <c r="M65" s="65" t="s">
+      <c r="L65" s="73"/>
+      <c r="M65" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="N65" s="68"/>
+      <c r="N65" s="75"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="1" t="s">
@@ -9674,23 +9596,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
@@ -9704,6 +9609,23 @@
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="I65:J65"/>
     <mergeCell ref="M49:N49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -9715,11 +9637,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="1" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10076,814 +9997,384 @@
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A19" s="105" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="107" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="97" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A20" s="102" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="103" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="104" t="s">
+      <c r="A20" s="95" t="s">
         <v>57</v>
       </c>
+      <c r="B20" s="95" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="95" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A21" s="96" t="s">
-        <v>7</v>
+      <c r="A21" s="95" t="s">
+        <v>59</v>
       </c>
       <c r="B21" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="95" t="s">
         <v>59</v>
       </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A22" s="98" t="s">
-        <v>8</v>
+      <c r="A22" s="95" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="95" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="97" t="s">
-        <v>61</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A23" s="96" t="s">
-        <v>5</v>
+      <c r="A23" s="95" t="s">
+        <v>65</v>
       </c>
       <c r="B23" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="97" t="s">
-        <v>55</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C23" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A24" s="96" t="s">
-        <v>10</v>
+      <c r="A24" s="95" t="s">
+        <v>67</v>
       </c>
       <c r="B24" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="95" t="s">
         <v>65</v>
       </c>
+      <c r="D24" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A25" s="96" t="s">
-        <v>11</v>
+      <c r="A25" s="95" t="s">
+        <v>68</v>
       </c>
       <c r="B25" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="97" t="s">
-        <v>67</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C25" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A26" s="98" t="s">
-        <v>12</v>
+      <c r="A26" s="95" t="s">
+        <v>72</v>
       </c>
       <c r="B26" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="97"/>
+        <v>74</v>
+      </c>
+      <c r="C26" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="95" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A27" s="96" t="s">
-        <v>9</v>
+      <c r="A27" s="95" t="s">
+        <v>74</v>
       </c>
       <c r="B27" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="97" t="s">
-        <v>63</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C27" s="95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" ht="13.5" customHeight="1">
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
       <c r="A28" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="97" t="s">
-        <v>72</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B28" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="96" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A29" s="96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="97" t="s">
-        <v>74</v>
-      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A30" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="97" t="s">
-        <v>76</v>
-      </c>
+      <c r="B30" s="32"/>
+      <c r="C30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A31" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>70</v>
-      </c>
+      <c r="B31" s="32"/>
+      <c r="C31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A32" s="99" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="100" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="101" t="s">
-        <v>78</v>
-      </c>
+    <row r="32" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B32" s="32"/>
+      <c r="C32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
+    <row r="33" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B33" s="32"/>
       <c r="C33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
+    <row r="34" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B34" s="32"/>
       <c r="C34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A35" s="105" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="107" t="s">
-        <v>49</v>
-      </c>
+    <row r="35" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B35" s="32"/>
+      <c r="C35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A36" s="102" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="103" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="104" t="s">
-        <v>59</v>
-      </c>
+    <row r="36" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B36" s="32"/>
+      <c r="C36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A37" s="98" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="95" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="97" t="s">
-        <v>61</v>
-      </c>
+    <row r="37" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B37" s="32"/>
+      <c r="C37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A38" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="97" t="s">
-        <v>55</v>
-      </c>
+    <row r="38" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B38" s="32"/>
+      <c r="C38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A39" s="96" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="95" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="97" t="s">
-        <v>57</v>
-      </c>
+    <row r="39" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B39" s="32"/>
+      <c r="C39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A40" s="96" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="97" t="s">
-        <v>67</v>
-      </c>
+    <row r="40" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B40" s="32"/>
+      <c r="C40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A41" s="98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="97"/>
+    <row r="41" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B41" s="32"/>
+      <c r="C41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A42" s="96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="97" t="s">
-        <v>63</v>
-      </c>
+    <row r="42" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B42" s="32"/>
+      <c r="C42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A43" s="96" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="97" t="s">
-        <v>65</v>
-      </c>
+    <row r="43" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B43" s="32"/>
+      <c r="C43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A44" s="96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="97" t="s">
-        <v>74</v>
-      </c>
+    <row r="44" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B44" s="32"/>
+      <c r="C44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A45" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="97" t="s">
-        <v>76</v>
-      </c>
+    <row r="45" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B45" s="32"/>
+      <c r="C45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A46" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="B46" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="C46" s="97" t="s">
-        <v>70</v>
-      </c>
+    <row r="46" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B46" s="32"/>
+      <c r="C46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A47" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="97" t="s">
-        <v>72</v>
-      </c>
+    <row r="47" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B47" s="32"/>
+      <c r="C47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A48" s="99" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="100" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="101" t="s">
-        <v>78</v>
-      </c>
+    <row r="48" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B48" s="32"/>
+      <c r="C48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="6"/>
     </row>
-    <row r="49" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
+    <row r="49" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B49" s="32"/>
       <c r="C49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="6"/>
     </row>
-    <row r="50" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+    <row r="50" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B50" s="32"/>
       <c r="C50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="6"/>
     </row>
-    <row r="51" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A51" s="105" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="107" t="s">
-        <v>49</v>
-      </c>
+    <row r="51" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B51" s="32"/>
+      <c r="C51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="6"/>
     </row>
-    <row r="52" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A52" s="108" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="103" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="104" t="s">
-        <v>61</v>
-      </c>
+    <row r="52" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B52" s="32"/>
+      <c r="C52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="6"/>
     </row>
-    <row r="53" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A53" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="97" t="s">
-        <v>55</v>
-      </c>
+    <row r="53" spans="2:8" ht="13.5" customHeight="1">
+      <c r="B53" s="32"/>
+      <c r="C53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A54" s="96" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="95" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" s="97" t="s">
-        <v>57</v>
-      </c>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A55" s="96" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="97" t="s">
-        <v>59</v>
-      </c>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A56" s="98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" s="97"/>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A57" s="96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A58" s="96" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A59" s="96" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A60" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="97" t="s">
-        <v>76</v>
-      </c>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A61" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A62" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B62" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A63" s="96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="97" t="s">
-        <v>74</v>
-      </c>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A64" s="99" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" s="100" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="101" t="s">
-        <v>78</v>
-      </c>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B65" s="32"/>
-      <c r="C65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B66" s="32"/>
-      <c r="C66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B67" s="32"/>
-      <c r="C67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B68" s="32"/>
-      <c r="C68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B69" s="32"/>
-      <c r="C69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B70" s="32"/>
-      <c r="C70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B71" s="32"/>
-      <c r="C71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B72" s="32"/>
-      <c r="C72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B73" s="32"/>
-      <c r="C73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-    </row>
-    <row r="74" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B74" s="32"/>
-      <c r="C74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-    </row>
-    <row r="75" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B75" s="32"/>
-      <c r="C75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-    </row>
-    <row r="76" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B76" s="32"/>
-      <c r="C76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-    </row>
-    <row r="77" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B77" s="32"/>
-      <c r="C77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-    </row>
-    <row r="78" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B78" s="32"/>
-      <c r="C78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-    </row>
-    <row r="79" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B79" s="32"/>
-      <c r="C79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-    </row>
-    <row r="80" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B80" s="32"/>
-      <c r="C80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-    </row>
-    <row r="81" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B81" s="32"/>
-      <c r="C81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-    </row>
-    <row r="82" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B82" s="32"/>
-      <c r="C82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-    </row>
-    <row r="83" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B83" s="32"/>
-      <c r="C83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-    </row>
-    <row r="84" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B84" s="32"/>
-      <c r="C84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-    </row>
-    <row r="85" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B85" s="32"/>
-      <c r="C85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-    </row>
-    <row r="86" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B86" s="32"/>
-      <c r="C86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-    </row>
-    <row r="87" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B87" s="32"/>
-      <c r="C87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-    </row>
-    <row r="88" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B88" s="32"/>
-      <c r="C88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-    </row>
-    <row r="89" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B89" s="32"/>
-      <c r="C89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B90" s="32"/>
-      <c r="C90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B91" s="32"/>
-      <c r="C91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B92" s="32"/>
-      <c r="C92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-    </row>
-    <row r="93" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B93" s="32"/>
-      <c r="C93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-    </row>
-    <row r="94" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B94" s="32"/>
-      <c r="C94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-    </row>
-    <row r="95" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B95" s="32"/>
-      <c r="C95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-    </row>
-    <row r="96" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B96" s="32"/>
-      <c r="C96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-    </row>
-    <row r="97" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B97" s="32"/>
-      <c r="C97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-    </row>
-    <row r="98" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B98" s="32"/>
-      <c r="C98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-    </row>
-    <row r="99" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B99" s="32"/>
-      <c r="C99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-    </row>
-    <row r="100" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B100" s="32"/>
-      <c r="C100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12253,7 +11744,7 @@
       <c r="A1" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="93"/>
+      <c r="B1" s="90"/>
       <c r="C1" s="57" t="s">
         <v>83</v>
       </c>
@@ -12262,7 +11753,7 @@
       <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="94"/>
+      <c r="B2" s="91"/>
       <c r="C2" s="58">
         <v>8835</v>
       </c>
@@ -12370,7 +11861,7 @@
       <c r="A14" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="90"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="60">
         <v>5614</v>
       </c>
@@ -12379,7 +11870,7 @@
       <c r="A15" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="61">
         <v>1538</v>
       </c>
@@ -12388,19 +11879,13 @@
       <c r="A16" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="92"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="62">
         <v>1867</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -12411,6 +11896,12 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375A9327-426A-42FD-809F-A3B30DA3C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B62FA9-7C74-4F59-B195-3EB3BB790833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EQUIPOS QR" sheetId="1" r:id="rId1"/>
     <sheet name="EQUIPOS PRUEBAS" sheetId="2" r:id="rId2"/>
-    <sheet name="IMPRIMIR EQUIPOS" sheetId="9" r:id="rId3"/>
-    <sheet name="TARJETAS" sheetId="3" r:id="rId4"/>
-    <sheet name="CENTRO SOCIAL" sheetId="4" r:id="rId5"/>
-    <sheet name="AMBULANCIA" sheetId="5" r:id="rId6"/>
-    <sheet name="COMPRESOR" sheetId="6" r:id="rId7"/>
-    <sheet name="FINAL" sheetId="8" r:id="rId8"/>
+    <sheet name="Hoja1" sheetId="10" r:id="rId3"/>
+    <sheet name="IMPRIMIR EQUIPOS" sheetId="9" r:id="rId4"/>
+    <sheet name="TARJETAS" sheetId="3" r:id="rId5"/>
+    <sheet name="CENTRO SOCIAL" sheetId="4" r:id="rId6"/>
+    <sheet name="AMBULANCIA" sheetId="5" r:id="rId7"/>
+    <sheet name="COMPRESOR" sheetId="6" r:id="rId8"/>
+    <sheet name="FINAL" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'EQUIPOS QR'!$A$1:$L$46</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="89">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -367,7 +368,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="79">
+  <borders count="92">
     <border>
       <left/>
       <right/>
@@ -1389,11 +1390,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1581,6 +1767,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1590,6 +1785,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1599,15 +1803,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1638,20 +1833,65 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1993,30 +2233,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="63" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="63" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="63" t="s">
+      <c r="F1" s="67"/>
+      <c r="G1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="63" t="s">
+      <c r="H1" s="67"/>
+      <c r="I1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="64"/>
-      <c r="K1" s="63" t="s">
+      <c r="J1" s="67"/>
+      <c r="K1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="64"/>
+      <c r="L1" s="67"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2529,30 +2769,30 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="63" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="63" t="s">
+      <c r="D17" s="67"/>
+      <c r="E17" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="63" t="s">
+      <c r="F17" s="67"/>
+      <c r="G17" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="63" t="s">
+      <c r="H17" s="67"/>
+      <c r="I17" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="63" t="s">
+      <c r="J17" s="67"/>
+      <c r="K17" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="64"/>
+      <c r="L17" s="67"/>
     </row>
     <row r="18" spans="1:12" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
@@ -3066,30 +3306,30 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="63" t="s">
+      <c r="B33" s="67"/>
+      <c r="C33" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66" t="s">
+      <c r="D33" s="68"/>
+      <c r="E33" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="67"/>
-      <c r="G33" s="63" t="s">
+      <c r="F33" s="70"/>
+      <c r="G33" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="64"/>
-      <c r="I33" s="63" t="s">
+      <c r="H33" s="67"/>
+      <c r="I33" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="64"/>
-      <c r="K33" s="63" t="s">
+      <c r="J33" s="67"/>
+      <c r="K33" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="64"/>
+      <c r="L33" s="67"/>
     </row>
     <row r="34" spans="1:12" ht="13.5" customHeight="1">
       <c r="A34" s="1" t="s">
@@ -3602,30 +3842,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="64"/>
-      <c r="C49" s="63" t="s">
+      <c r="B49" s="67"/>
+      <c r="C49" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="64"/>
-      <c r="E49" s="63" t="s">
+      <c r="D49" s="67"/>
+      <c r="E49" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="64"/>
-      <c r="G49" s="63" t="s">
+      <c r="F49" s="67"/>
+      <c r="G49" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="64"/>
-      <c r="I49" s="63" t="s">
+      <c r="H49" s="67"/>
+      <c r="I49" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="63" t="s">
+      <c r="J49" s="67"/>
+      <c r="K49" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="64"/>
+      <c r="L49" s="67"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -4440,20 +4680,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
@@ -4464,6 +4690,20 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -4475,37 +4715,37 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:S100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="12" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="63" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="63" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="63" t="s">
+      <c r="F1" s="67"/>
+      <c r="G1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="63" t="s">
+      <c r="H1" s="67"/>
+      <c r="I1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="64"/>
-      <c r="K1" s="63" t="s">
+      <c r="J1" s="67"/>
+      <c r="K1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="64"/>
+      <c r="L1" s="67"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -5017,33 +5257,33 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A17" s="63" t="s">
+    <row r="17" spans="1:19" ht="13.5" customHeight="1">
+      <c r="A17" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="63" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="63" t="s">
+      <c r="D17" s="67"/>
+      <c r="E17" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="63" t="s">
+      <c r="F17" s="67"/>
+      <c r="G17" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="63" t="s">
+      <c r="H17" s="67"/>
+      <c r="I17" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="63" t="s">
+      <c r="J17" s="67"/>
+      <c r="K17" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="64"/>
-    </row>
-    <row r="18" spans="1:12" ht="13.5" customHeight="1">
+      <c r="L17" s="67"/>
+    </row>
+    <row r="18" spans="1:19" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -5081,7 +5321,7 @@
         <v>6914</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="13.5" customHeight="1">
+    <row r="19" spans="1:19" ht="13.5" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -5119,7 +5359,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="13.5" customHeight="1">
+    <row r="20" spans="1:19" ht="13.5" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -5157,7 +5397,7 @@
         <v>9119</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="13.5" customHeight="1">
+    <row r="21" spans="1:19" ht="13.5" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -5195,7 +5435,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="13.5" customHeight="1">
+    <row r="22" spans="1:19" ht="13.5" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
@@ -5233,7 +5473,7 @@
         <v>3739</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="13.5" customHeight="1">
+    <row r="23" spans="1:19" ht="13.5" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
@@ -5271,7 +5511,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="13.5" customHeight="1">
+    <row r="24" spans="1:19" ht="13.5" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>38</v>
       </c>
@@ -5309,7 +5549,7 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="13.5" customHeight="1">
+    <row r="25" spans="1:19" ht="13.5" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
@@ -5347,7 +5587,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="13.5" customHeight="1">
+    <row r="26" spans="1:19" ht="13.5" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
@@ -5385,7 +5625,7 @@
         <v>5086</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="13.5" customHeight="1">
+    <row r="27" spans="1:19" ht="13.5" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
@@ -5423,7 +5663,7 @@
         <v>9640</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="13.5" customHeight="1">
+    <row r="28" spans="1:19" ht="13.5" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
@@ -5461,7 +5701,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="13.5" customHeight="1">
+    <row r="29" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
       <c r="A29" s="1" t="s">
         <v>43</v>
       </c>
@@ -5499,7 +5739,7 @@
         <v>8181</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>46</v>
       </c>
@@ -5536,8 +5776,20 @@
       <c r="L30" s="5">
         <v>7759</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N30" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="O30" s="67"/>
+      <c r="P30" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="S30" s="67"/>
+    </row>
+    <row r="31" spans="1:19" ht="13.5" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -5545,42 +5797,84 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
+      <c r="N31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" s="6">
+        <v>9652</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>4487</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S31" s="2">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="63" t="s">
+      <c r="N32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O32" s="6">
+        <v>7622</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>6906</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S32" s="2">
+        <v>5737</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A33" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="63" t="s">
+      <c r="B33" s="67"/>
+      <c r="C33" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66" t="s">
+      <c r="D33" s="68"/>
+      <c r="E33" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="67"/>
-      <c r="G33" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="64"/>
-      <c r="I33" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="64"/>
-      <c r="K33" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="64"/>
-    </row>
-    <row r="34" spans="1:12" ht="13.5" customHeight="1">
+      <c r="F33" s="70"/>
+      <c r="N33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33" s="6">
+        <v>9171</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>2906</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S33" s="2">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="13.5" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -5599,26 +5893,26 @@
       <c r="F34" s="52">
         <v>1993</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="N34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O34" s="6">
+        <v>9446</v>
+      </c>
+      <c r="P34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="6">
-        <v>9652</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="Q34" s="6">
+        <v>7012</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J34" s="6">
-        <v>4487</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L34" s="2">
-        <v>7822</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="13.5" customHeight="1">
+      <c r="S34" s="2">
+        <v>9616</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="13.5" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -5637,26 +5931,26 @@
       <c r="F35" s="52">
         <v>4593</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="6">
-        <v>7622</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J35" s="6">
-        <v>6906</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="2">
-        <v>5737</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O35" s="6">
+        <v>2949</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>3761</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S35" s="2">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="13.5" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -5675,26 +5969,26 @@
       <c r="F36" s="52">
         <v>5085</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="6">
-        <v>9171</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" s="6">
-        <v>2906</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="2">
-        <v>7486</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O36" s="6">
+        <v>3596</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>9096</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S36" s="2">
+        <v>9538</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="13.5" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -5713,26 +6007,26 @@
       <c r="F37" s="52">
         <v>7688</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="6">
-        <v>9446</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J37" s="6">
-        <v>7012</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L37" s="2">
-        <v>9616</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O37" s="6">
+        <v>5237</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>7636</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S37" s="2">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="13.5" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
@@ -5751,26 +6045,26 @@
       <c r="F38" s="52">
         <v>4387</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="N38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O38" s="6">
+        <v>7448</v>
+      </c>
+      <c r="P38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H38" s="6">
-        <v>2949</v>
-      </c>
-      <c r="I38" s="1" t="s">
+      <c r="Q38" s="6">
+        <v>2113</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J38" s="6">
-        <v>3761</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" s="2">
-        <v>6698</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="13.5" customHeight="1">
+      <c r="S38" s="2">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="13.5" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -5789,26 +6083,26 @@
       <c r="F39" s="52">
         <v>1908</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="6">
-        <v>3596</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="6">
-        <v>9096</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L39" s="2">
-        <v>9538</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="6">
+        <v>5888</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>7052</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S39" s="2">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="13.5" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
@@ -5827,26 +6121,26 @@
       <c r="F40" s="52">
         <v>4198</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" s="6">
-        <v>5237</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J40" s="6">
-        <v>7636</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L40" s="2">
-        <v>7742</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O40" s="6">
+        <v>2759</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>1435</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S40" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="13.5" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
@@ -5865,26 +6159,26 @@
       <c r="F41" s="52">
         <v>4150</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H41" s="6">
-        <v>7448</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="6">
-        <v>2113</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="2">
-        <v>6575</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O41" s="6">
+        <v>9745</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>3551</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S41" s="2">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="13.5" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -5903,26 +6197,26 @@
       <c r="F42" s="52">
         <v>6970</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="N42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42" s="6">
+        <v>3441</v>
+      </c>
+      <c r="P42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="6">
-        <v>5888</v>
-      </c>
-      <c r="I42" s="1" t="s">
+      <c r="Q42" s="6">
+        <v>7867</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J42" s="6">
-        <v>7052</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="2">
-        <v>2845</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="13.5" customHeight="1">
+      <c r="S42" s="2">
+        <v>8930</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -5941,26 +6235,26 @@
       <c r="F43" s="52">
         <v>5221</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="6">
-        <v>2759</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J43" s="6">
-        <v>1435</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L43" s="2">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="13.5" customHeight="1">
+      <c r="N43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O43" s="7">
+        <v>8872</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>9956</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" s="5">
+        <v>9733</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="13.5" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -5979,26 +6273,8 @@
       <c r="F44" s="52">
         <v>4105</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="6">
-        <v>9745</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J44" s="6">
-        <v>3551</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L44" s="2">
-        <v>4477</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="13.5" customHeight="1">
+    </row>
+    <row r="45" spans="1:19" ht="13.5" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>45</v>
       </c>
@@ -6017,26 +6293,8 @@
       <c r="F45" s="52">
         <v>8648</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H45" s="6">
-        <v>3441</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J45" s="6">
-        <v>7867</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L45" s="2">
-        <v>8930</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
+    </row>
+    <row r="46" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
       <c r="A46" s="4" t="s">
         <v>46</v>
       </c>
@@ -6055,26 +6313,8 @@
       <c r="F46" s="55">
         <v>1867</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="7">
-        <v>8872</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="7">
-        <v>9956</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="5">
-        <v>9733</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="13.5" customHeight="1">
+    </row>
+    <row r="47" spans="1:19" ht="13.5" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -6082,7 +6322,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:12" ht="13.5" customHeight="1">
+    <row r="48" spans="1:19" ht="13.5" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -6091,30 +6331,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="64"/>
-      <c r="C49" s="63" t="s">
+      <c r="B49" s="67"/>
+      <c r="C49" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="64"/>
-      <c r="E49" s="63" t="s">
+      <c r="D49" s="67"/>
+      <c r="E49" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="64"/>
-      <c r="G49" s="63" t="s">
+      <c r="F49" s="67"/>
+      <c r="G49" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="64"/>
-      <c r="I49" s="63" t="s">
+      <c r="H49" s="67"/>
+      <c r="I49" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="63" t="s">
+      <c r="J49" s="67"/>
+      <c r="K49" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="64"/>
+      <c r="L49" s="67"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -6929,30 +7169,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -6960,6 +7200,1895 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3AC2DF-655E-4920-B2B7-B6BD4E4815EB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P77"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="16" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A1" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="67"/>
+      <c r="E1" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="67"/>
+      <c r="G1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="67"/>
+      <c r="I1" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="67"/>
+      <c r="K1" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="67"/>
+      <c r="M1" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="68"/>
+      <c r="O1" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="70"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5377</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3218</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2">
+        <v>6531</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4504</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="2">
+        <v>3016</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2">
+        <v>9943</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="6">
+        <v>9842</v>
+      </c>
+      <c r="O2" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="52">
+        <v>7609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2">
+        <v>8008</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1058</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8216</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7612</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5551</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="2">
+        <v>6109</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="6">
+        <v>2529</v>
+      </c>
+      <c r="O3" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="52">
+        <v>8698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2">
+        <v>8613</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4089</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7792</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1439</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="2">
+        <v>8688</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="2">
+        <v>6014</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="6">
+        <v>6665</v>
+      </c>
+      <c r="O4" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="52">
+        <v>9623</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1764</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8058</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6066</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3560</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2">
+        <v>9390</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="2">
+        <v>8036</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="6">
+        <v>7345</v>
+      </c>
+      <c r="O5" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="52">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2">
+        <v>7120</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2226</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9330</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1020</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1324</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="2">
+        <v>6590</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="6">
+        <v>4828</v>
+      </c>
+      <c r="O6" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="52">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5895</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8706</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6301</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8684</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="2">
+        <v>7067</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2077</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="6">
+        <v>5817</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="52">
+        <v>9182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2">
+        <v>8962</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4675</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2537</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1996</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="2">
+        <v>9836</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2">
+        <v>9856</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="6">
+        <v>2768</v>
+      </c>
+      <c r="O8" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" s="52">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7928</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5063</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5296</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5402</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1330</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5988</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="6">
+        <v>2645</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="52">
+        <v>9237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2">
+        <v>8131</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2844</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9632</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8597</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6409</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="2">
+        <v>8913</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="6">
+        <v>7069</v>
+      </c>
+      <c r="O10" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="52">
+        <v>8746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4659</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1248</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6394</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2">
+        <v>6164</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4904</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="2">
+        <v>6825</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="6">
+        <v>4397</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" s="52">
+        <v>8477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2386</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9634</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9756</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6263</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4182</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2058</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="6">
+        <v>3408</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" s="52">
+        <v>8418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>9201</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8118</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="2">
+        <v>5934</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5259</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="2">
+        <v>9947</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="2">
+        <v>4523</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="6">
+        <v>2785</v>
+      </c>
+      <c r="O13" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="52">
+        <v>5778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="5">
+        <v>8835</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2597</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="5">
+        <v>7686</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="5">
+        <v>3140</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="5">
+        <v>5043</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1434</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="7">
+        <v>3647</v>
+      </c>
+      <c r="O14" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="55">
+        <v>8677</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A17" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="67"/>
+      <c r="C17" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="67"/>
+      <c r="G17" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="67"/>
+      <c r="I17" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="67"/>
+      <c r="K17" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="68"/>
+      <c r="M17" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="N17" s="70"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6">
+        <v>5914</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="6">
+        <v>7625</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3552</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="2">
+        <v>6914</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="6">
+        <v>2749</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="6">
+        <v>2064</v>
+      </c>
+      <c r="M18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" s="52">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6">
+        <v>6312</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="6">
+        <v>7268</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4498</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="2">
+        <v>3787</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="6">
+        <v>9086</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="6">
+        <v>4298</v>
+      </c>
+      <c r="M19" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="52">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1429</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2068</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4994</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="2">
+        <v>9119</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="6">
+        <v>4179</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="6">
+        <v>2357</v>
+      </c>
+      <c r="M20" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="N20" s="52">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6">
+        <v>6767</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="6">
+        <v>4954</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="2">
+        <v>7407</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1997</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1837</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="6">
+        <v>7799</v>
+      </c>
+      <c r="M21" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" s="52">
+        <v>7688</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1648</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1372</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4899</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="2">
+        <v>3739</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" s="6">
+        <v>5328</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" s="6">
+        <v>7324</v>
+      </c>
+      <c r="M22" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="N22" s="52">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6">
+        <v>3205</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3347</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8392</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="2">
+        <v>6515</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="6">
+        <v>9455</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" s="6">
+        <v>9992</v>
+      </c>
+      <c r="M23" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="52">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6">
+        <v>4677</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="6">
+        <v>6523</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8868</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="2">
+        <v>3892</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="6">
+        <v>5861</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" s="6">
+        <v>4433</v>
+      </c>
+      <c r="M24" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="N24" s="52">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6">
+        <v>5806</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="6">
+        <v>7401</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8322</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="2">
+        <v>4368</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="6">
+        <v>3945</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="6">
+        <v>1033</v>
+      </c>
+      <c r="M25" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="N25" s="52">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6">
+        <v>6217</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2021</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="2">
+        <v>4444</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5086</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="6">
+        <v>9707</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="6">
+        <v>4753</v>
+      </c>
+      <c r="M26" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="52">
+        <v>6970</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6">
+        <v>2471</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3640</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1583</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="2">
+        <v>9640</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="6">
+        <v>2394</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="6">
+        <v>8735</v>
+      </c>
+      <c r="M27" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="N27" s="52">
+        <v>5221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6">
+        <v>4859</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="6">
+        <v>8252</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1568</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2639</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" s="6">
+        <v>4889</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L28" s="6">
+        <v>1070</v>
+      </c>
+      <c r="M28" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="52">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2928</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1581</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6986</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8181</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" s="6">
+        <v>4590</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" s="6">
+        <v>2535</v>
+      </c>
+      <c r="M29" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="52">
+        <v>8648</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="7">
+        <v>5463</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1035</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="5">
+        <v>7412</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="5">
+        <v>7759</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="7">
+        <v>5614</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="7">
+        <v>1538</v>
+      </c>
+      <c r="M30" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="55">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1"/>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A50" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="E50" s="108" t="s">
+        <v>50</v>
+      </c>
+      <c r="F50" s="109" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" s="110" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="111" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H51" s="112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="103" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H52" s="113" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="103" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="113" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54" s="113" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="103" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="103" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H55" s="114" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H56" s="113" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="103" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" s="113" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="43"/>
+      <c r="E58" s="104" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" s="113" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="103" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H59" s="114" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="113" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" s="103" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" s="113" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="113" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A63" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="115" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="115" t="s">
+        <v>46</v>
+      </c>
+      <c r="H63" s="107" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="B64" s="32"/>
+      <c r="C64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="B65" s="32"/>
+      <c r="C65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="B66" s="32"/>
+      <c r="C66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1">
+      <c r="B67" s="32"/>
+      <c r="C67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A68" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B68" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C68" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D71" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="B72" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D73" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="D74" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A77" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="66" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A7BE38-5CCC-4F22-BE73-BF5B656FE56E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6971,38 +9100,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="68" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="72"/>
-      <c r="E1" s="68" t="s">
+      <c r="D1" s="78"/>
+      <c r="E1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="72"/>
-      <c r="G1" s="68" t="s">
+      <c r="F1" s="78"/>
+      <c r="G1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="68" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="68" t="s">
+      <c r="J1" s="78"/>
+      <c r="K1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="72"/>
-      <c r="M1" s="68" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="69"/>
-      <c r="O1" s="70" t="s">
+      <c r="N1" s="75"/>
+      <c r="O1" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="71"/>
+      <c r="P1" s="77"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -7671,34 +9800,34 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="63" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="63" t="s">
+      <c r="D17" s="71"/>
+      <c r="E17" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="63" t="s">
+      <c r="F17" s="67"/>
+      <c r="G17" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="63" t="s">
+      <c r="H17" s="67"/>
+      <c r="I17" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="63" t="s">
+      <c r="J17" s="67"/>
+      <c r="K17" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="65"/>
-      <c r="M17" s="66" t="s">
+      <c r="L17" s="68"/>
+      <c r="M17" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="67"/>
+      <c r="N17" s="70"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
@@ -8291,38 +10420,38 @@
     </row>
     <row r="48" ht="15.75" thickBot="1"/>
     <row r="49" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="74"/>
-      <c r="C49" s="63" t="s">
+      <c r="B49" s="71"/>
+      <c r="C49" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="63" t="s">
+      <c r="D49" s="71"/>
+      <c r="E49" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="74"/>
-      <c r="G49" s="63" t="s">
+      <c r="F49" s="71"/>
+      <c r="G49" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="74"/>
-      <c r="I49" s="63" t="s">
+      <c r="H49" s="71"/>
+      <c r="I49" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="74"/>
-      <c r="K49" s="63" t="s">
+      <c r="J49" s="71"/>
+      <c r="K49" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="74"/>
-      <c r="M49" s="63" t="s">
+      <c r="L49" s="71"/>
+      <c r="M49" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="N49" s="65"/>
-      <c r="O49" s="66" t="s">
+      <c r="N49" s="68"/>
+      <c r="O49" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="67"/>
+      <c r="P49" s="70"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
@@ -8976,34 +11105,34 @@
     </row>
     <row r="64" spans="1:16" ht="15.75" thickBot="1"/>
     <row r="65" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A65" s="63" t="s">
+      <c r="A65" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="74"/>
-      <c r="C65" s="63" t="s">
+      <c r="B65" s="71"/>
+      <c r="C65" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="74"/>
-      <c r="E65" s="63" t="s">
+      <c r="D65" s="71"/>
+      <c r="E65" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="F65" s="74"/>
-      <c r="G65" s="63" t="s">
+      <c r="F65" s="71"/>
+      <c r="G65" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="74"/>
-      <c r="I65" s="63" t="s">
+      <c r="H65" s="71"/>
+      <c r="I65" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J65" s="74"/>
-      <c r="K65" s="63" t="s">
+      <c r="J65" s="71"/>
+      <c r="K65" s="66" t="s">
         <v>86</v>
       </c>
       <c r="L65" s="73"/>
-      <c r="M65" s="66" t="s">
+      <c r="M65" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="N65" s="75"/>
+      <c r="N65" s="72"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="1" t="s">
@@ -9596,6 +11725,23 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
@@ -9609,30 +11755,13 @@
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="I65:J65"/>
     <mergeCell ref="M49:N49"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9997,16 +12126,16 @@
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="97" t="s">
+      <c r="D19" s="65" t="s">
         <v>53</v>
       </c>
       <c r="E19" s="6"/>
@@ -10015,16 +12144,16 @@
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="95" t="s">
+      <c r="C20" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="63" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="6"/>
@@ -10033,16 +12162,16 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="95" t="s">
+      <c r="C21" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="63" t="s">
         <v>59</v>
       </c>
       <c r="E21" s="6"/>
@@ -10051,16 +12180,16 @@
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="95" t="s">
+      <c r="C22" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="63" t="s">
         <v>68</v>
       </c>
       <c r="E22" s="6"/>
@@ -10069,16 +12198,16 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A23" s="95" t="s">
+      <c r="A23" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="63" t="s">
         <v>65</v>
       </c>
       <c r="E23" s="6"/>
@@ -10087,16 +12216,16 @@
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="95" t="s">
+      <c r="C24" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="63" t="s">
         <v>67</v>
       </c>
       <c r="E24" s="6"/>
@@ -10105,16 +12234,16 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="63" t="s">
         <v>76</v>
       </c>
       <c r="E25" s="6"/>
@@ -10123,16 +12252,16 @@
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="63" t="s">
         <v>72</v>
       </c>
       <c r="E26" s="6"/>
@@ -10141,16 +12270,16 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="95" t="s">
+      <c r="D27" s="63" t="s">
         <v>74</v>
       </c>
       <c r="E27" s="6"/>
@@ -10159,16 +12288,16 @@
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="96" t="s">
+      <c r="D28" s="64" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="6"/>
@@ -10382,7 +12511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10396,10 +12525,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="84"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -10417,10 +12546,10 @@
       <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="83"/>
+      <c r="B2" s="86"/>
       <c r="C2" s="39">
         <v>1764</v>
       </c>
@@ -10438,10 +12567,10 @@
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="42">
         <v>4089</v>
       </c>
@@ -10459,10 +12588,10 @@
       <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="42">
         <v>8216</v>
       </c>
@@ -10480,10 +12609,10 @@
       <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="79"/>
+      <c r="B5" s="82"/>
       <c r="C5" s="42">
         <v>4504</v>
       </c>
@@ -10501,10 +12630,10 @@
       <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="79"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="42">
         <v>9390</v>
       </c>
@@ -10522,10 +12651,10 @@
       <c r="K6" s="33"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="79"/>
+      <c r="B7" s="82"/>
       <c r="C7" s="42">
         <v>6014</v>
       </c>
@@ -10543,10 +12672,10 @@
       <c r="K7" s="33"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="79"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="42">
         <v>2529</v>
       </c>
@@ -10564,10 +12693,10 @@
       <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="79"/>
+      <c r="B9" s="82"/>
       <c r="C9" s="42">
         <v>7609</v>
       </c>
@@ -10585,10 +12714,10 @@
       <c r="K9" s="33"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="79"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="42">
         <v>6767</v>
       </c>
@@ -10606,10 +12735,10 @@
       <c r="K10" s="33"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="79"/>
+      <c r="B11" s="82"/>
       <c r="C11" s="42">
         <v>2068</v>
       </c>
@@ -10627,10 +12756,10 @@
       <c r="K11" s="33"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="42">
         <v>4498</v>
       </c>
@@ -10648,10 +12777,10 @@
       <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="79"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="42">
         <v>6914</v>
       </c>
@@ -10669,10 +12798,10 @@
       <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="44">
         <v>1837</v>
       </c>
@@ -10690,10 +12819,10 @@
       <c r="K14" s="33"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="88"/>
+      <c r="B15" s="91"/>
       <c r="C15" s="46">
         <v>2357</v>
       </c>
@@ -10711,10 +12840,10 @@
       <c r="K15" s="33"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="48">
         <v>4593</v>
       </c>
@@ -11015,7 +13144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -11026,10 +13155,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="84"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -11041,10 +13170,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="83"/>
+      <c r="B2" s="86"/>
       <c r="C2" s="39">
         <v>7928</v>
       </c>
@@ -11056,10 +13185,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="42">
         <v>4675</v>
       </c>
@@ -11071,10 +13200,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="42">
         <v>6301</v>
       </c>
@@ -11086,10 +13215,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="79"/>
+      <c r="B5" s="82"/>
       <c r="C5" s="42">
         <v>1020</v>
       </c>
@@ -11101,10 +13230,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="79"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="42">
         <v>1330</v>
       </c>
@@ -11116,10 +13245,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="79"/>
+      <c r="B7" s="82"/>
       <c r="C7" s="42">
         <v>9856</v>
       </c>
@@ -11131,10 +13260,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="79"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="42">
         <v>5817</v>
       </c>
@@ -11146,10 +13275,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="79"/>
+      <c r="B9" s="82"/>
       <c r="C9" s="42">
         <v>1116</v>
       </c>
@@ -11161,10 +13290,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="79"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="42">
         <v>5806</v>
       </c>
@@ -11176,10 +13305,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="79"/>
+      <c r="B11" s="82"/>
       <c r="C11" s="42">
         <v>6523</v>
       </c>
@@ -11191,10 +13320,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="42">
         <v>8392</v>
       </c>
@@ -11206,10 +13335,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="79"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="42">
         <v>3739</v>
       </c>
@@ -11221,10 +13350,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="44">
         <v>3945</v>
       </c>
@@ -11236,10 +13365,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="88"/>
+      <c r="B15" s="91"/>
       <c r="C15" s="46">
         <v>4433</v>
       </c>
@@ -11251,10 +13380,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="48">
         <v>1908</v>
       </c>
@@ -11373,7 +13502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -11384,10 +13513,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="84"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -11399,10 +13528,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="83"/>
+      <c r="B2" s="86"/>
       <c r="C2" s="39">
         <v>9201</v>
       </c>
@@ -11414,10 +13543,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="42">
         <v>9634</v>
       </c>
@@ -11429,10 +13558,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="42">
         <v>6394</v>
       </c>
@@ -11444,10 +13573,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="79"/>
+      <c r="B5" s="82"/>
       <c r="C5" s="42">
         <v>8597</v>
       </c>
@@ -11459,10 +13588,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="79"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="42">
         <v>9947</v>
       </c>
@@ -11474,10 +13603,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="79"/>
+      <c r="B7" s="82"/>
       <c r="C7" s="42">
         <v>2058</v>
       </c>
@@ -11489,10 +13618,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="79"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="42">
         <v>4397</v>
       </c>
@@ -11504,10 +13633,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="79"/>
+      <c r="B9" s="82"/>
       <c r="C9" s="42">
         <v>8746</v>
       </c>
@@ -11519,10 +13648,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="79"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="42">
         <v>2928</v>
       </c>
@@ -11534,10 +13663,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="79"/>
+      <c r="B11" s="82"/>
       <c r="C11" s="42">
         <v>8252</v>
       </c>
@@ -11549,10 +13678,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="42">
         <v>1583</v>
       </c>
@@ -11564,10 +13693,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="79"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="42">
         <v>5086</v>
       </c>
@@ -11579,10 +13708,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="44">
         <v>4590</v>
       </c>
@@ -11594,10 +13723,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="88"/>
+      <c r="B15" s="91"/>
       <c r="C15" s="46">
         <v>1070</v>
       </c>
@@ -11609,10 +13738,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="48">
         <v>5221</v>
       </c>
@@ -11731,7 +13860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D030E7C4-BD5A-40E8-BF7A-C2810B810BBB}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -11741,151 +13870,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="90"/>
+      <c r="B1" s="96"/>
       <c r="C1" s="57" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="91"/>
+      <c r="B2" s="97"/>
       <c r="C2" s="58">
         <v>8835</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="89"/>
+      <c r="B3" s="92"/>
       <c r="C3" s="59">
         <v>2597</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="89"/>
+      <c r="B4" s="92"/>
       <c r="C4" s="59">
         <v>7686</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="89"/>
+      <c r="B5" s="92"/>
       <c r="C5" s="59">
         <v>3140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="89"/>
+      <c r="B6" s="92"/>
       <c r="C6" s="59">
         <v>5043</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="89"/>
+      <c r="B7" s="92"/>
       <c r="C7" s="59">
         <v>1434</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="89"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="59">
         <v>3647</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="89"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="59">
         <v>8677</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="89"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="59">
         <v>5463</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="89"/>
+      <c r="B11" s="92"/>
       <c r="C11" s="59">
         <v>1035</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="89"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="59">
         <v>7412</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="89"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="59">
         <v>7759</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="92"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="60">
         <v>5614</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="93"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="61">
         <v>1538</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="94"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="62">
         <v>1867</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
@@ -11896,12 +14031,6 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/CODIGOS EQUIPOS.xlsx
+++ b/CODIGOS EQUIPOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalonso\Desktop\juegoQR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B62FA9-7C74-4F59-B195-3EB3BB790833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A60DC8E-BDAB-49DE-AAE9-3F1DC5AE22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,13 @@
     <sheet name="EQUIPOS QR" sheetId="1" r:id="rId1"/>
     <sheet name="EQUIPOS PRUEBAS" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja1" sheetId="10" r:id="rId3"/>
-    <sheet name="IMPRIMIR EQUIPOS" sheetId="9" r:id="rId4"/>
-    <sheet name="TARJETAS" sheetId="3" r:id="rId5"/>
-    <sheet name="CENTRO SOCIAL" sheetId="4" r:id="rId6"/>
-    <sheet name="AMBULANCIA" sheetId="5" r:id="rId7"/>
-    <sheet name="COMPRESOR" sheetId="6" r:id="rId8"/>
-    <sheet name="FINAL" sheetId="8" r:id="rId9"/>
+    <sheet name="CUENTAS" sheetId="11" r:id="rId4"/>
+    <sheet name="IMPRIMIR EQUIPOS" sheetId="9" r:id="rId5"/>
+    <sheet name="TARJETAS" sheetId="3" r:id="rId6"/>
+    <sheet name="CENTRO SOCIAL" sheetId="4" r:id="rId7"/>
+    <sheet name="AMBULANCIA" sheetId="5" r:id="rId8"/>
+    <sheet name="COMPRESOR" sheetId="6" r:id="rId9"/>
+    <sheet name="FINAL" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'EQUIPOS QR'!$A$1:$L$46</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="148">
   <si>
     <t>El Trío Dinámico</t>
   </si>
@@ -312,6 +313,183 @@
   <si>
     <t>Las 4 fantásticas</t>
   </si>
+  <si>
+    <t>EQUIPO 1</t>
+  </si>
+  <si>
+    <t>GUILLE</t>
+  </si>
+  <si>
+    <t>BIN LADEN</t>
+  </si>
+  <si>
+    <t>CARLOTA</t>
+  </si>
+  <si>
+    <t>PAGADO</t>
+  </si>
+  <si>
+    <t>PAGADO X</t>
+  </si>
+  <si>
+    <t>LAS 4 FANTASTICAS</t>
+  </si>
+  <si>
+    <t>IRENE</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>SOFIA</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>LOS JOHN DEERE</t>
+  </si>
+  <si>
+    <t>MARY</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>JAVI</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>LOS RAPOSOS DE ABARCA</t>
+  </si>
+  <si>
+    <t>PALENCIA</t>
+  </si>
+  <si>
+    <t>LOS LOCOS ESCAPISTAS</t>
+  </si>
+  <si>
+    <t>YO QUE SE</t>
+  </si>
+  <si>
+    <t>SILVIA</t>
+  </si>
+  <si>
+    <t>DESMADRADAS</t>
+  </si>
+  <si>
+    <t>DUNIA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>PAULA</t>
+  </si>
+  <si>
+    <t>MARINA</t>
+  </si>
+  <si>
+    <t>2 Y 1</t>
+  </si>
+  <si>
+    <t>TERE</t>
+  </si>
+  <si>
+    <t>DORABEL</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>GACELAS Y PEREZOSAS</t>
+  </si>
+  <si>
+    <t>LOS MAPACHINOS</t>
+  </si>
+  <si>
+    <t>SANTI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>LOS REVUELCATABOBES</t>
+  </si>
+  <si>
+    <t>LOS RONDILLEROS</t>
+  </si>
+  <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>LOS PSICOPATAS ANONIMOS</t>
+  </si>
+  <si>
+    <t>VERO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>JOSITO</t>
+  </si>
+  <si>
+    <t>CRISTINA</t>
+  </si>
+  <si>
+    <t>DEVOLVER</t>
+  </si>
+  <si>
+    <t>LAS HIPPY COLGAS</t>
+  </si>
+  <si>
+    <t>NURIA</t>
+  </si>
+  <si>
+    <t>NAIARA</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>LOS ESQUIZOFRENICOS</t>
+  </si>
+  <si>
+    <t>PABLO LECHON</t>
+  </si>
+  <si>
+    <t>JAVI LECHON</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>LUNATICO</t>
+  </si>
+  <si>
+    <t>S3GUR1D4D</t>
+  </si>
+  <si>
+    <t>0089-VALV-2026</t>
+  </si>
+  <si>
+    <t>FAMILIA</t>
+  </si>
+  <si>
+    <t>3AZ87</t>
+  </si>
+  <si>
+    <t>RESPUESTA</t>
+  </si>
+  <si>
+    <t>28/09/82</t>
+  </si>
 </sst>
 </file>
 
@@ -368,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="92">
+  <borders count="93">
     <border>
       <left/>
       <right/>
@@ -1397,75 +1575,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1575,11 +1684,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1776,6 +1969,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1785,15 +2014,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1803,6 +2023,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1833,65 +2062,72 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2233,30 +2469,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="66" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="67"/>
-      <c r="E1" s="66" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="66" t="s">
+      <c r="F1" s="79"/>
+      <c r="G1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="66" t="s">
+      <c r="H1" s="79"/>
+      <c r="I1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="66" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="67"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2769,30 +3005,30 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="66" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="66" t="s">
+      <c r="D17" s="79"/>
+      <c r="E17" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="66" t="s">
+      <c r="H17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="66" t="s">
+      <c r="J17" s="79"/>
+      <c r="K17" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="67"/>
+      <c r="L17" s="79"/>
     </row>
     <row r="18" spans="1:12" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
@@ -3306,30 +3542,30 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="66" t="s">
+      <c r="B33" s="79"/>
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="69" t="s">
+      <c r="D33" s="80"/>
+      <c r="E33" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="70"/>
-      <c r="G33" s="66" t="s">
+      <c r="F33" s="82"/>
+      <c r="G33" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="67"/>
-      <c r="I33" s="66" t="s">
+      <c r="H33" s="79"/>
+      <c r="I33" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="67"/>
-      <c r="K33" s="66" t="s">
+      <c r="J33" s="79"/>
+      <c r="K33" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="67"/>
+      <c r="L33" s="79"/>
     </row>
     <row r="34" spans="1:12" ht="13.5" customHeight="1">
       <c r="A34" s="1" t="s">
@@ -3842,30 +4078,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="67"/>
-      <c r="C49" s="66" t="s">
+      <c r="B49" s="79"/>
+      <c r="C49" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="67"/>
-      <c r="E49" s="66" t="s">
+      <c r="D49" s="79"/>
+      <c r="E49" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="67"/>
-      <c r="G49" s="66" t="s">
+      <c r="F49" s="79"/>
+      <c r="G49" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="66" t="s">
+      <c r="H49" s="79"/>
+      <c r="I49" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="67"/>
-      <c r="K49" s="66" t="s">
+      <c r="J49" s="79"/>
+      <c r="K49" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="67"/>
+      <c r="L49" s="79"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -4680,6 +4916,20 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="G49:H49"/>
@@ -4690,23 +4940,186 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D030E7C4-BD5A-40E8-BF7A-C2810B810BBB}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A1" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="106"/>
+      <c r="C2" s="58">
+        <v>8835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="104"/>
+      <c r="C3" s="59">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="104"/>
+      <c r="C4" s="59">
+        <v>7686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="104"/>
+      <c r="C5" s="59">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="59">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="104"/>
+      <c r="C7" s="59">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="104"/>
+      <c r="C8" s="59">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="104"/>
+      <c r="C9" s="59">
+        <v>8677</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="104"/>
+      <c r="C10" s="59">
+        <v>5463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="104"/>
+      <c r="C11" s="59">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="104"/>
+      <c r="C12" s="59">
+        <v>7412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="104"/>
+      <c r="C13" s="59">
+        <v>7759</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="107"/>
+      <c r="C14" s="60">
+        <v>5614</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="108"/>
+      <c r="C15" s="61">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A16" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="109"/>
+      <c r="C16" s="62">
+        <v>1867</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4722,30 +5135,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="66" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="67"/>
-      <c r="E1" s="66" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="66" t="s">
+      <c r="F1" s="79"/>
+      <c r="G1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="66" t="s">
+      <c r="H1" s="79"/>
+      <c r="I1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="66" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="67"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -5258,30 +5671,30 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:19" ht="13.5" customHeight="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="66" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="66" t="s">
+      <c r="D17" s="79"/>
+      <c r="E17" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="66" t="s">
+      <c r="H17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="66" t="s">
+      <c r="J17" s="79"/>
+      <c r="K17" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="67"/>
+      <c r="L17" s="79"/>
     </row>
     <row r="18" spans="1:19" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
@@ -5776,18 +6189,18 @@
       <c r="L30" s="5">
         <v>7759</v>
       </c>
-      <c r="N30" s="66" t="s">
+      <c r="N30" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="O30" s="67"/>
-      <c r="P30" s="66" t="s">
+      <c r="O30" s="79"/>
+      <c r="P30" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="66" t="s">
+      <c r="Q30" s="79"/>
+      <c r="R30" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="S30" s="67"/>
+      <c r="S30" s="79"/>
     </row>
     <row r="31" spans="1:19" ht="13.5" customHeight="1">
       <c r="A31" s="6"/>
@@ -5843,18 +6256,18 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="66" t="s">
+      <c r="B33" s="79"/>
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="69" t="s">
+      <c r="D33" s="80"/>
+      <c r="E33" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="70"/>
+      <c r="F33" s="82"/>
       <c r="N33" s="1" t="s">
         <v>35</v>
       </c>
@@ -6331,30 +6744,30 @@
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="67"/>
-      <c r="C49" s="66" t="s">
+      <c r="B49" s="79"/>
+      <c r="C49" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="67"/>
-      <c r="E49" s="66" t="s">
+      <c r="D49" s="79"/>
+      <c r="E49" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="67"/>
-      <c r="G49" s="66" t="s">
+      <c r="F49" s="79"/>
+      <c r="G49" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="66" t="s">
+      <c r="H49" s="79"/>
+      <c r="I49" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="67"/>
-      <c r="K49" s="66" t="s">
+      <c r="J49" s="79"/>
+      <c r="K49" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="67"/>
+      <c r="L49" s="79"/>
     </row>
     <row r="50" spans="1:12" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
@@ -7169,13 +7582,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="I1:J1"/>
@@ -7186,13 +7598,14 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
@@ -7210,42 +7623,43 @@
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="16" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="66" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="67"/>
-      <c r="E1" s="66" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="66" t="s">
+      <c r="F1" s="79"/>
+      <c r="G1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="66" t="s">
+      <c r="H1" s="79"/>
+      <c r="I1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="66" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="67"/>
-      <c r="M1" s="66" t="s">
+      <c r="L1" s="79"/>
+      <c r="M1" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="68"/>
-      <c r="O1" s="69" t="s">
+      <c r="N1" s="80"/>
+      <c r="O1" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="70"/>
+      <c r="P1" s="82"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -7914,34 +8328,34 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="66" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="66" t="s">
+      <c r="D17" s="79"/>
+      <c r="E17" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="66" t="s">
+      <c r="H17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="66" t="s">
+      <c r="J17" s="79"/>
+      <c r="K17" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="68"/>
-      <c r="M17" s="69" t="s">
+      <c r="L17" s="80"/>
+      <c r="M17" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="70"/>
+      <c r="N17" s="82"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
@@ -8532,334 +8946,365 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A50" s="98" t="s">
+    <row r="49" spans="1:9" ht="15.75" thickBot="1"/>
+    <row r="50" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A50" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="99" t="s">
+      <c r="B50" s="128" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="100" t="s">
+      <c r="C50" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="E50" s="108" t="s">
+      <c r="D50" s="130" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="F50" s="109" t="s">
+      <c r="G50" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="G50" s="109" t="s">
+      <c r="H50" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="H50" s="110" t="s">
+      <c r="I50" s="72" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="101" t="s">
+    <row r="51" spans="1:9">
+      <c r="A51" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="102" t="s">
+      <c r="C51" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="111" t="s">
+      <c r="D51" s="126">
+        <v>3995</v>
+      </c>
+      <c r="F51" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="F51" s="18" t="s">
+      <c r="G51" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="H51" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H51" s="112" t="s">
+      <c r="I51" s="74" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="103" t="s">
+    <row r="52" spans="1:9">
+      <c r="A52" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="103" t="s">
+      <c r="D52" s="116" t="s">
+        <v>141</v>
+      </c>
+      <c r="F52" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="G52" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="H52" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H52" s="113" t="s">
+      <c r="I52" s="75" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="103" t="s">
+    <row r="53" spans="1:9">
+      <c r="A53" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="103" t="s">
+      <c r="D53" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="F53" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="G53" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G53" s="23" t="s">
+      <c r="H53" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="113" t="s">
+      <c r="I53" s="75" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="104" t="s">
+    <row r="54" spans="1:9">
+      <c r="A54" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="104" t="s">
+      <c r="D54" s="116"/>
+      <c r="F54" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="23" t="s">
+      <c r="G54" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="G54" s="23" t="s">
+      <c r="H54" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H54" s="113" t="s">
+      <c r="I54" s="75" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="103" t="s">
+    <row r="55" spans="1:9">
+      <c r="A55" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="E55" s="103" t="s">
+      <c r="D55" s="116" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="F55" s="23" t="s">
+      <c r="G55" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="23" t="s">
+      <c r="H55" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H55" s="114" t="s">
+      <c r="I55" s="76" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="103" t="s">
+    <row r="56" spans="1:9">
+      <c r="A56" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C56" s="43" t="s">
+      <c r="C56" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="E56" s="103" t="s">
+      <c r="D56" s="116">
+        <v>852437</v>
+      </c>
+      <c r="F56" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="F56" s="23" t="s">
+      <c r="G56" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G56" s="24" t="s">
+      <c r="H56" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="113" t="s">
+      <c r="I56" s="75" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="103" t="s">
+    <row r="57" spans="1:9">
+      <c r="A57" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="43" t="s">
+      <c r="C57" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="103" t="s">
+      <c r="D57" s="116" t="s">
+        <v>143</v>
+      </c>
+      <c r="F57" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="24" t="s">
+      <c r="G57" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="H57" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="H57" s="113" t="s">
+      <c r="I57" s="75" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="104" t="s">
+    <row r="58" spans="1:9">
+      <c r="A58" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C58" s="43"/>
-      <c r="E58" s="104" t="s">
+      <c r="C58" s="114"/>
+      <c r="D58" s="116"/>
+      <c r="F58" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="23" t="s">
+      <c r="G58" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G58" s="23" t="s">
+      <c r="H58" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="H58" s="113" t="s">
+      <c r="I58" s="75" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="103" t="s">
+    <row r="59" spans="1:9">
+      <c r="A59" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="43" t="s">
+      <c r="C59" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="E59" s="103" t="s">
+      <c r="D59" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="23" t="s">
+      <c r="G59" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G59" s="23" t="s">
+      <c r="H59" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="H59" s="114" t="s">
+      <c r="I59" s="76" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="103" t="s">
+    <row r="60" spans="1:9">
+      <c r="A60" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="43" t="s">
+      <c r="C60" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="103" t="s">
+      <c r="D60" s="116" t="s">
+        <v>145</v>
+      </c>
+      <c r="F60" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="F60" s="23" t="s">
+      <c r="G60" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G60" s="24" t="s">
+      <c r="H60" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="H60" s="113" t="s">
+      <c r="I60" s="75" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="103" t="s">
+    <row r="61" spans="1:9">
+      <c r="A61" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="C61" s="43" t="s">
+      <c r="C61" s="114" t="s">
         <v>74</v>
       </c>
-      <c r="E61" s="103" t="s">
+      <c r="D61" s="116">
+        <v>4728</v>
+      </c>
+      <c r="F61" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="G61" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="G61" s="23" t="s">
+      <c r="H61" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="113" t="s">
+      <c r="I61" s="75" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="104" t="s">
+    <row r="62" spans="1:9">
+      <c r="A62" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="113" t="s">
         <v>75</v>
       </c>
-      <c r="C62" s="43" t="s">
+      <c r="C62" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="104" t="s">
+      <c r="D62" s="116"/>
+      <c r="F62" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="F62" s="23" t="s">
+      <c r="G62" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G62" s="23" t="s">
+      <c r="H62" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="113" t="s">
+      <c r="I62" s="75" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A63" s="105" t="s">
+    <row r="63" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A63" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="106" t="s">
+      <c r="B63" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="107" t="s">
+      <c r="C63" s="121" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="105" t="s">
+      <c r="D63" s="122"/>
+      <c r="F63" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F63" s="115" t="s">
+      <c r="G63" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="G63" s="115" t="s">
+      <c r="H63" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="H63" s="107" t="s">
+      <c r="I63" s="69" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9">
       <c r="B64" s="32"/>
       <c r="C64" s="6"/>
       <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8">
       <c r="B65" s="32"/>
@@ -8899,8 +9344,6 @@
         <v>53</v>
       </c>
       <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8">
@@ -8917,8 +9360,6 @@
         <v>57</v>
       </c>
       <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8">
@@ -8935,8 +9376,6 @@
         <v>59</v>
       </c>
       <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8">
@@ -8953,8 +9392,6 @@
         <v>68</v>
       </c>
       <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8">
@@ -8971,8 +9408,6 @@
         <v>65</v>
       </c>
       <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8">
@@ -8989,8 +9424,6 @@
         <v>67</v>
       </c>
       <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
       <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:8">
@@ -9007,8 +9440,6 @@
         <v>76</v>
       </c>
       <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:8">
@@ -9025,8 +9456,6 @@
         <v>72</v>
       </c>
       <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
       <c r="H75" s="6"/>
     </row>
     <row r="76" spans="1:8">
@@ -9043,8 +9472,6 @@
         <v>74</v>
       </c>
       <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1">
@@ -9067,11 +9494,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
@@ -9080,6 +9502,11 @@
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
@@ -9089,6 +9516,552 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B54EA29-0738-46A9-91B8-D8096AD5F857}">
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="110" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="110"/>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="110"/>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="111" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="111"/>
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="111"/>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="111"/>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="111" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="111"/>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="111"/>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="111"/>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="111" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="111"/>
+      <c r="B13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="111"/>
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="111" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="111"/>
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="111"/>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="111" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="111"/>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="111"/>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="111" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="111"/>
+      <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="111"/>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="111"/>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="111" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="111"/>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="111"/>
+      <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="111" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="111"/>
+      <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="111"/>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="111"/>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="111" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="111"/>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="111"/>
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="111"/>
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="111"/>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="111" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="111"/>
+      <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="111"/>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="112" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="111" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="111" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="111"/>
+      <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="111"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="111"/>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="111"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="111"/>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="111"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="111"/>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="111"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="111" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="111"/>
+      <c r="B47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="111"/>
+      <c r="B48" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="111"/>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="111" t="s">
+        <v>137</v>
+      </c>
+      <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="111"/>
+      <c r="B51" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="111"/>
+      <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="111"/>
+      <c r="B53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="D41:D45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A7BE38-5CCC-4F22-BE73-BF5B656FE56E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9100,38 +10073,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="74" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="74" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="78"/>
-      <c r="G1" s="74" t="s">
+      <c r="F1" s="87"/>
+      <c r="G1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="74" t="s">
+      <c r="H1" s="87"/>
+      <c r="I1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="78"/>
-      <c r="K1" s="74" t="s">
+      <c r="J1" s="87"/>
+      <c r="K1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="74" t="s">
+      <c r="L1" s="87"/>
+      <c r="M1" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76" t="s">
+      <c r="N1" s="84"/>
+      <c r="O1" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="77"/>
+      <c r="P1" s="86"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -9800,34 +10773,34 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="66" t="s">
+      <c r="B17" s="88"/>
+      <c r="C17" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="66" t="s">
+      <c r="D17" s="88"/>
+      <c r="E17" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="66" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="66" t="s">
+      <c r="H17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="66" t="s">
+      <c r="J17" s="79"/>
+      <c r="K17" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="68"/>
-      <c r="M17" s="69" t="s">
+      <c r="L17" s="80"/>
+      <c r="M17" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="70"/>
+      <c r="N17" s="82"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
@@ -10420,38 +11393,38 @@
     </row>
     <row r="48" ht="15.75" thickBot="1"/>
     <row r="49" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="66" t="s">
+      <c r="B49" s="88"/>
+      <c r="C49" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="66" t="s">
+      <c r="D49" s="88"/>
+      <c r="E49" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="66" t="s">
+      <c r="F49" s="88"/>
+      <c r="G49" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="71"/>
-      <c r="I49" s="66" t="s">
+      <c r="H49" s="88"/>
+      <c r="I49" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="71"/>
-      <c r="K49" s="66" t="s">
+      <c r="J49" s="88"/>
+      <c r="K49" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="71"/>
-      <c r="M49" s="66" t="s">
+      <c r="L49" s="88"/>
+      <c r="M49" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="N49" s="68"/>
-      <c r="O49" s="69" t="s">
+      <c r="N49" s="80"/>
+      <c r="O49" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="70"/>
+      <c r="P49" s="82"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
@@ -11105,34 +12078,34 @@
     </row>
     <row r="64" spans="1:16" ht="15.75" thickBot="1"/>
     <row r="65" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A65" s="66" t="s">
+      <c r="A65" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="71"/>
-      <c r="C65" s="66" t="s">
+      <c r="B65" s="88"/>
+      <c r="C65" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="71"/>
-      <c r="E65" s="66" t="s">
+      <c r="D65" s="88"/>
+      <c r="E65" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="F65" s="71"/>
-      <c r="G65" s="66" t="s">
+      <c r="F65" s="88"/>
+      <c r="G65" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="71"/>
-      <c r="I65" s="66" t="s">
+      <c r="H65" s="88"/>
+      <c r="I65" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J65" s="71"/>
-      <c r="K65" s="66" t="s">
+      <c r="J65" s="88"/>
+      <c r="K65" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="L65" s="73"/>
-      <c r="M65" s="69" t="s">
+      <c r="L65" s="89"/>
+      <c r="M65" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="N65" s="72"/>
+      <c r="N65" s="90"/>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="1" t="s">
@@ -11725,23 +12698,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="E49:F49"/>
@@ -11755,13 +12711,30 @@
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="I65:J65"/>
     <mergeCell ref="M49:N49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -12511,7 +13484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -12525,10 +13498,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="84"/>
+      <c r="B1" s="96"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -12546,10 +13519,10 @@
       <c r="K1" s="33"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="86"/>
+      <c r="B2" s="98"/>
       <c r="C2" s="39">
         <v>1764</v>
       </c>
@@ -12567,10 +13540,10 @@
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="82"/>
+      <c r="B3" s="94"/>
       <c r="C3" s="42">
         <v>4089</v>
       </c>
@@ -12588,10 +13561,10 @@
       <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="42">
         <v>8216</v>
       </c>
@@ -12609,10 +13582,10 @@
       <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="82"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="42">
         <v>4504</v>
       </c>
@@ -12630,10 +13603,10 @@
       <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="82"/>
+      <c r="B6" s="94"/>
       <c r="C6" s="42">
         <v>9390</v>
       </c>
@@ -12651,10 +13624,10 @@
       <c r="K6" s="33"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="42">
         <v>6014</v>
       </c>
@@ -12672,10 +13645,10 @@
       <c r="K7" s="33"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="82"/>
+      <c r="B8" s="94"/>
       <c r="C8" s="42">
         <v>2529</v>
       </c>
@@ -12693,10 +13666,10 @@
       <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="42">
         <v>7609</v>
       </c>
@@ -12714,10 +13687,10 @@
       <c r="K9" s="33"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="42">
         <v>6767</v>
       </c>
@@ -12735,10 +13708,10 @@
       <c r="K10" s="33"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="94"/>
       <c r="C11" s="42">
         <v>2068</v>
       </c>
@@ -12756,10 +13729,10 @@
       <c r="K11" s="33"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="42">
         <v>4498</v>
       </c>
@@ -12777,10 +13750,10 @@
       <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="42">
         <v>6914</v>
       </c>
@@ -12798,10 +13771,10 @@
       <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="44">
         <v>1837</v>
       </c>
@@ -12819,10 +13792,10 @@
       <c r="K14" s="33"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="46">
         <v>2357</v>
       </c>
@@ -12840,10 +13813,10 @@
       <c r="K15" s="33"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="80"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="48">
         <v>4593</v>
       </c>
@@ -13144,7 +14117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -13155,10 +14128,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="84"/>
+      <c r="B1" s="96"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -13170,10 +14143,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="86"/>
+      <c r="B2" s="98"/>
       <c r="C2" s="39">
         <v>7928</v>
       </c>
@@ -13185,10 +14158,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="82"/>
+      <c r="B3" s="94"/>
       <c r="C3" s="42">
         <v>4675</v>
       </c>
@@ -13200,10 +14173,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="42">
         <v>6301</v>
       </c>
@@ -13215,10 +14188,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="82"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="42">
         <v>1020</v>
       </c>
@@ -13230,10 +14203,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="82"/>
+      <c r="B6" s="94"/>
       <c r="C6" s="42">
         <v>1330</v>
       </c>
@@ -13245,10 +14218,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="42">
         <v>9856</v>
       </c>
@@ -13260,10 +14233,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="82"/>
+      <c r="B8" s="94"/>
       <c r="C8" s="42">
         <v>5817</v>
       </c>
@@ -13275,10 +14248,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="42">
         <v>1116</v>
       </c>
@@ -13290,10 +14263,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="42">
         <v>5806</v>
       </c>
@@ -13305,10 +14278,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="94"/>
       <c r="C11" s="42">
         <v>6523</v>
       </c>
@@ -13320,10 +14293,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="42">
         <v>8392</v>
       </c>
@@ -13335,10 +14308,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="42">
         <v>3739</v>
       </c>
@@ -13350,10 +14323,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="44">
         <v>3945</v>
       </c>
@@ -13365,10 +14338,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="46">
         <v>4433</v>
       </c>
@@ -13380,10 +14353,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="80"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="48">
         <v>1908</v>
       </c>
@@ -13502,7 +14475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -13513,10 +14486,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="84"/>
+      <c r="B1" s="96"/>
       <c r="C1" s="56" t="s">
         <v>83</v>
       </c>
@@ -13528,10 +14501,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="86"/>
+      <c r="B2" s="98"/>
       <c r="C2" s="39">
         <v>9201</v>
       </c>
@@ -13543,10 +14516,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="82"/>
+      <c r="B3" s="94"/>
       <c r="C3" s="42">
         <v>9634</v>
       </c>
@@ -13558,10 +14531,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="42">
         <v>6394</v>
       </c>
@@ -13573,10 +14546,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="82"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="42">
         <v>8597</v>
       </c>
@@ -13588,10 +14561,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="82"/>
+      <c r="B6" s="94"/>
       <c r="C6" s="42">
         <v>9947</v>
       </c>
@@ -13603,10 +14576,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="42">
         <v>2058</v>
       </c>
@@ -13618,10 +14591,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="82"/>
+      <c r="B8" s="94"/>
       <c r="C8" s="42">
         <v>4397</v>
       </c>
@@ -13633,10 +14606,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="42">
         <v>8746</v>
       </c>
@@ -13648,10 +14621,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="42">
         <v>2928</v>
       </c>
@@ -13663,10 +14636,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="94"/>
       <c r="C11" s="42">
         <v>8252</v>
       </c>
@@ -13678,10 +14651,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="42">
         <v>1583</v>
       </c>
@@ -13693,10 +14666,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="42">
         <v>5086</v>
       </c>
@@ -13708,10 +14681,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="89"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="44">
         <v>4590</v>
       </c>
@@ -13723,10 +14696,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="46">
         <v>1070</v>
       </c>
@@ -13738,10 +14711,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="80"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="48">
         <v>5221</v>
       </c>
@@ -13858,181 +14831,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D030E7C4-BD5A-40E8-BF7A-C2810B810BBB}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="83" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="57" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="58">
-        <v>8835</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="59">
-        <v>2597</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="59">
-        <v>7686</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="81" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="59">
-        <v>3140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="81" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="59">
-        <v>5043</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="59">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="59">
-        <v>3647</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="59">
-        <v>8677</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="59">
-        <v>5463</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="81" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="59">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="81" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="59">
-        <v>7412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="81" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="59">
-        <v>7759</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="60">
-        <v>5614</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="90" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="61">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A16" s="79" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="62">
-        <v>1867</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>